--- a/F_grouping/reference/backtesting_score.xlsx
+++ b/F_grouping/reference/backtesting_score.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="133">
   <si>
     <t>factor_name</t>
   </si>
@@ -46,6 +46,9 @@
     <t>I001</t>
   </si>
   <si>
+    <t>G001</t>
+  </si>
+  <si>
     <t>I002</t>
   </si>
   <si>
@@ -92,9 +95,6 @@
   </si>
   <si>
     <t>G002</t>
-  </si>
-  <si>
-    <t>G001</t>
   </si>
   <si>
     <t>L005</t>
@@ -744,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -831,7 +831,7 @@
         <v>4</v>
       </c>
       <c r="I3">
-        <v>0.525</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -860,12 +860,12 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>0.525</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
@@ -894,7 +894,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="b">
         <v>1</v>
@@ -918,12 +918,12 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>0.521875</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
@@ -947,12 +947,12 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>0.5145833333333332</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" t="b">
         <v>1</v>
@@ -961,10 +961,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -976,12 +976,12 @@
         <v>4</v>
       </c>
       <c r="I8">
-        <v>0.5104166666666666</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B9" t="b">
         <v>1</v>
@@ -990,10 +990,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -1005,12 +1005,12 @@
         <v>4</v>
       </c>
       <c r="I9">
-        <v>0.509375</v>
+        <v>0.51875</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B10" t="b">
         <v>1</v>
@@ -1034,12 +1034,12 @@
         <v>4</v>
       </c>
       <c r="I10">
-        <v>0.5052083333333334</v>
+        <v>0.51875</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B11" t="b">
         <v>1</v>
@@ -1063,12 +1063,12 @@
         <v>4</v>
       </c>
       <c r="I11">
-        <v>0.5052083333333334</v>
+        <v>0.5145833333333332</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B12" t="b">
         <v>1</v>
@@ -1092,24 +1092,24 @@
         <v>4</v>
       </c>
       <c r="I12">
-        <v>0.478125</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
       </c>
       <c r="D13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
@@ -1118,15 +1118,15 @@
         <v>1</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13">
-        <v>0.5354166666666667</v>
+        <v>0.509375</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B14" t="b">
         <v>1</v>
@@ -1135,7 +1135,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -1147,15 +1147,15 @@
         <v>1</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14">
-        <v>0.5302083333333333</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B15" t="b">
         <v>1</v>
@@ -1164,7 +1164,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -1176,15 +1176,15 @@
         <v>1</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15">
-        <v>0.5302083333333333</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B16" t="b">
         <v>1</v>
@@ -1196,7 +1196,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
@@ -1205,24 +1205,24 @@
         <v>1</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I16">
-        <v>0.5291666666666667</v>
+        <v>0.478125</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="b">
         <v>1</v>
       </c>
       <c r="D17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -1237,12 +1237,12 @@
         <v>3</v>
       </c>
       <c r="I17">
-        <v>0.5291666666666667</v>
+        <v>0.5354166666666667</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B18" t="b">
         <v>1</v>
@@ -1266,12 +1266,12 @@
         <v>3</v>
       </c>
       <c r="I18">
-        <v>0.5291666666666666</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B19" t="b">
         <v>1</v>
@@ -1295,12 +1295,12 @@
         <v>3</v>
       </c>
       <c r="I19">
-        <v>0.528125</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B20" t="b">
         <v>1</v>
@@ -1324,12 +1324,12 @@
         <v>3</v>
       </c>
       <c r="I20">
-        <v>0.5229166666666666</v>
+        <v>0.5291666666666667</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B21" t="b">
         <v>1</v>
@@ -1353,12 +1353,12 @@
         <v>3</v>
       </c>
       <c r="I21">
-        <v>0.521875</v>
+        <v>0.5291666666666667</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B22" t="b">
         <v>1</v>
@@ -1382,12 +1382,12 @@
         <v>3</v>
       </c>
       <c r="I22">
-        <v>0.521875</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B23" t="b">
         <v>1</v>
@@ -1411,15 +1411,15 @@
         <v>3</v>
       </c>
       <c r="I23">
-        <v>0.5166666666666666</v>
+        <v>0.528125</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="b">
         <v>1</v>
@@ -1428,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -1440,12 +1440,12 @@
         <v>3</v>
       </c>
       <c r="I24">
-        <v>0.5114583333333333</v>
+        <v>0.5229166666666666</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B25" t="b">
         <v>1</v>
@@ -1469,15 +1469,15 @@
         <v>3</v>
       </c>
       <c r="I25">
-        <v>0.5114583333333333</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" t="b">
         <v>1</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1498,12 +1498,12 @@
         <v>3</v>
       </c>
       <c r="I26">
-        <v>0.5104166666666666</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B27" t="b">
         <v>1</v>
@@ -1527,15 +1527,15 @@
         <v>3</v>
       </c>
       <c r="I27">
-        <v>0.509375</v>
+        <v>0.5166666666666666</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="b">
         <v>1</v>
@@ -1544,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1556,12 +1556,12 @@
         <v>3</v>
       </c>
       <c r="I28">
-        <v>0.5083333333333334</v>
+        <v>0.5114583333333333</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B29" t="b">
         <v>1</v>
@@ -1585,15 +1585,15 @@
         <v>3</v>
       </c>
       <c r="I29">
-        <v>0.5083333333333334</v>
+        <v>0.5114583333333333</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="b">
         <v>1</v>
@@ -1602,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
@@ -1614,12 +1614,12 @@
         <v>3</v>
       </c>
       <c r="I30">
-        <v>0.5072916666666666</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B31" t="b">
         <v>1</v>
@@ -1643,12 +1643,12 @@
         <v>3</v>
       </c>
       <c r="I31">
-        <v>0.5062500000000001</v>
+        <v>0.509375</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B32" t="b">
         <v>1</v>
@@ -1672,12 +1672,12 @@
         <v>3</v>
       </c>
       <c r="I32">
-        <v>0.5062500000000001</v>
+        <v>0.5083333333333334</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B33" t="b">
         <v>1</v>
@@ -1701,12 +1701,12 @@
         <v>3</v>
       </c>
       <c r="I33">
-        <v>0.5062500000000001</v>
+        <v>0.5083333333333334</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B34" t="b">
         <v>1</v>
@@ -1730,12 +1730,12 @@
         <v>3</v>
       </c>
       <c r="I34">
-        <v>0.5</v>
+        <v>0.5072916666666666</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B35" t="b">
         <v>1</v>
@@ -1759,12 +1759,12 @@
         <v>3</v>
       </c>
       <c r="I35">
-        <v>0.4989583333333334</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B36" t="b">
         <v>1</v>
@@ -1776,24 +1776,24 @@
         <v>0</v>
       </c>
       <c r="E36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
       </c>
       <c r="G36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>3</v>
       </c>
       <c r="I36">
-        <v>0.4989583333333333</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B37" t="b">
         <v>1</v>
@@ -1817,12 +1817,12 @@
         <v>3</v>
       </c>
       <c r="I37">
-        <v>0.4979166666666666</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="B38" t="b">
         <v>1</v>
@@ -1846,12 +1846,12 @@
         <v>3</v>
       </c>
       <c r="I38">
-        <v>0.4958333333333334</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B39" t="b">
         <v>1</v>
@@ -1863,24 +1863,24 @@
         <v>0</v>
       </c>
       <c r="E39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
       </c>
       <c r="G39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <v>3</v>
       </c>
       <c r="I39">
-        <v>0.4947916666666666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B40" t="b">
         <v>1</v>
@@ -1904,12 +1904,12 @@
         <v>3</v>
       </c>
       <c r="I40">
-        <v>0.4916666666666666</v>
+        <v>0.4989583333333334</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B41" t="b">
         <v>1</v>
@@ -1921,24 +1921,24 @@
         <v>0</v>
       </c>
       <c r="E41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="b">
         <v>0</v>
       </c>
       <c r="G41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41">
         <v>3</v>
       </c>
       <c r="I41">
-        <v>0.490625</v>
+        <v>0.4989583333333333</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B42" t="b">
         <v>1</v>
@@ -1962,12 +1962,12 @@
         <v>3</v>
       </c>
       <c r="I42">
-        <v>0.4885416666666667</v>
+        <v>0.4979166666666666</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B43" t="b">
         <v>1</v>
@@ -1991,12 +1991,12 @@
         <v>3</v>
       </c>
       <c r="I43">
-        <v>0.4875</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B44" t="b">
         <v>1</v>
@@ -2008,24 +2008,24 @@
         <v>0</v>
       </c>
       <c r="E44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
       </c>
       <c r="G44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44">
         <v>3</v>
       </c>
       <c r="I44">
-        <v>0.484375</v>
+        <v>0.4947916666666666</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B45" t="b">
         <v>1</v>
@@ -2049,12 +2049,12 @@
         <v>3</v>
       </c>
       <c r="I45">
-        <v>0.4802083333333333</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B46" t="b">
         <v>1</v>
@@ -2078,12 +2078,12 @@
         <v>3</v>
       </c>
       <c r="I46">
-        <v>0.4770833333333333</v>
+        <v>0.490625</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B47" t="b">
         <v>1</v>
@@ -2101,18 +2101,18 @@
         <v>0</v>
       </c>
       <c r="G47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47">
-        <v>0.5291666666666666</v>
+        <v>0.4885416666666667</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B48" t="b">
         <v>1</v>
@@ -2130,18 +2130,18 @@
         <v>0</v>
       </c>
       <c r="G48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I48">
-        <v>0.5270833333333332</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B49" t="b">
         <v>1</v>
@@ -2159,18 +2159,18 @@
         <v>0</v>
       </c>
       <c r="G49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49">
-        <v>0.5260416666666667</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B50" t="b">
         <v>1</v>
@@ -2188,18 +2188,18 @@
         <v>0</v>
       </c>
       <c r="G50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I50">
-        <v>0.5260416666666667</v>
+        <v>0.4802083333333333</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B51" t="b">
         <v>1</v>
@@ -2217,18 +2217,18 @@
         <v>0</v>
       </c>
       <c r="G51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51">
-        <v>0.5239583333333334</v>
+        <v>0.4770833333333333</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B52" t="b">
         <v>1</v>
@@ -2252,12 +2252,12 @@
         <v>2</v>
       </c>
       <c r="I52">
-        <v>0.5177083333333334</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B53" t="b">
         <v>1</v>
@@ -2281,12 +2281,12 @@
         <v>2</v>
       </c>
       <c r="I53">
-        <v>0.5166666666666667</v>
+        <v>0.5270833333333332</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B54" t="b">
         <v>1</v>
@@ -2310,12 +2310,12 @@
         <v>2</v>
       </c>
       <c r="I54">
-        <v>0.515625</v>
+        <v>0.5260416666666667</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B55" t="b">
         <v>1</v>
@@ -2339,12 +2339,12 @@
         <v>2</v>
       </c>
       <c r="I55">
-        <v>0.5135416666666666</v>
+        <v>0.5260416666666667</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B56" t="b">
         <v>1</v>
@@ -2368,12 +2368,12 @@
         <v>2</v>
       </c>
       <c r="I56">
-        <v>0.5135416666666666</v>
+        <v>0.5239583333333334</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B57" t="b">
         <v>1</v>
@@ -2397,12 +2397,12 @@
         <v>2</v>
       </c>
       <c r="I57">
-        <v>0.5104166666666667</v>
+        <v>0.5177083333333334</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B58" t="b">
         <v>1</v>
@@ -2426,12 +2426,12 @@
         <v>2</v>
       </c>
       <c r="I58">
-        <v>0.5083333333333333</v>
+        <v>0.5166666666666667</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B59" t="b">
         <v>1</v>
@@ -2455,12 +2455,12 @@
         <v>2</v>
       </c>
       <c r="I59">
-        <v>0.5083333333333333</v>
+        <v>0.515625</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B60" t="b">
         <v>1</v>
@@ -2484,12 +2484,12 @@
         <v>2</v>
       </c>
       <c r="I60">
-        <v>0.5062500000000001</v>
+        <v>0.5135416666666666</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B61" t="b">
         <v>1</v>
@@ -2513,12 +2513,12 @@
         <v>2</v>
       </c>
       <c r="I61">
-        <v>0.50625</v>
+        <v>0.5135416666666666</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B62" t="b">
         <v>1</v>
@@ -2542,12 +2542,12 @@
         <v>2</v>
       </c>
       <c r="I62">
-        <v>0.503125</v>
+        <v>0.5104166666666667</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B63" t="b">
         <v>1</v>
@@ -2571,12 +2571,12 @@
         <v>2</v>
       </c>
       <c r="I63">
-        <v>0.503125</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B64" t="b">
         <v>1</v>
@@ -2600,12 +2600,12 @@
         <v>2</v>
       </c>
       <c r="I64">
-        <v>0.503125</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B65" t="b">
         <v>1</v>
@@ -2629,12 +2629,12 @@
         <v>2</v>
       </c>
       <c r="I65">
-        <v>0.5020833333333333</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B66" t="b">
         <v>1</v>
@@ -2658,12 +2658,12 @@
         <v>2</v>
       </c>
       <c r="I66">
-        <v>0.5010416666666667</v>
+        <v>0.50625</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B67" t="b">
         <v>1</v>
@@ -2687,12 +2687,12 @@
         <v>2</v>
       </c>
       <c r="I67">
-        <v>0.5</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B68" t="b">
         <v>1</v>
@@ -2716,12 +2716,12 @@
         <v>2</v>
       </c>
       <c r="I68">
-        <v>0.5</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B69" t="b">
         <v>1</v>
@@ -2745,12 +2745,12 @@
         <v>2</v>
       </c>
       <c r="I69">
-        <v>0.5</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B70" t="b">
         <v>1</v>
@@ -2774,12 +2774,12 @@
         <v>2</v>
       </c>
       <c r="I70">
-        <v>0.5</v>
+        <v>0.5020833333333333</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B71" t="b">
         <v>1</v>
@@ -2803,12 +2803,12 @@
         <v>2</v>
       </c>
       <c r="I71">
-        <v>0.4989583333333333</v>
+        <v>0.5010416666666667</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B72" t="b">
         <v>1</v>
@@ -2832,12 +2832,12 @@
         <v>2</v>
       </c>
       <c r="I72">
-        <v>0.496875</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B73" t="b">
         <v>1</v>
@@ -2861,12 +2861,12 @@
         <v>2</v>
       </c>
       <c r="I73">
-        <v>0.4958333333333334</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B74" t="b">
         <v>1</v>
@@ -2890,12 +2890,12 @@
         <v>2</v>
       </c>
       <c r="I74">
-        <v>0.4958333333333334</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B75" t="b">
         <v>1</v>
@@ -2919,12 +2919,12 @@
         <v>2</v>
       </c>
       <c r="I75">
-        <v>0.4958333333333334</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B76" t="b">
         <v>1</v>
@@ -2948,12 +2948,12 @@
         <v>2</v>
       </c>
       <c r="I76">
-        <v>0.4958333333333333</v>
+        <v>0.4989583333333333</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B77" t="b">
         <v>1</v>
@@ -2977,12 +2977,12 @@
         <v>2</v>
       </c>
       <c r="I77">
-        <v>0.4947916666666667</v>
+        <v>0.496875</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B78" t="b">
         <v>1</v>
@@ -3006,12 +3006,12 @@
         <v>2</v>
       </c>
       <c r="I78">
-        <v>0.4947916666666667</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B79" t="b">
         <v>1</v>
@@ -3035,12 +3035,12 @@
         <v>2</v>
       </c>
       <c r="I79">
-        <v>0.4947916666666667</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B80" t="b">
         <v>1</v>
@@ -3064,12 +3064,12 @@
         <v>2</v>
       </c>
       <c r="I80">
-        <v>0.4947916666666667</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B81" t="b">
         <v>1</v>
@@ -3093,12 +3093,12 @@
         <v>2</v>
       </c>
       <c r="I81">
-        <v>0.4927083333333334</v>
+        <v>0.4958333333333333</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B82" t="b">
         <v>1</v>
@@ -3122,12 +3122,12 @@
         <v>2</v>
       </c>
       <c r="I82">
-        <v>0.4927083333333333</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B83" t="b">
         <v>1</v>
@@ -3151,12 +3151,12 @@
         <v>2</v>
       </c>
       <c r="I83">
-        <v>0.4927083333333333</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B84" t="b">
         <v>1</v>
@@ -3180,12 +3180,12 @@
         <v>2</v>
       </c>
       <c r="I84">
-        <v>0.4927083333333333</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B85" t="b">
         <v>1</v>
@@ -3209,12 +3209,12 @@
         <v>2</v>
       </c>
       <c r="I85">
-        <v>0.4916666666666667</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B86" t="b">
         <v>1</v>
@@ -3238,12 +3238,12 @@
         <v>2</v>
       </c>
       <c r="I86">
-        <v>0.4916666666666666</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B87" t="b">
         <v>1</v>
@@ -3267,15 +3267,15 @@
         <v>2</v>
       </c>
       <c r="I87">
-        <v>0.4895833333333333</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C88" t="b">
         <v>1</v>
@@ -3290,18 +3290,18 @@
         <v>0</v>
       </c>
       <c r="G88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88">
         <v>2</v>
       </c>
       <c r="I88">
-        <v>0.4885416666666666</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B89" t="b">
         <v>1</v>
@@ -3325,12 +3325,12 @@
         <v>2</v>
       </c>
       <c r="I89">
-        <v>0.4885416666666666</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B90" t="b">
         <v>1</v>
@@ -3354,12 +3354,12 @@
         <v>2</v>
       </c>
       <c r="I90">
-        <v>0.4864583333333333</v>
+        <v>0.4916666666666667</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B91" t="b">
         <v>1</v>
@@ -3383,12 +3383,12 @@
         <v>2</v>
       </c>
       <c r="I91">
-        <v>0.4854166666666666</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B92" t="b">
         <v>1</v>
@@ -3412,15 +3412,15 @@
         <v>2</v>
       </c>
       <c r="I92">
-        <v>0.484375</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" t="b">
         <v>1</v>
@@ -3435,18 +3435,18 @@
         <v>0</v>
       </c>
       <c r="G93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93">
         <v>2</v>
       </c>
       <c r="I93">
-        <v>0.484375</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B94" t="b">
         <v>1</v>
@@ -3470,12 +3470,12 @@
         <v>2</v>
       </c>
       <c r="I94">
-        <v>0.4833333333333334</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B95" t="b">
         <v>1</v>
@@ -3499,12 +3499,12 @@
         <v>2</v>
       </c>
       <c r="I95">
-        <v>0.4833333333333333</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B96" t="b">
         <v>1</v>
@@ -3528,12 +3528,12 @@
         <v>2</v>
       </c>
       <c r="I96">
-        <v>0.4833333333333333</v>
+        <v>0.4854166666666666</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B97" t="b">
         <v>1</v>
@@ -3557,12 +3557,12 @@
         <v>2</v>
       </c>
       <c r="I97">
-        <v>0.4802083333333334</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B98" t="b">
         <v>1</v>
@@ -3586,12 +3586,12 @@
         <v>2</v>
       </c>
       <c r="I98">
-        <v>0.4791666666666667</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B99" t="b">
         <v>1</v>
@@ -3615,12 +3615,12 @@
         <v>2</v>
       </c>
       <c r="I99">
-        <v>0.4770833333333333</v>
+        <v>0.4833333333333334</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B100" t="b">
         <v>1</v>
@@ -3644,12 +3644,12 @@
         <v>2</v>
       </c>
       <c r="I100">
-        <v>0.4739583333333333</v>
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B101" t="b">
         <v>1</v>
@@ -3673,18 +3673,18 @@
         <v>2</v>
       </c>
       <c r="I101">
-        <v>0.4739583333333333</v>
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B102" t="b">
         <v>1</v>
       </c>
       <c r="C102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D102" t="b">
         <v>0</v>
@@ -3699,18 +3699,18 @@
         <v>0</v>
       </c>
       <c r="H102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I102">
-        <v>0.5354166666666667</v>
+        <v>0.4802083333333334</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C103" t="b">
         <v>1</v>
@@ -3728,18 +3728,18 @@
         <v>0</v>
       </c>
       <c r="H103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I103">
-        <v>0.53125</v>
+        <v>0.4791666666666667</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C104" t="b">
         <v>1</v>
@@ -3757,18 +3757,18 @@
         <v>0</v>
       </c>
       <c r="H104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I104">
-        <v>0.5125</v>
+        <v>0.4770833333333333</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C105" t="b">
         <v>1</v>
@@ -3786,18 +3786,18 @@
         <v>0</v>
       </c>
       <c r="H105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I105">
-        <v>0.5104166666666666</v>
+        <v>0.4739583333333333</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C106" t="b">
         <v>1</v>
@@ -3815,21 +3815,21 @@
         <v>0</v>
       </c>
       <c r="H106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I106">
-        <v>0.5104166666666666</v>
+        <v>0.4739583333333333</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107" t="b">
         <v>0</v>
@@ -3847,12 +3847,12 @@
         <v>1</v>
       </c>
       <c r="I107">
-        <v>0.5104166666666666</v>
+        <v>0.5354166666666667</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B108" t="b">
         <v>0</v>
@@ -3876,12 +3876,12 @@
         <v>1</v>
       </c>
       <c r="I108">
-        <v>0.5104166666666666</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B109" t="b">
         <v>0</v>
@@ -3905,12 +3905,12 @@
         <v>1</v>
       </c>
       <c r="I109">
-        <v>0.5052083333333334</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B110" t="b">
         <v>0</v>
@@ -3934,18 +3934,18 @@
         <v>1</v>
       </c>
       <c r="I110">
-        <v>0.5052083333333334</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D111" t="b">
         <v>0</v>
@@ -3963,18 +3963,18 @@
         <v>1</v>
       </c>
       <c r="I111">
-        <v>0.5041666666666667</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112" t="b">
         <v>0</v>
@@ -3992,18 +3992,18 @@
         <v>1</v>
       </c>
       <c r="I112">
-        <v>0.5041666666666667</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D113" t="b">
         <v>0</v>
@@ -4021,18 +4021,18 @@
         <v>1</v>
       </c>
       <c r="I113">
-        <v>0.4947916666666667</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D114" t="b">
         <v>0</v>
@@ -4050,12 +4050,12 @@
         <v>1</v>
       </c>
       <c r="I114">
-        <v>0.4927083333333333</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B115" t="b">
         <v>0</v>
@@ -4079,12 +4079,12 @@
         <v>1</v>
       </c>
       <c r="I115">
-        <v>0.4895833333333333</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B116" t="b">
         <v>1</v>
@@ -4108,18 +4108,18 @@
         <v>1</v>
       </c>
       <c r="I116">
-        <v>0.4875</v>
+        <v>0.5041666666666667</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117" t="b">
         <v>0</v>
@@ -4137,18 +4137,18 @@
         <v>1</v>
       </c>
       <c r="I117">
-        <v>0.4864583333333333</v>
+        <v>0.5041666666666667</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118" t="b">
         <v>0</v>
@@ -4166,18 +4166,18 @@
         <v>1</v>
       </c>
       <c r="I118">
-        <v>0.4864583333333333</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D119" t="b">
         <v>0</v>
@@ -4195,18 +4195,18 @@
         <v>1</v>
       </c>
       <c r="I119">
-        <v>0.4864583333333333</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120" t="b">
         <v>0</v>
@@ -4224,12 +4224,12 @@
         <v>1</v>
       </c>
       <c r="I120">
-        <v>0.4854166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B121" t="b">
         <v>1</v>
@@ -4253,18 +4253,18 @@
         <v>1</v>
       </c>
       <c r="I121">
-        <v>0.4760416666666667</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D122" t="b">
         <v>0</v>
@@ -4282,18 +4282,18 @@
         <v>1</v>
       </c>
       <c r="I122">
-        <v>0.4614583333333333</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123" t="b">
         <v>0</v>
@@ -4311,18 +4311,18 @@
         <v>1</v>
       </c>
       <c r="I123">
-        <v>0.45</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D124" t="b">
         <v>0</v>
@@ -4340,35 +4340,180 @@
         <v>1</v>
       </c>
       <c r="I124">
-        <v>0.4260416666666667</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" t="s">
+        <v>127</v>
+      </c>
+      <c r="B125" t="b">
+        <v>1</v>
+      </c>
+      <c r="C125" t="b">
+        <v>0</v>
+      </c>
+      <c r="D125" t="b">
+        <v>0</v>
+      </c>
+      <c r="E125" t="b">
+        <v>0</v>
+      </c>
+      <c r="F125" t="b">
+        <v>0</v>
+      </c>
+      <c r="G125" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>1</v>
+      </c>
+      <c r="I125">
+        <v>0.4854166666666666</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" t="s">
+        <v>128</v>
+      </c>
+      <c r="B126" t="b">
+        <v>1</v>
+      </c>
+      <c r="C126" t="b">
+        <v>0</v>
+      </c>
+      <c r="D126" t="b">
+        <v>0</v>
+      </c>
+      <c r="E126" t="b">
+        <v>0</v>
+      </c>
+      <c r="F126" t="b">
+        <v>0</v>
+      </c>
+      <c r="G126" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>1</v>
+      </c>
+      <c r="I126">
+        <v>0.4760416666666667</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" t="s">
+        <v>129</v>
+      </c>
+      <c r="B127" t="b">
+        <v>1</v>
+      </c>
+      <c r="C127" t="b">
+        <v>0</v>
+      </c>
+      <c r="D127" t="b">
+        <v>0</v>
+      </c>
+      <c r="E127" t="b">
+        <v>0</v>
+      </c>
+      <c r="F127" t="b">
+        <v>0</v>
+      </c>
+      <c r="G127" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>1</v>
+      </c>
+      <c r="I127">
+        <v>0.4614583333333333</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" t="s">
+        <v>130</v>
+      </c>
+      <c r="B128" t="b">
+        <v>1</v>
+      </c>
+      <c r="C128" t="b">
+        <v>0</v>
+      </c>
+      <c r="D128" t="b">
+        <v>0</v>
+      </c>
+      <c r="E128" t="b">
+        <v>0</v>
+      </c>
+      <c r="F128" t="b">
+        <v>0</v>
+      </c>
+      <c r="G128" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>1</v>
+      </c>
+      <c r="I128">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" t="s">
+        <v>131</v>
+      </c>
+      <c r="B129" t="b">
+        <v>1</v>
+      </c>
+      <c r="C129" t="b">
+        <v>0</v>
+      </c>
+      <c r="D129" t="b">
+        <v>0</v>
+      </c>
+      <c r="E129" t="b">
+        <v>0</v>
+      </c>
+      <c r="F129" t="b">
+        <v>0</v>
+      </c>
+      <c r="G129" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>1</v>
+      </c>
+      <c r="I129">
+        <v>0.4260416666666667</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" t="s">
         <v>132</v>
       </c>
-      <c r="B125" t="b">
-        <v>0</v>
-      </c>
-      <c r="C125" t="b">
-        <v>0</v>
-      </c>
-      <c r="D125" t="b">
-        <v>0</v>
-      </c>
-      <c r="E125" t="b">
-        <v>0</v>
-      </c>
-      <c r="F125" t="b">
-        <v>0</v>
-      </c>
-      <c r="G125" t="b">
-        <v>0</v>
-      </c>
-      <c r="H125">
-        <v>0</v>
-      </c>
-      <c r="I125">
+      <c r="B130" t="b">
+        <v>0</v>
+      </c>
+      <c r="C130" t="b">
+        <v>0</v>
+      </c>
+      <c r="D130" t="b">
+        <v>0</v>
+      </c>
+      <c r="E130" t="b">
+        <v>0</v>
+      </c>
+      <c r="F130" t="b">
+        <v>0</v>
+      </c>
+      <c r="G130" t="b">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
         <v>0.478125</v>
       </c>
     </row>

--- a/F_grouping/reference/backtesting_score.xlsx
+++ b/F_grouping/reference/backtesting_score.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t>factor_name</t>
   </si>
@@ -52,15 +52,15 @@
     <t>I002</t>
   </si>
   <si>
+    <t>W004_I_signal</t>
+  </si>
+  <si>
     <t>W001</t>
   </si>
   <si>
     <t>W002</t>
   </si>
   <si>
-    <t>W004_I_signal</t>
-  </si>
-  <si>
     <t>G004</t>
   </si>
   <si>
@@ -70,73 +70,73 @@
     <t>I004</t>
   </si>
   <si>
+    <t>W004_P_signal</t>
+  </si>
+  <si>
+    <t>O005</t>
+  </si>
+  <si>
+    <t>P002</t>
+  </si>
+  <si>
+    <t>V002</t>
+  </si>
+  <si>
+    <t>V004</t>
+  </si>
+  <si>
+    <t>I003</t>
+  </si>
+  <si>
+    <t>I024</t>
+  </si>
+  <si>
+    <t>G002</t>
+  </si>
+  <si>
+    <t>L005</t>
+  </si>
+  <si>
+    <t>W003_I</t>
+  </si>
+  <si>
+    <t>W004_I</t>
+  </si>
+  <si>
+    <t>F005</t>
+  </si>
+  <si>
+    <t>P016</t>
+  </si>
+  <si>
+    <t>W004_signal</t>
+  </si>
+  <si>
+    <t>F002</t>
+  </si>
+  <si>
+    <t>W003_W</t>
+  </si>
+  <si>
+    <t>L023</t>
+  </si>
+  <si>
+    <t>L025</t>
+  </si>
+  <si>
+    <t>L011</t>
+  </si>
+  <si>
+    <t>G003</t>
+  </si>
+  <si>
+    <t>V003</t>
+  </si>
+  <si>
+    <t>V016</t>
+  </si>
+  <si>
     <t>P001</t>
-  </si>
-  <si>
-    <t>W004_P_signal</t>
-  </si>
-  <si>
-    <t>O005</t>
-  </si>
-  <si>
-    <t>P002</t>
-  </si>
-  <si>
-    <t>V002</t>
-  </si>
-  <si>
-    <t>V004</t>
-  </si>
-  <si>
-    <t>I003</t>
-  </si>
-  <si>
-    <t>I024</t>
-  </si>
-  <si>
-    <t>G002</t>
-  </si>
-  <si>
-    <t>L005</t>
-  </si>
-  <si>
-    <t>W003_I</t>
-  </si>
-  <si>
-    <t>W004_I</t>
-  </si>
-  <si>
-    <t>F005</t>
-  </si>
-  <si>
-    <t>P016</t>
-  </si>
-  <si>
-    <t>W004_signal</t>
-  </si>
-  <si>
-    <t>F002</t>
-  </si>
-  <si>
-    <t>W003_W</t>
-  </si>
-  <si>
-    <t>L023</t>
-  </si>
-  <si>
-    <t>L025</t>
-  </si>
-  <si>
-    <t>L011</t>
-  </si>
-  <si>
-    <t>G003</t>
-  </si>
-  <si>
-    <t>V003</t>
-  </si>
-  <si>
-    <t>V016</t>
   </si>
   <si>
     <t>V001</t>
@@ -744,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:I125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -865,7 +865,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
@@ -889,12 +889,12 @@
         <v>4</v>
       </c>
       <c r="I5">
-        <v>0.525</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="b">
         <v>1</v>
@@ -918,12 +918,12 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>0.525</v>
+        <v>0.51875</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
@@ -947,12 +947,12 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>0.525</v>
+        <v>0.51875</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" t="b">
         <v>1</v>
@@ -976,12 +976,12 @@
         <v>4</v>
       </c>
       <c r="I8">
-        <v>0.521875</v>
+        <v>0.5145833333333332</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B9" t="b">
         <v>1</v>
@@ -990,10 +990,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -1005,12 +1005,12 @@
         <v>4</v>
       </c>
       <c r="I9">
-        <v>0.51875</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="b">
         <v>1</v>
@@ -1019,10 +1019,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -1034,12 +1034,12 @@
         <v>4</v>
       </c>
       <c r="I10">
-        <v>0.51875</v>
+        <v>0.509375</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B11" t="b">
         <v>1</v>
@@ -1063,12 +1063,12 @@
         <v>4</v>
       </c>
       <c r="I11">
-        <v>0.5145833333333332</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B12" t="b">
         <v>1</v>
@@ -1092,24 +1092,24 @@
         <v>4</v>
       </c>
       <c r="I12">
-        <v>0.5104166666666666</v>
+        <v>0.478125</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
       </c>
       <c r="D13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
@@ -1118,15 +1118,15 @@
         <v>1</v>
       </c>
       <c r="H13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>0.509375</v>
+        <v>0.5354166666666667</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B14" t="b">
         <v>1</v>
@@ -1135,7 +1135,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -1147,15 +1147,15 @@
         <v>1</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>0.5052083333333334</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B15" t="b">
         <v>1</v>
@@ -1164,7 +1164,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -1176,15 +1176,15 @@
         <v>1</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>0.5052083333333334</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B16" t="b">
         <v>1</v>
@@ -1196,7 +1196,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
@@ -1205,24 +1205,24 @@
         <v>1</v>
       </c>
       <c r="H16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <v>0.478125</v>
+        <v>0.5291666666666667</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="b">
         <v>1</v>
       </c>
       <c r="D17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -1237,12 +1237,12 @@
         <v>3</v>
       </c>
       <c r="I17">
-        <v>0.5354166666666667</v>
+        <v>0.5291666666666667</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B18" t="b">
         <v>1</v>
@@ -1266,12 +1266,12 @@
         <v>3</v>
       </c>
       <c r="I18">
-        <v>0.5302083333333333</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B19" t="b">
         <v>1</v>
@@ -1295,12 +1295,12 @@
         <v>3</v>
       </c>
       <c r="I19">
-        <v>0.5302083333333333</v>
+        <v>0.5229166666666666</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B20" t="b">
         <v>1</v>
@@ -1324,12 +1324,12 @@
         <v>3</v>
       </c>
       <c r="I20">
-        <v>0.5291666666666667</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B21" t="b">
         <v>1</v>
@@ -1353,12 +1353,12 @@
         <v>3</v>
       </c>
       <c r="I21">
-        <v>0.5291666666666667</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B22" t="b">
         <v>1</v>
@@ -1382,15 +1382,15 @@
         <v>3</v>
       </c>
       <c r="I22">
-        <v>0.5291666666666666</v>
+        <v>0.5166666666666666</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="b">
         <v>1</v>
@@ -1399,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1411,12 +1411,12 @@
         <v>3</v>
       </c>
       <c r="I23">
-        <v>0.528125</v>
+        <v>0.5114583333333333</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B24" t="b">
         <v>1</v>
@@ -1440,15 +1440,15 @@
         <v>3</v>
       </c>
       <c r="I24">
-        <v>0.5229166666666666</v>
+        <v>0.5114583333333333</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="b">
         <v>1</v>
@@ -1457,7 +1457,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
@@ -1469,12 +1469,12 @@
         <v>3</v>
       </c>
       <c r="I25">
-        <v>0.521875</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B26" t="b">
         <v>1</v>
@@ -1498,12 +1498,12 @@
         <v>3</v>
       </c>
       <c r="I26">
-        <v>0.521875</v>
+        <v>0.509375</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B27" t="b">
         <v>1</v>
@@ -1527,15 +1527,15 @@
         <v>3</v>
       </c>
       <c r="I27">
-        <v>0.5166666666666666</v>
+        <v>0.5083333333333334</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="b">
         <v>1</v>
@@ -1544,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1556,12 +1556,12 @@
         <v>3</v>
       </c>
       <c r="I28">
-        <v>0.5114583333333333</v>
+        <v>0.5083333333333334</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B29" t="b">
         <v>1</v>
@@ -1585,15 +1585,15 @@
         <v>3</v>
       </c>
       <c r="I29">
-        <v>0.5114583333333333</v>
+        <v>0.5072916666666666</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="b">
         <v>1</v>
@@ -1602,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
@@ -1614,12 +1614,12 @@
         <v>3</v>
       </c>
       <c r="I30">
-        <v>0.5104166666666666</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B31" t="b">
         <v>1</v>
@@ -1643,12 +1643,12 @@
         <v>3</v>
       </c>
       <c r="I31">
-        <v>0.509375</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B32" t="b">
         <v>1</v>
@@ -1672,12 +1672,12 @@
         <v>3</v>
       </c>
       <c r="I32">
-        <v>0.5083333333333334</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B33" t="b">
         <v>1</v>
@@ -1701,12 +1701,12 @@
         <v>3</v>
       </c>
       <c r="I33">
-        <v>0.5083333333333334</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B34" t="b">
         <v>1</v>
@@ -1730,12 +1730,12 @@
         <v>3</v>
       </c>
       <c r="I34">
-        <v>0.5072916666666666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B35" t="b">
         <v>1</v>
@@ -1759,12 +1759,12 @@
         <v>3</v>
       </c>
       <c r="I35">
-        <v>0.5062500000000001</v>
+        <v>0.4989583333333334</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B36" t="b">
         <v>1</v>
@@ -1776,24 +1776,24 @@
         <v>0</v>
       </c>
       <c r="E36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
       </c>
       <c r="G36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36">
         <v>3</v>
       </c>
       <c r="I36">
-        <v>0.5062500000000001</v>
+        <v>0.4989583333333333</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B37" t="b">
         <v>1</v>
@@ -1817,12 +1817,12 @@
         <v>3</v>
       </c>
       <c r="I37">
-        <v>0.5062500000000001</v>
+        <v>0.4979166666666666</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="B38" t="b">
         <v>1</v>
@@ -1846,12 +1846,12 @@
         <v>3</v>
       </c>
       <c r="I38">
-        <v>0.5052083333333334</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B39" t="b">
         <v>1</v>
@@ -1863,24 +1863,24 @@
         <v>0</v>
       </c>
       <c r="E39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
       </c>
       <c r="G39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>3</v>
       </c>
       <c r="I39">
-        <v>0.5</v>
+        <v>0.4947916666666666</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B40" t="b">
         <v>1</v>
@@ -1904,12 +1904,12 @@
         <v>3</v>
       </c>
       <c r="I40">
-        <v>0.4989583333333334</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B41" t="b">
         <v>1</v>
@@ -1921,24 +1921,24 @@
         <v>0</v>
       </c>
       <c r="E41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="b">
         <v>0</v>
       </c>
       <c r="G41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
         <v>3</v>
       </c>
       <c r="I41">
-        <v>0.4989583333333333</v>
+        <v>0.490625</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B42" t="b">
         <v>1</v>
@@ -1962,12 +1962,12 @@
         <v>3</v>
       </c>
       <c r="I42">
-        <v>0.4979166666666666</v>
+        <v>0.4885416666666667</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B43" t="b">
         <v>1</v>
@@ -1991,12 +1991,12 @@
         <v>3</v>
       </c>
       <c r="I43">
-        <v>0.4958333333333334</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B44" t="b">
         <v>1</v>
@@ -2008,24 +2008,24 @@
         <v>0</v>
       </c>
       <c r="E44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
       </c>
       <c r="G44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44">
         <v>3</v>
       </c>
       <c r="I44">
-        <v>0.4947916666666666</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B45" t="b">
         <v>1</v>
@@ -2049,12 +2049,12 @@
         <v>3</v>
       </c>
       <c r="I45">
-        <v>0.4916666666666666</v>
+        <v>0.4802083333333333</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B46" t="b">
         <v>1</v>
@@ -2078,12 +2078,12 @@
         <v>3</v>
       </c>
       <c r="I46">
-        <v>0.490625</v>
+        <v>0.4770833333333333</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B47" t="b">
         <v>1</v>
@@ -2101,18 +2101,18 @@
         <v>0</v>
       </c>
       <c r="G47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I47">
-        <v>0.4885416666666667</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B48" t="b">
         <v>1</v>
@@ -2130,18 +2130,18 @@
         <v>0</v>
       </c>
       <c r="G48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I48">
-        <v>0.4875</v>
+        <v>0.5270833333333332</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B49" t="b">
         <v>1</v>
@@ -2159,18 +2159,18 @@
         <v>0</v>
       </c>
       <c r="G49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I49">
-        <v>0.484375</v>
+        <v>0.5260416666666667</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B50" t="b">
         <v>1</v>
@@ -2188,18 +2188,18 @@
         <v>0</v>
       </c>
       <c r="G50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I50">
-        <v>0.4802083333333333</v>
+        <v>0.5260416666666667</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B51" t="b">
         <v>1</v>
@@ -2217,18 +2217,18 @@
         <v>0</v>
       </c>
       <c r="G51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I51">
-        <v>0.4770833333333333</v>
+        <v>0.5239583333333334</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B52" t="b">
         <v>1</v>
@@ -2252,12 +2252,12 @@
         <v>2</v>
       </c>
       <c r="I52">
-        <v>0.5291666666666666</v>
+        <v>0.5177083333333334</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B53" t="b">
         <v>1</v>
@@ -2281,12 +2281,12 @@
         <v>2</v>
       </c>
       <c r="I53">
-        <v>0.5270833333333332</v>
+        <v>0.5166666666666667</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B54" t="b">
         <v>1</v>
@@ -2310,12 +2310,12 @@
         <v>2</v>
       </c>
       <c r="I54">
-        <v>0.5260416666666667</v>
+        <v>0.515625</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B55" t="b">
         <v>1</v>
@@ -2339,12 +2339,12 @@
         <v>2</v>
       </c>
       <c r="I55">
-        <v>0.5260416666666667</v>
+        <v>0.5135416666666666</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B56" t="b">
         <v>1</v>
@@ -2368,12 +2368,12 @@
         <v>2</v>
       </c>
       <c r="I56">
-        <v>0.5239583333333334</v>
+        <v>0.5135416666666666</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B57" t="b">
         <v>1</v>
@@ -2397,12 +2397,12 @@
         <v>2</v>
       </c>
       <c r="I57">
-        <v>0.5177083333333334</v>
+        <v>0.5104166666666667</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B58" t="b">
         <v>1</v>
@@ -2426,12 +2426,12 @@
         <v>2</v>
       </c>
       <c r="I58">
-        <v>0.5166666666666667</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B59" t="b">
         <v>1</v>
@@ -2455,12 +2455,12 @@
         <v>2</v>
       </c>
       <c r="I59">
-        <v>0.515625</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B60" t="b">
         <v>1</v>
@@ -2484,12 +2484,12 @@
         <v>2</v>
       </c>
       <c r="I60">
-        <v>0.5135416666666666</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B61" t="b">
         <v>1</v>
@@ -2513,12 +2513,12 @@
         <v>2</v>
       </c>
       <c r="I61">
-        <v>0.5135416666666666</v>
+        <v>0.50625</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B62" t="b">
         <v>1</v>
@@ -2542,12 +2542,12 @@
         <v>2</v>
       </c>
       <c r="I62">
-        <v>0.5104166666666667</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B63" t="b">
         <v>1</v>
@@ -2571,12 +2571,12 @@
         <v>2</v>
       </c>
       <c r="I63">
-        <v>0.5083333333333333</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B64" t="b">
         <v>1</v>
@@ -2600,12 +2600,12 @@
         <v>2</v>
       </c>
       <c r="I64">
-        <v>0.5083333333333333</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B65" t="b">
         <v>1</v>
@@ -2629,12 +2629,12 @@
         <v>2</v>
       </c>
       <c r="I65">
-        <v>0.5062500000000001</v>
+        <v>0.5020833333333333</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B66" t="b">
         <v>1</v>
@@ -2658,12 +2658,12 @@
         <v>2</v>
       </c>
       <c r="I66">
-        <v>0.50625</v>
+        <v>0.5010416666666667</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B67" t="b">
         <v>1</v>
@@ -2687,12 +2687,12 @@
         <v>2</v>
       </c>
       <c r="I67">
-        <v>0.503125</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B68" t="b">
         <v>1</v>
@@ -2716,12 +2716,12 @@
         <v>2</v>
       </c>
       <c r="I68">
-        <v>0.503125</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B69" t="b">
         <v>1</v>
@@ -2745,12 +2745,12 @@
         <v>2</v>
       </c>
       <c r="I69">
-        <v>0.503125</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B70" t="b">
         <v>1</v>
@@ -2774,12 +2774,12 @@
         <v>2</v>
       </c>
       <c r="I70">
-        <v>0.5020833333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B71" t="b">
         <v>1</v>
@@ -2803,12 +2803,12 @@
         <v>2</v>
       </c>
       <c r="I71">
-        <v>0.5010416666666667</v>
+        <v>0.4989583333333333</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B72" t="b">
         <v>1</v>
@@ -2832,12 +2832,12 @@
         <v>2</v>
       </c>
       <c r="I72">
-        <v>0.5</v>
+        <v>0.496875</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B73" t="b">
         <v>1</v>
@@ -2861,12 +2861,12 @@
         <v>2</v>
       </c>
       <c r="I73">
-        <v>0.5</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B74" t="b">
         <v>1</v>
@@ -2890,12 +2890,12 @@
         <v>2</v>
       </c>
       <c r="I74">
-        <v>0.5</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B75" t="b">
         <v>1</v>
@@ -2919,12 +2919,12 @@
         <v>2</v>
       </c>
       <c r="I75">
-        <v>0.5</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B76" t="b">
         <v>1</v>
@@ -2948,12 +2948,12 @@
         <v>2</v>
       </c>
       <c r="I76">
-        <v>0.4989583333333333</v>
+        <v>0.4958333333333333</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B77" t="b">
         <v>1</v>
@@ -2977,12 +2977,12 @@
         <v>2</v>
       </c>
       <c r="I77">
-        <v>0.496875</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B78" t="b">
         <v>1</v>
@@ -3006,12 +3006,12 @@
         <v>2</v>
       </c>
       <c r="I78">
-        <v>0.4958333333333334</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B79" t="b">
         <v>1</v>
@@ -3035,12 +3035,12 @@
         <v>2</v>
       </c>
       <c r="I79">
-        <v>0.4958333333333334</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B80" t="b">
         <v>1</v>
@@ -3064,12 +3064,12 @@
         <v>2</v>
       </c>
       <c r="I80">
-        <v>0.4958333333333334</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B81" t="b">
         <v>1</v>
@@ -3093,12 +3093,12 @@
         <v>2</v>
       </c>
       <c r="I81">
-        <v>0.4958333333333333</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B82" t="b">
         <v>1</v>
@@ -3122,12 +3122,12 @@
         <v>2</v>
       </c>
       <c r="I82">
-        <v>0.4947916666666667</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B83" t="b">
         <v>1</v>
@@ -3151,12 +3151,12 @@
         <v>2</v>
       </c>
       <c r="I83">
-        <v>0.4947916666666667</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B84" t="b">
         <v>1</v>
@@ -3180,12 +3180,12 @@
         <v>2</v>
       </c>
       <c r="I84">
-        <v>0.4947916666666667</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B85" t="b">
         <v>1</v>
@@ -3209,12 +3209,12 @@
         <v>2</v>
       </c>
       <c r="I85">
-        <v>0.4947916666666667</v>
+        <v>0.4916666666666667</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B86" t="b">
         <v>1</v>
@@ -3238,12 +3238,12 @@
         <v>2</v>
       </c>
       <c r="I86">
-        <v>0.4927083333333334</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B87" t="b">
         <v>1</v>
@@ -3267,15 +3267,15 @@
         <v>2</v>
       </c>
       <c r="I87">
-        <v>0.4927083333333333</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" t="b">
         <v>1</v>
@@ -3290,18 +3290,18 @@
         <v>0</v>
       </c>
       <c r="G88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88">
         <v>2</v>
       </c>
       <c r="I88">
-        <v>0.4927083333333333</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B89" t="b">
         <v>1</v>
@@ -3325,12 +3325,12 @@
         <v>2</v>
       </c>
       <c r="I89">
-        <v>0.4927083333333333</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B90" t="b">
         <v>1</v>
@@ -3354,12 +3354,12 @@
         <v>2</v>
       </c>
       <c r="I90">
-        <v>0.4916666666666667</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B91" t="b">
         <v>1</v>
@@ -3383,12 +3383,12 @@
         <v>2</v>
       </c>
       <c r="I91">
-        <v>0.4916666666666666</v>
+        <v>0.4854166666666666</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B92" t="b">
         <v>1</v>
@@ -3412,15 +3412,15 @@
         <v>2</v>
       </c>
       <c r="I92">
-        <v>0.4895833333333333</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" t="b">
         <v>1</v>
@@ -3435,18 +3435,18 @@
         <v>0</v>
       </c>
       <c r="G93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93">
         <v>2</v>
       </c>
       <c r="I93">
-        <v>0.4885416666666666</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B94" t="b">
         <v>1</v>
@@ -3470,12 +3470,12 @@
         <v>2</v>
       </c>
       <c r="I94">
-        <v>0.4885416666666666</v>
+        <v>0.4833333333333334</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B95" t="b">
         <v>1</v>
@@ -3499,12 +3499,12 @@
         <v>2</v>
       </c>
       <c r="I95">
-        <v>0.4864583333333333</v>
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B96" t="b">
         <v>1</v>
@@ -3528,12 +3528,12 @@
         <v>2</v>
       </c>
       <c r="I96">
-        <v>0.4854166666666666</v>
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B97" t="b">
         <v>1</v>
@@ -3557,12 +3557,12 @@
         <v>2</v>
       </c>
       <c r="I97">
-        <v>0.484375</v>
+        <v>0.4802083333333334</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B98" t="b">
         <v>1</v>
@@ -3586,12 +3586,12 @@
         <v>2</v>
       </c>
       <c r="I98">
-        <v>0.484375</v>
+        <v>0.4791666666666667</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B99" t="b">
         <v>1</v>
@@ -3615,12 +3615,12 @@
         <v>2</v>
       </c>
       <c r="I99">
-        <v>0.4833333333333334</v>
+        <v>0.4770833333333333</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B100" t="b">
         <v>1</v>
@@ -3644,12 +3644,12 @@
         <v>2</v>
       </c>
       <c r="I100">
-        <v>0.4833333333333333</v>
+        <v>0.4739583333333333</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B101" t="b">
         <v>1</v>
@@ -3673,18 +3673,18 @@
         <v>2</v>
       </c>
       <c r="I101">
-        <v>0.4833333333333333</v>
+        <v>0.4739583333333333</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B102" t="b">
         <v>1</v>
       </c>
       <c r="C102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102" t="b">
         <v>0</v>
@@ -3699,18 +3699,18 @@
         <v>0</v>
       </c>
       <c r="H102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I102">
-        <v>0.4802083333333334</v>
+        <v>0.5354166666666667</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C103" t="b">
         <v>1</v>
@@ -3728,18 +3728,18 @@
         <v>0</v>
       </c>
       <c r="H103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I103">
-        <v>0.4791666666666667</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C104" t="b">
         <v>1</v>
@@ -3757,18 +3757,18 @@
         <v>0</v>
       </c>
       <c r="H104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I104">
-        <v>0.4770833333333333</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C105" t="b">
         <v>1</v>
@@ -3786,18 +3786,18 @@
         <v>0</v>
       </c>
       <c r="H105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I105">
-        <v>0.4739583333333333</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C106" t="b">
         <v>1</v>
@@ -3815,21 +3815,21 @@
         <v>0</v>
       </c>
       <c r="H106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I106">
-        <v>0.4739583333333333</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107" t="b">
         <v>0</v>
@@ -3847,12 +3847,12 @@
         <v>1</v>
       </c>
       <c r="I107">
-        <v>0.5354166666666667</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B108" t="b">
         <v>0</v>
@@ -3876,12 +3876,12 @@
         <v>1</v>
       </c>
       <c r="I108">
-        <v>0.53125</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B109" t="b">
         <v>0</v>
@@ -3905,12 +3905,12 @@
         <v>1</v>
       </c>
       <c r="I109">
-        <v>0.5125</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B110" t="b">
         <v>0</v>
@@ -3934,18 +3934,18 @@
         <v>1</v>
       </c>
       <c r="I110">
-        <v>0.5104166666666666</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111" t="b">
         <v>0</v>
@@ -3963,18 +3963,18 @@
         <v>1</v>
       </c>
       <c r="I111">
-        <v>0.5104166666666666</v>
+        <v>0.5041666666666667</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112" t="b">
         <v>0</v>
@@ -3992,18 +3992,18 @@
         <v>1</v>
       </c>
       <c r="I112">
-        <v>0.5104166666666666</v>
+        <v>0.5041666666666667</v>
       </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113" t="b">
         <v>0</v>
@@ -4021,18 +4021,18 @@
         <v>1</v>
       </c>
       <c r="I113">
-        <v>0.5104166666666666</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D114" t="b">
         <v>0</v>
@@ -4050,12 +4050,12 @@
         <v>1</v>
       </c>
       <c r="I114">
-        <v>0.5052083333333334</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B115" t="b">
         <v>0</v>
@@ -4079,12 +4079,12 @@
         <v>1</v>
       </c>
       <c r="I115">
-        <v>0.5052083333333334</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B116" t="b">
         <v>1</v>
@@ -4108,18 +4108,18 @@
         <v>1</v>
       </c>
       <c r="I116">
-        <v>0.5041666666666667</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117" t="b">
         <v>0</v>
@@ -4137,18 +4137,18 @@
         <v>1</v>
       </c>
       <c r="I117">
-        <v>0.5041666666666667</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118" t="b">
         <v>0</v>
@@ -4166,18 +4166,18 @@
         <v>1</v>
       </c>
       <c r="I118">
-        <v>0.4947916666666667</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D119" t="b">
         <v>0</v>
@@ -4195,18 +4195,18 @@
         <v>1</v>
       </c>
       <c r="I119">
-        <v>0.4927083333333333</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120" t="b">
         <v>0</v>
@@ -4224,12 +4224,12 @@
         <v>1</v>
       </c>
       <c r="I120">
-        <v>0.4895833333333333</v>
+        <v>0.4854166666666666</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B121" t="b">
         <v>1</v>
@@ -4253,18 +4253,18 @@
         <v>1</v>
       </c>
       <c r="I121">
-        <v>0.4875</v>
+        <v>0.4760416666666667</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D122" t="b">
         <v>0</v>
@@ -4282,18 +4282,18 @@
         <v>1</v>
       </c>
       <c r="I122">
-        <v>0.4864583333333333</v>
+        <v>0.4614583333333333</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123" t="b">
         <v>0</v>
@@ -4311,18 +4311,18 @@
         <v>1</v>
       </c>
       <c r="I123">
-        <v>0.4864583333333333</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D124" t="b">
         <v>0</v>
@@ -4340,15 +4340,15 @@
         <v>1</v>
       </c>
       <c r="I124">
-        <v>0.4864583333333333</v>
+        <v>0.4260416666666667</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C125" t="b">
         <v>0</v>
@@ -4366,154 +4366,9 @@
         <v>0</v>
       </c>
       <c r="H125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I125">
-        <v>0.4854166666666666</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9">
-      <c r="A126" t="s">
-        <v>128</v>
-      </c>
-      <c r="B126" t="b">
-        <v>1</v>
-      </c>
-      <c r="C126" t="b">
-        <v>0</v>
-      </c>
-      <c r="D126" t="b">
-        <v>0</v>
-      </c>
-      <c r="E126" t="b">
-        <v>0</v>
-      </c>
-      <c r="F126" t="b">
-        <v>0</v>
-      </c>
-      <c r="G126" t="b">
-        <v>0</v>
-      </c>
-      <c r="H126">
-        <v>1</v>
-      </c>
-      <c r="I126">
-        <v>0.4760416666666667</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9">
-      <c r="A127" t="s">
-        <v>129</v>
-      </c>
-      <c r="B127" t="b">
-        <v>1</v>
-      </c>
-      <c r="C127" t="b">
-        <v>0</v>
-      </c>
-      <c r="D127" t="b">
-        <v>0</v>
-      </c>
-      <c r="E127" t="b">
-        <v>0</v>
-      </c>
-      <c r="F127" t="b">
-        <v>0</v>
-      </c>
-      <c r="G127" t="b">
-        <v>0</v>
-      </c>
-      <c r="H127">
-        <v>1</v>
-      </c>
-      <c r="I127">
-        <v>0.4614583333333333</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9">
-      <c r="A128" t="s">
-        <v>130</v>
-      </c>
-      <c r="B128" t="b">
-        <v>1</v>
-      </c>
-      <c r="C128" t="b">
-        <v>0</v>
-      </c>
-      <c r="D128" t="b">
-        <v>0</v>
-      </c>
-      <c r="E128" t="b">
-        <v>0</v>
-      </c>
-      <c r="F128" t="b">
-        <v>0</v>
-      </c>
-      <c r="G128" t="b">
-        <v>0</v>
-      </c>
-      <c r="H128">
-        <v>1</v>
-      </c>
-      <c r="I128">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9">
-      <c r="A129" t="s">
-        <v>131</v>
-      </c>
-      <c r="B129" t="b">
-        <v>1</v>
-      </c>
-      <c r="C129" t="b">
-        <v>0</v>
-      </c>
-      <c r="D129" t="b">
-        <v>0</v>
-      </c>
-      <c r="E129" t="b">
-        <v>0</v>
-      </c>
-      <c r="F129" t="b">
-        <v>0</v>
-      </c>
-      <c r="G129" t="b">
-        <v>0</v>
-      </c>
-      <c r="H129">
-        <v>1</v>
-      </c>
-      <c r="I129">
-        <v>0.4260416666666667</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9">
-      <c r="A130" t="s">
-        <v>132</v>
-      </c>
-      <c r="B130" t="b">
-        <v>0</v>
-      </c>
-      <c r="C130" t="b">
-        <v>0</v>
-      </c>
-      <c r="D130" t="b">
-        <v>0</v>
-      </c>
-      <c r="E130" t="b">
-        <v>0</v>
-      </c>
-      <c r="F130" t="b">
-        <v>0</v>
-      </c>
-      <c r="G130" t="b">
-        <v>0</v>
-      </c>
-      <c r="H130">
-        <v>0</v>
-      </c>
-      <c r="I130">
         <v>0.478125</v>
       </c>
     </row>

--- a/F_grouping/reference/backtesting_score.xlsx
+++ b/F_grouping/reference/backtesting_score.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="133">
   <si>
     <t>factor_name</t>
   </si>
@@ -744,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1851,7 +1851,7 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B39" t="b">
         <v>1</v>
@@ -1863,24 +1863,24 @@
         <v>0</v>
       </c>
       <c r="E39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
       </c>
       <c r="G39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <v>3</v>
       </c>
       <c r="I39">
-        <v>0.4947916666666666</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="b">
         <v>1</v>
@@ -1892,24 +1892,24 @@
         <v>0</v>
       </c>
       <c r="E40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
       </c>
       <c r="G40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40">
         <v>3</v>
       </c>
       <c r="I40">
-        <v>0.4916666666666666</v>
+        <v>0.4947916666666666</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="B41" t="b">
         <v>1</v>
@@ -1933,12 +1933,12 @@
         <v>3</v>
       </c>
       <c r="I41">
-        <v>0.490625</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="B42" t="b">
         <v>1</v>
@@ -1962,12 +1962,12 @@
         <v>3</v>
       </c>
       <c r="I42">
-        <v>0.4885416666666667</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B43" t="b">
         <v>1</v>
@@ -1991,12 +1991,12 @@
         <v>3</v>
       </c>
       <c r="I43">
-        <v>0.4875</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B44" t="b">
         <v>1</v>
@@ -2020,12 +2020,12 @@
         <v>3</v>
       </c>
       <c r="I44">
-        <v>0.484375</v>
+        <v>0.490625</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B45" t="b">
         <v>1</v>
@@ -2049,12 +2049,12 @@
         <v>3</v>
       </c>
       <c r="I45">
-        <v>0.4802083333333333</v>
+        <v>0.4885416666666667</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B46" t="b">
         <v>1</v>
@@ -2078,12 +2078,12 @@
         <v>3</v>
       </c>
       <c r="I46">
-        <v>0.4770833333333333</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B47" t="b">
         <v>1</v>
@@ -2101,18 +2101,18 @@
         <v>0</v>
       </c>
       <c r="G47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47">
-        <v>0.5291666666666666</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B48" t="b">
         <v>1</v>
@@ -2130,18 +2130,18 @@
         <v>0</v>
       </c>
       <c r="G48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I48">
-        <v>0.5270833333333332</v>
+        <v>0.4802083333333333</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B49" t="b">
         <v>1</v>
@@ -2159,18 +2159,18 @@
         <v>0</v>
       </c>
       <c r="G49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49">
-        <v>0.5260416666666667</v>
+        <v>0.4770833333333333</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B50" t="b">
         <v>1</v>
@@ -2194,12 +2194,12 @@
         <v>2</v>
       </c>
       <c r="I50">
-        <v>0.5260416666666667</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B51" t="b">
         <v>1</v>
@@ -2223,12 +2223,12 @@
         <v>2</v>
       </c>
       <c r="I51">
-        <v>0.5239583333333334</v>
+        <v>0.5270833333333332</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B52" t="b">
         <v>1</v>
@@ -2252,12 +2252,12 @@
         <v>2</v>
       </c>
       <c r="I52">
-        <v>0.5177083333333334</v>
+        <v>0.5260416666666667</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B53" t="b">
         <v>1</v>
@@ -2281,12 +2281,12 @@
         <v>2</v>
       </c>
       <c r="I53">
-        <v>0.5166666666666667</v>
+        <v>0.5260416666666667</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B54" t="b">
         <v>1</v>
@@ -2310,12 +2310,12 @@
         <v>2</v>
       </c>
       <c r="I54">
-        <v>0.515625</v>
+        <v>0.5239583333333334</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B55" t="b">
         <v>1</v>
@@ -2339,12 +2339,12 @@
         <v>2</v>
       </c>
       <c r="I55">
-        <v>0.5135416666666666</v>
+        <v>0.5177083333333334</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B56" t="b">
         <v>1</v>
@@ -2368,12 +2368,12 @@
         <v>2</v>
       </c>
       <c r="I56">
-        <v>0.5135416666666666</v>
+        <v>0.5166666666666667</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B57" t="b">
         <v>1</v>
@@ -2397,12 +2397,12 @@
         <v>2</v>
       </c>
       <c r="I57">
-        <v>0.5104166666666667</v>
+        <v>0.515625</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B58" t="b">
         <v>1</v>
@@ -2426,12 +2426,12 @@
         <v>2</v>
       </c>
       <c r="I58">
-        <v>0.5083333333333333</v>
+        <v>0.5135416666666666</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B59" t="b">
         <v>1</v>
@@ -2455,12 +2455,12 @@
         <v>2</v>
       </c>
       <c r="I59">
-        <v>0.5083333333333333</v>
+        <v>0.5135416666666666</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B60" t="b">
         <v>1</v>
@@ -2484,12 +2484,12 @@
         <v>2</v>
       </c>
       <c r="I60">
-        <v>0.5062500000000001</v>
+        <v>0.5104166666666667</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B61" t="b">
         <v>1</v>
@@ -2513,12 +2513,12 @@
         <v>2</v>
       </c>
       <c r="I61">
-        <v>0.50625</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B62" t="b">
         <v>1</v>
@@ -2542,12 +2542,12 @@
         <v>2</v>
       </c>
       <c r="I62">
-        <v>0.503125</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B63" t="b">
         <v>1</v>
@@ -2571,12 +2571,12 @@
         <v>2</v>
       </c>
       <c r="I63">
-        <v>0.503125</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B64" t="b">
         <v>1</v>
@@ -2600,12 +2600,12 @@
         <v>2</v>
       </c>
       <c r="I64">
-        <v>0.503125</v>
+        <v>0.50625</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B65" t="b">
         <v>1</v>
@@ -2629,12 +2629,12 @@
         <v>2</v>
       </c>
       <c r="I65">
-        <v>0.5020833333333333</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B66" t="b">
         <v>1</v>
@@ -2658,12 +2658,12 @@
         <v>2</v>
       </c>
       <c r="I66">
-        <v>0.5010416666666667</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B67" t="b">
         <v>1</v>
@@ -2687,12 +2687,12 @@
         <v>2</v>
       </c>
       <c r="I67">
-        <v>0.5</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B68" t="b">
         <v>1</v>
@@ -2716,12 +2716,12 @@
         <v>2</v>
       </c>
       <c r="I68">
-        <v>0.5</v>
+        <v>0.5020833333333333</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B69" t="b">
         <v>1</v>
@@ -2745,12 +2745,12 @@
         <v>2</v>
       </c>
       <c r="I69">
-        <v>0.5</v>
+        <v>0.5010416666666667</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="B70" t="b">
         <v>1</v>
@@ -2774,12 +2774,12 @@
         <v>2</v>
       </c>
       <c r="I70">
-        <v>0.5</v>
+        <v>0.5000000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B71" t="b">
         <v>1</v>
@@ -2803,12 +2803,12 @@
         <v>2</v>
       </c>
       <c r="I71">
-        <v>0.4989583333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B72" t="b">
         <v>1</v>
@@ -2832,12 +2832,12 @@
         <v>2</v>
       </c>
       <c r="I72">
-        <v>0.496875</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B73" t="b">
         <v>1</v>
@@ -2861,12 +2861,12 @@
         <v>2</v>
       </c>
       <c r="I73">
-        <v>0.4958333333333334</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B74" t="b">
         <v>1</v>
@@ -2890,12 +2890,12 @@
         <v>2</v>
       </c>
       <c r="I74">
-        <v>0.4958333333333334</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B75" t="b">
         <v>1</v>
@@ -2919,12 +2919,12 @@
         <v>2</v>
       </c>
       <c r="I75">
-        <v>0.4958333333333334</v>
+        <v>0.4989583333333333</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B76" t="b">
         <v>1</v>
@@ -2948,12 +2948,12 @@
         <v>2</v>
       </c>
       <c r="I76">
-        <v>0.4958333333333333</v>
+        <v>0.496875</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B77" t="b">
         <v>1</v>
@@ -2977,12 +2977,12 @@
         <v>2</v>
       </c>
       <c r="I77">
-        <v>0.4947916666666667</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B78" t="b">
         <v>1</v>
@@ -3006,12 +3006,12 @@
         <v>2</v>
       </c>
       <c r="I78">
-        <v>0.4947916666666667</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B79" t="b">
         <v>1</v>
@@ -3035,12 +3035,12 @@
         <v>2</v>
       </c>
       <c r="I79">
-        <v>0.4947916666666667</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B80" t="b">
         <v>1</v>
@@ -3064,12 +3064,12 @@
         <v>2</v>
       </c>
       <c r="I80">
-        <v>0.4947916666666667</v>
+        <v>0.4958333333333333</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B81" t="b">
         <v>1</v>
@@ -3093,12 +3093,12 @@
         <v>2</v>
       </c>
       <c r="I81">
-        <v>0.4927083333333334</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B82" t="b">
         <v>1</v>
@@ -3122,12 +3122,12 @@
         <v>2</v>
       </c>
       <c r="I82">
-        <v>0.4927083333333333</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B83" t="b">
         <v>1</v>
@@ -3151,12 +3151,12 @@
         <v>2</v>
       </c>
       <c r="I83">
-        <v>0.4927083333333333</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B84" t="b">
         <v>1</v>
@@ -3180,12 +3180,12 @@
         <v>2</v>
       </c>
       <c r="I84">
-        <v>0.4927083333333333</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B85" t="b">
         <v>1</v>
@@ -3209,12 +3209,12 @@
         <v>2</v>
       </c>
       <c r="I85">
-        <v>0.4916666666666667</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B86" t="b">
         <v>1</v>
@@ -3238,12 +3238,12 @@
         <v>2</v>
       </c>
       <c r="I86">
-        <v>0.4916666666666666</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B87" t="b">
         <v>1</v>
@@ -3267,15 +3267,15 @@
         <v>2</v>
       </c>
       <c r="I87">
-        <v>0.4895833333333333</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C88" t="b">
         <v>1</v>
@@ -3290,18 +3290,18 @@
         <v>0</v>
       </c>
       <c r="G88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88">
         <v>2</v>
       </c>
       <c r="I88">
-        <v>0.4885416666666666</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B89" t="b">
         <v>1</v>
@@ -3325,12 +3325,12 @@
         <v>2</v>
       </c>
       <c r="I89">
-        <v>0.4885416666666666</v>
+        <v>0.4916666666666667</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B90" t="b">
         <v>1</v>
@@ -3354,12 +3354,12 @@
         <v>2</v>
       </c>
       <c r="I90">
-        <v>0.4864583333333333</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B91" t="b">
         <v>1</v>
@@ -3383,15 +3383,15 @@
         <v>2</v>
       </c>
       <c r="I91">
-        <v>0.4854166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" t="b">
         <v>1</v>
@@ -3406,18 +3406,18 @@
         <v>0</v>
       </c>
       <c r="G92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92">
         <v>2</v>
       </c>
       <c r="I92">
-        <v>0.484375</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B93" t="b">
         <v>1</v>
@@ -3441,12 +3441,12 @@
         <v>2</v>
       </c>
       <c r="I93">
-        <v>0.484375</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B94" t="b">
         <v>1</v>
@@ -3470,12 +3470,12 @@
         <v>2</v>
       </c>
       <c r="I94">
-        <v>0.4833333333333334</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B95" t="b">
         <v>1</v>
@@ -3499,12 +3499,12 @@
         <v>2</v>
       </c>
       <c r="I95">
-        <v>0.4833333333333333</v>
+        <v>0.4854166666666666</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B96" t="b">
         <v>1</v>
@@ -3528,12 +3528,12 @@
         <v>2</v>
       </c>
       <c r="I96">
-        <v>0.4833333333333333</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B97" t="b">
         <v>1</v>
@@ -3557,12 +3557,12 @@
         <v>2</v>
       </c>
       <c r="I97">
-        <v>0.4802083333333334</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B98" t="b">
         <v>1</v>
@@ -3586,12 +3586,12 @@
         <v>2</v>
       </c>
       <c r="I98">
-        <v>0.4791666666666667</v>
+        <v>0.4833333333333334</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B99" t="b">
         <v>1</v>
@@ -3615,12 +3615,12 @@
         <v>2</v>
       </c>
       <c r="I99">
-        <v>0.4770833333333333</v>
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B100" t="b">
         <v>1</v>
@@ -3644,12 +3644,12 @@
         <v>2</v>
       </c>
       <c r="I100">
-        <v>0.4739583333333333</v>
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B101" t="b">
         <v>1</v>
@@ -3673,18 +3673,18 @@
         <v>2</v>
       </c>
       <c r="I101">
-        <v>0.4739583333333333</v>
+        <v>0.4802083333333334</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B102" t="b">
         <v>1</v>
       </c>
       <c r="C102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D102" t="b">
         <v>0</v>
@@ -3699,18 +3699,18 @@
         <v>0</v>
       </c>
       <c r="H102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I102">
-        <v>0.5354166666666667</v>
+        <v>0.4791666666666667</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C103" t="b">
         <v>1</v>
@@ -3728,18 +3728,18 @@
         <v>0</v>
       </c>
       <c r="H103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I103">
-        <v>0.53125</v>
+        <v>0.4770833333333333</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C104" t="b">
         <v>1</v>
@@ -3757,18 +3757,18 @@
         <v>0</v>
       </c>
       <c r="H104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I104">
-        <v>0.5125</v>
+        <v>0.4739583333333333</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C105" t="b">
         <v>1</v>
@@ -3786,21 +3786,21 @@
         <v>0</v>
       </c>
       <c r="H105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I105">
-        <v>0.5104166666666666</v>
+        <v>0.4739583333333333</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106" t="b">
         <v>0</v>
@@ -3818,12 +3818,12 @@
         <v>1</v>
       </c>
       <c r="I106">
-        <v>0.5104166666666666</v>
+        <v>0.5354166666666667</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B107" t="b">
         <v>0</v>
@@ -3847,12 +3847,12 @@
         <v>1</v>
       </c>
       <c r="I107">
-        <v>0.5104166666666666</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B108" t="b">
         <v>0</v>
@@ -3876,12 +3876,12 @@
         <v>1</v>
       </c>
       <c r="I108">
-        <v>0.5104166666666666</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B109" t="b">
         <v>0</v>
@@ -3905,12 +3905,12 @@
         <v>1</v>
       </c>
       <c r="I109">
-        <v>0.5052083333333334</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B110" t="b">
         <v>0</v>
@@ -3934,18 +3934,18 @@
         <v>1</v>
       </c>
       <c r="I110">
-        <v>0.5052083333333334</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D111" t="b">
         <v>0</v>
@@ -3963,18 +3963,18 @@
         <v>1</v>
       </c>
       <c r="I111">
-        <v>0.5041666666666667</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112" t="b">
         <v>0</v>
@@ -3992,18 +3992,18 @@
         <v>1</v>
       </c>
       <c r="I112">
-        <v>0.5041666666666667</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D113" t="b">
         <v>0</v>
@@ -4021,18 +4021,18 @@
         <v>1</v>
       </c>
       <c r="I113">
-        <v>0.4947916666666667</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D114" t="b">
         <v>0</v>
@@ -4050,18 +4050,18 @@
         <v>1</v>
       </c>
       <c r="I114">
-        <v>0.4927083333333333</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D115" t="b">
         <v>0</v>
@@ -4079,12 +4079,12 @@
         <v>1</v>
       </c>
       <c r="I115">
-        <v>0.4895833333333333</v>
+        <v>0.5041666666666667</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B116" t="b">
         <v>1</v>
@@ -4108,18 +4108,18 @@
         <v>1</v>
       </c>
       <c r="I116">
-        <v>0.4875</v>
+        <v>0.5041666666666667</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117" t="b">
         <v>0</v>
@@ -4137,18 +4137,18 @@
         <v>1</v>
       </c>
       <c r="I117">
-        <v>0.4864583333333333</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118" t="b">
         <v>0</v>
@@ -4166,12 +4166,12 @@
         <v>1</v>
       </c>
       <c r="I118">
-        <v>0.4864583333333333</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B119" t="b">
         <v>0</v>
@@ -4195,12 +4195,12 @@
         <v>1</v>
       </c>
       <c r="I119">
-        <v>0.4864583333333333</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B120" t="b">
         <v>1</v>
@@ -4224,18 +4224,18 @@
         <v>1</v>
       </c>
       <c r="I120">
-        <v>0.4854166666666666</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D121" t="b">
         <v>0</v>
@@ -4253,18 +4253,18 @@
         <v>1</v>
       </c>
       <c r="I121">
-        <v>0.4760416666666667</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D122" t="b">
         <v>0</v>
@@ -4282,18 +4282,18 @@
         <v>1</v>
       </c>
       <c r="I122">
-        <v>0.4614583333333333</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123" t="b">
         <v>0</v>
@@ -4311,12 +4311,12 @@
         <v>1</v>
       </c>
       <c r="I123">
-        <v>0.45</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B124" t="b">
         <v>1</v>
@@ -4340,35 +4340,151 @@
         <v>1</v>
       </c>
       <c r="I124">
-        <v>0.4260416666666667</v>
+        <v>0.4854166666666666</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" t="s">
+        <v>128</v>
+      </c>
+      <c r="B125" t="b">
+        <v>1</v>
+      </c>
+      <c r="C125" t="b">
+        <v>0</v>
+      </c>
+      <c r="D125" t="b">
+        <v>0</v>
+      </c>
+      <c r="E125" t="b">
+        <v>0</v>
+      </c>
+      <c r="F125" t="b">
+        <v>0</v>
+      </c>
+      <c r="G125" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>1</v>
+      </c>
+      <c r="I125">
+        <v>0.4760416666666667</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" t="s">
+        <v>129</v>
+      </c>
+      <c r="B126" t="b">
+        <v>1</v>
+      </c>
+      <c r="C126" t="b">
+        <v>0</v>
+      </c>
+      <c r="D126" t="b">
+        <v>0</v>
+      </c>
+      <c r="E126" t="b">
+        <v>0</v>
+      </c>
+      <c r="F126" t="b">
+        <v>0</v>
+      </c>
+      <c r="G126" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>1</v>
+      </c>
+      <c r="I126">
+        <v>0.4614583333333333</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" t="s">
+        <v>130</v>
+      </c>
+      <c r="B127" t="b">
+        <v>1</v>
+      </c>
+      <c r="C127" t="b">
+        <v>0</v>
+      </c>
+      <c r="D127" t="b">
+        <v>0</v>
+      </c>
+      <c r="E127" t="b">
+        <v>0</v>
+      </c>
+      <c r="F127" t="b">
+        <v>0</v>
+      </c>
+      <c r="G127" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>1</v>
+      </c>
+      <c r="I127">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" t="s">
+        <v>131</v>
+      </c>
+      <c r="B128" t="b">
+        <v>1</v>
+      </c>
+      <c r="C128" t="b">
+        <v>0</v>
+      </c>
+      <c r="D128" t="b">
+        <v>0</v>
+      </c>
+      <c r="E128" t="b">
+        <v>0</v>
+      </c>
+      <c r="F128" t="b">
+        <v>0</v>
+      </c>
+      <c r="G128" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>1</v>
+      </c>
+      <c r="I128">
+        <v>0.4260416666666667</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" t="s">
         <v>132</v>
       </c>
-      <c r="B125" t="b">
-        <v>0</v>
-      </c>
-      <c r="C125" t="b">
-        <v>0</v>
-      </c>
-      <c r="D125" t="b">
-        <v>0</v>
-      </c>
-      <c r="E125" t="b">
-        <v>0</v>
-      </c>
-      <c r="F125" t="b">
-        <v>0</v>
-      </c>
-      <c r="G125" t="b">
-        <v>0</v>
-      </c>
-      <c r="H125">
-        <v>0</v>
-      </c>
-      <c r="I125">
+      <c r="B129" t="b">
+        <v>0</v>
+      </c>
+      <c r="C129" t="b">
+        <v>0</v>
+      </c>
+      <c r="D129" t="b">
+        <v>0</v>
+      </c>
+      <c r="E129" t="b">
+        <v>0</v>
+      </c>
+      <c r="F129" t="b">
+        <v>0</v>
+      </c>
+      <c r="G129" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+      <c r="I129">
         <v>0.478125</v>
       </c>
     </row>

--- a/F_grouping/reference/backtesting_score.xlsx
+++ b/F_grouping/reference/backtesting_score.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="133">
   <si>
     <t>factor_name</t>
   </si>
@@ -744,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:I140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1706,7 +1706,7 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B34" t="b">
         <v>1</v>
@@ -1730,12 +1730,12 @@
         <v>3</v>
       </c>
       <c r="I34">
-        <v>0.5</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="B35" t="b">
         <v>1</v>
@@ -1759,12 +1759,12 @@
         <v>3</v>
       </c>
       <c r="I35">
-        <v>0.4989583333333334</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B36" t="b">
         <v>1</v>
@@ -1776,24 +1776,24 @@
         <v>0</v>
       </c>
       <c r="E36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
       </c>
       <c r="G36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>3</v>
       </c>
       <c r="I36">
-        <v>0.4989583333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="B37" t="b">
         <v>1</v>
@@ -1817,12 +1817,12 @@
         <v>3</v>
       </c>
       <c r="I37">
-        <v>0.4979166666666666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="B38" t="b">
         <v>1</v>
@@ -1846,12 +1846,12 @@
         <v>3</v>
       </c>
       <c r="I38">
-        <v>0.4958333333333334</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="b">
         <v>1</v>
@@ -1875,12 +1875,12 @@
         <v>3</v>
       </c>
       <c r="I39">
-        <v>0.4958333333333334</v>
+        <v>0.4989583333333334</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B40" t="b">
         <v>1</v>
@@ -1904,12 +1904,12 @@
         <v>3</v>
       </c>
       <c r="I40">
-        <v>0.4947916666666666</v>
+        <v>0.4989583333333333</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="B41" t="b">
         <v>1</v>
@@ -1933,12 +1933,12 @@
         <v>3</v>
       </c>
       <c r="I41">
-        <v>0.4927083333333334</v>
+        <v>0.4979166666666666</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B42" t="b">
         <v>1</v>
@@ -1962,12 +1962,12 @@
         <v>3</v>
       </c>
       <c r="I42">
-        <v>0.4927083333333334</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B43" t="b">
         <v>1</v>
@@ -1991,12 +1991,12 @@
         <v>3</v>
       </c>
       <c r="I43">
-        <v>0.4916666666666666</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B44" t="b">
         <v>1</v>
@@ -2020,12 +2020,12 @@
         <v>3</v>
       </c>
       <c r="I44">
-        <v>0.490625</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B45" t="b">
         <v>1</v>
@@ -2037,24 +2037,24 @@
         <v>0</v>
       </c>
       <c r="E45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
       </c>
       <c r="G45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45">
         <v>3</v>
       </c>
       <c r="I45">
-        <v>0.4885416666666667</v>
+        <v>0.4947916666666666</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B46" t="b">
         <v>1</v>
@@ -2078,12 +2078,12 @@
         <v>3</v>
       </c>
       <c r="I46">
-        <v>0.4875</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="B47" t="b">
         <v>1</v>
@@ -2107,12 +2107,12 @@
         <v>3</v>
       </c>
       <c r="I47">
-        <v>0.484375</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="B48" t="b">
         <v>1</v>
@@ -2136,12 +2136,12 @@
         <v>3</v>
       </c>
       <c r="I48">
-        <v>0.4802083333333333</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="B49" t="b">
         <v>1</v>
@@ -2165,12 +2165,12 @@
         <v>3</v>
       </c>
       <c r="I49">
-        <v>0.4770833333333333</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B50" t="b">
         <v>1</v>
@@ -2188,18 +2188,18 @@
         <v>0</v>
       </c>
       <c r="G50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I50">
-        <v>0.5291666666666666</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B51" t="b">
         <v>1</v>
@@ -2217,18 +2217,18 @@
         <v>0</v>
       </c>
       <c r="G51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51">
-        <v>0.5270833333333332</v>
+        <v>0.490625</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B52" t="b">
         <v>1</v>
@@ -2246,18 +2246,18 @@
         <v>0</v>
       </c>
       <c r="G52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I52">
-        <v>0.5260416666666667</v>
+        <v>0.4885416666666667</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B53" t="b">
         <v>1</v>
@@ -2275,18 +2275,18 @@
         <v>0</v>
       </c>
       <c r="G53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I53">
-        <v>0.5260416666666667</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B54" t="b">
         <v>1</v>
@@ -2304,18 +2304,18 @@
         <v>0</v>
       </c>
       <c r="G54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I54">
-        <v>0.5239583333333334</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B55" t="b">
         <v>1</v>
@@ -2333,18 +2333,18 @@
         <v>0</v>
       </c>
       <c r="G55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I55">
-        <v>0.5177083333333334</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B56" t="b">
         <v>1</v>
@@ -2362,18 +2362,18 @@
         <v>0</v>
       </c>
       <c r="G56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I56">
-        <v>0.5166666666666667</v>
+        <v>0.4802083333333333</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B57" t="b">
         <v>1</v>
@@ -2391,18 +2391,18 @@
         <v>0</v>
       </c>
       <c r="G57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I57">
-        <v>0.515625</v>
+        <v>0.4770833333333333</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="B58" t="b">
         <v>1</v>
@@ -2420,18 +2420,18 @@
         <v>0</v>
       </c>
       <c r="G58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I58">
-        <v>0.5135416666666666</v>
+        <v>0.465625</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="B59" t="b">
         <v>1</v>
@@ -2449,18 +2449,18 @@
         <v>0</v>
       </c>
       <c r="G59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I59">
-        <v>0.5135416666666666</v>
+        <v>0.4645833333333334</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B60" t="b">
         <v>1</v>
@@ -2484,12 +2484,12 @@
         <v>2</v>
       </c>
       <c r="I60">
-        <v>0.5104166666666667</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B61" t="b">
         <v>1</v>
@@ -2513,12 +2513,12 @@
         <v>2</v>
       </c>
       <c r="I61">
-        <v>0.5083333333333333</v>
+        <v>0.5270833333333332</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B62" t="b">
         <v>1</v>
@@ -2542,12 +2542,12 @@
         <v>2</v>
       </c>
       <c r="I62">
-        <v>0.5083333333333333</v>
+        <v>0.5260416666666667</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B63" t="b">
         <v>1</v>
@@ -2571,12 +2571,12 @@
         <v>2</v>
       </c>
       <c r="I63">
-        <v>0.5062500000000001</v>
+        <v>0.5260416666666667</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B64" t="b">
         <v>1</v>
@@ -2600,12 +2600,12 @@
         <v>2</v>
       </c>
       <c r="I64">
-        <v>0.50625</v>
+        <v>0.5239583333333334</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B65" t="b">
         <v>1</v>
@@ -2629,12 +2629,12 @@
         <v>2</v>
       </c>
       <c r="I65">
-        <v>0.503125</v>
+        <v>0.5177083333333334</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B66" t="b">
         <v>1</v>
@@ -2658,12 +2658,12 @@
         <v>2</v>
       </c>
       <c r="I66">
-        <v>0.503125</v>
+        <v>0.5166666666666667</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B67" t="b">
         <v>1</v>
@@ -2687,12 +2687,12 @@
         <v>2</v>
       </c>
       <c r="I67">
-        <v>0.503125</v>
+        <v>0.515625</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B68" t="b">
         <v>1</v>
@@ -2716,12 +2716,12 @@
         <v>2</v>
       </c>
       <c r="I68">
-        <v>0.5020833333333333</v>
+        <v>0.5135416666666666</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B69" t="b">
         <v>1</v>
@@ -2745,12 +2745,12 @@
         <v>2</v>
       </c>
       <c r="I69">
-        <v>0.5010416666666667</v>
+        <v>0.5135416666666666</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="B70" t="b">
         <v>1</v>
@@ -2774,12 +2774,12 @@
         <v>2</v>
       </c>
       <c r="I70">
-        <v>0.5000000000000001</v>
+        <v>0.5104166666666667</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B71" t="b">
         <v>1</v>
@@ -2803,12 +2803,12 @@
         <v>2</v>
       </c>
       <c r="I71">
-        <v>0.5</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B72" t="b">
         <v>1</v>
@@ -2832,12 +2832,12 @@
         <v>2</v>
       </c>
       <c r="I72">
-        <v>0.5</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B73" t="b">
         <v>1</v>
@@ -2861,12 +2861,12 @@
         <v>2</v>
       </c>
       <c r="I73">
-        <v>0.5</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B74" t="b">
         <v>1</v>
@@ -2890,12 +2890,12 @@
         <v>2</v>
       </c>
       <c r="I74">
-        <v>0.5</v>
+        <v>0.50625</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B75" t="b">
         <v>1</v>
@@ -2919,12 +2919,12 @@
         <v>2</v>
       </c>
       <c r="I75">
-        <v>0.4989583333333333</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B76" t="b">
         <v>1</v>
@@ -2948,12 +2948,12 @@
         <v>2</v>
       </c>
       <c r="I76">
-        <v>0.496875</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B77" t="b">
         <v>1</v>
@@ -2977,12 +2977,12 @@
         <v>2</v>
       </c>
       <c r="I77">
-        <v>0.4958333333333334</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B78" t="b">
         <v>1</v>
@@ -3006,12 +3006,12 @@
         <v>2</v>
       </c>
       <c r="I78">
-        <v>0.4958333333333334</v>
+        <v>0.5020833333333333</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B79" t="b">
         <v>1</v>
@@ -3035,12 +3035,12 @@
         <v>2</v>
       </c>
       <c r="I79">
-        <v>0.4958333333333334</v>
+        <v>0.5010416666666667</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="B80" t="b">
         <v>1</v>
@@ -3064,12 +3064,12 @@
         <v>2</v>
       </c>
       <c r="I80">
-        <v>0.4958333333333333</v>
+        <v>0.5000000000000001</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="B81" t="b">
         <v>1</v>
@@ -3093,12 +3093,12 @@
         <v>2</v>
       </c>
       <c r="I81">
-        <v>0.4947916666666667</v>
+        <v>0.5000000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="B82" t="b">
         <v>1</v>
@@ -3122,12 +3122,12 @@
         <v>2</v>
       </c>
       <c r="I82">
-        <v>0.4947916666666667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B83" t="b">
         <v>1</v>
@@ -3151,12 +3151,12 @@
         <v>2</v>
       </c>
       <c r="I83">
-        <v>0.4947916666666667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B84" t="b">
         <v>1</v>
@@ -3180,12 +3180,12 @@
         <v>2</v>
       </c>
       <c r="I84">
-        <v>0.4947916666666667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B85" t="b">
         <v>1</v>
@@ -3209,12 +3209,12 @@
         <v>2</v>
       </c>
       <c r="I85">
-        <v>0.4927083333333334</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B86" t="b">
         <v>1</v>
@@ -3238,12 +3238,12 @@
         <v>2</v>
       </c>
       <c r="I86">
-        <v>0.4927083333333333</v>
+        <v>0.4989583333333333</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B87" t="b">
         <v>1</v>
@@ -3267,12 +3267,12 @@
         <v>2</v>
       </c>
       <c r="I87">
-        <v>0.4927083333333333</v>
+        <v>0.496875</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B88" t="b">
         <v>1</v>
@@ -3296,12 +3296,12 @@
         <v>2</v>
       </c>
       <c r="I88">
-        <v>0.4927083333333333</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B89" t="b">
         <v>1</v>
@@ -3325,12 +3325,12 @@
         <v>2</v>
       </c>
       <c r="I89">
-        <v>0.4916666666666667</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B90" t="b">
         <v>1</v>
@@ -3354,12 +3354,12 @@
         <v>2</v>
       </c>
       <c r="I90">
-        <v>0.4916666666666666</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B91" t="b">
         <v>1</v>
@@ -3383,15 +3383,15 @@
         <v>2</v>
       </c>
       <c r="I91">
-        <v>0.4895833333333333</v>
+        <v>0.4958333333333333</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C92" t="b">
         <v>1</v>
@@ -3406,18 +3406,18 @@
         <v>0</v>
       </c>
       <c r="G92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92">
         <v>2</v>
       </c>
       <c r="I92">
-        <v>0.4885416666666666</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B93" t="b">
         <v>1</v>
@@ -3441,12 +3441,12 @@
         <v>2</v>
       </c>
       <c r="I93">
-        <v>0.4885416666666666</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B94" t="b">
         <v>1</v>
@@ -3470,12 +3470,12 @@
         <v>2</v>
       </c>
       <c r="I94">
-        <v>0.4864583333333333</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B95" t="b">
         <v>1</v>
@@ -3499,12 +3499,12 @@
         <v>2</v>
       </c>
       <c r="I95">
-        <v>0.4854166666666666</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B96" t="b">
         <v>1</v>
@@ -3528,12 +3528,12 @@
         <v>2</v>
       </c>
       <c r="I96">
-        <v>0.484375</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B97" t="b">
         <v>1</v>
@@ -3557,12 +3557,12 @@
         <v>2</v>
       </c>
       <c r="I97">
-        <v>0.484375</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B98" t="b">
         <v>1</v>
@@ -3586,12 +3586,12 @@
         <v>2</v>
       </c>
       <c r="I98">
-        <v>0.4833333333333334</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B99" t="b">
         <v>1</v>
@@ -3615,12 +3615,12 @@
         <v>2</v>
       </c>
       <c r="I99">
-        <v>0.4833333333333333</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B100" t="b">
         <v>1</v>
@@ -3644,12 +3644,12 @@
         <v>2</v>
       </c>
       <c r="I100">
-        <v>0.4833333333333333</v>
+        <v>0.4916666666666667</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B101" t="b">
         <v>1</v>
@@ -3673,12 +3673,12 @@
         <v>2</v>
       </c>
       <c r="I101">
-        <v>0.4802083333333334</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B102" t="b">
         <v>1</v>
@@ -3702,15 +3702,15 @@
         <v>2</v>
       </c>
       <c r="I102">
-        <v>0.4791666666666667</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C103" t="b">
         <v>1</v>
@@ -3725,18 +3725,18 @@
         <v>0</v>
       </c>
       <c r="G103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103">
         <v>2</v>
       </c>
       <c r="I103">
-        <v>0.4770833333333333</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B104" t="b">
         <v>1</v>
@@ -3760,12 +3760,12 @@
         <v>2</v>
       </c>
       <c r="I104">
-        <v>0.4739583333333333</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B105" t="b">
         <v>1</v>
@@ -3789,18 +3789,18 @@
         <v>2</v>
       </c>
       <c r="I105">
-        <v>0.4739583333333333</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B106" t="b">
         <v>1</v>
       </c>
       <c r="C106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106" t="b">
         <v>0</v>
@@ -3815,18 +3815,18 @@
         <v>0</v>
       </c>
       <c r="H106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I106">
-        <v>0.5354166666666667</v>
+        <v>0.4854166666666666</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C107" t="b">
         <v>1</v>
@@ -3844,18 +3844,18 @@
         <v>0</v>
       </c>
       <c r="H107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I107">
-        <v>0.53125</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C108" t="b">
         <v>1</v>
@@ -3873,18 +3873,18 @@
         <v>0</v>
       </c>
       <c r="H108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I108">
-        <v>0.5125</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C109" t="b">
         <v>1</v>
@@ -3902,18 +3902,18 @@
         <v>0</v>
       </c>
       <c r="H109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I109">
-        <v>0.5104166666666666</v>
+        <v>0.4833333333333334</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C110" t="b">
         <v>1</v>
@@ -3931,18 +3931,18 @@
         <v>0</v>
       </c>
       <c r="H110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I110">
-        <v>0.5104166666666666</v>
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C111" t="b">
         <v>1</v>
@@ -3960,18 +3960,18 @@
         <v>0</v>
       </c>
       <c r="H111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I111">
-        <v>0.5104166666666666</v>
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C112" t="b">
         <v>1</v>
@@ -3989,18 +3989,18 @@
         <v>0</v>
       </c>
       <c r="H112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I112">
-        <v>0.5104166666666666</v>
+        <v>0.4802083333333334</v>
       </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C113" t="b">
         <v>1</v>
@@ -4018,18 +4018,18 @@
         <v>0</v>
       </c>
       <c r="H113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I113">
-        <v>0.5052083333333334</v>
+        <v>0.4791666666666667</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C114" t="b">
         <v>1</v>
@@ -4047,21 +4047,21 @@
         <v>0</v>
       </c>
       <c r="H114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I114">
-        <v>0.5052083333333334</v>
+        <v>0.4770833333333333</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B115" t="b">
         <v>1</v>
       </c>
       <c r="C115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D115" t="b">
         <v>0</v>
@@ -4076,21 +4076,21 @@
         <v>0</v>
       </c>
       <c r="H115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I115">
-        <v>0.5041666666666667</v>
+        <v>0.4739583333333333</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="B116" t="b">
         <v>1</v>
       </c>
       <c r="C116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D116" t="b">
         <v>0</v>
@@ -4105,15 +4105,15 @@
         <v>0</v>
       </c>
       <c r="H116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I116">
-        <v>0.5041666666666667</v>
+        <v>0.4739583333333333</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B117" t="b">
         <v>1</v>
@@ -4137,18 +4137,18 @@
         <v>1</v>
       </c>
       <c r="I117">
-        <v>0.4947916666666667</v>
+        <v>0.5354166666666667</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="B118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118" t="b">
         <v>0</v>
@@ -4166,12 +4166,12 @@
         <v>1</v>
       </c>
       <c r="I118">
-        <v>0.4927083333333333</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="B119" t="b">
         <v>0</v>
@@ -4195,18 +4195,18 @@
         <v>1</v>
       </c>
       <c r="I119">
-        <v>0.4895833333333333</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="B120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120" t="b">
         <v>0</v>
@@ -4224,12 +4224,12 @@
         <v>1</v>
       </c>
       <c r="I120">
-        <v>0.4875</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B121" t="b">
         <v>0</v>
@@ -4253,12 +4253,12 @@
         <v>1</v>
       </c>
       <c r="I121">
-        <v>0.4864583333333333</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B122" t="b">
         <v>0</v>
@@ -4282,12 +4282,12 @@
         <v>1</v>
       </c>
       <c r="I122">
-        <v>0.4864583333333333</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B123" t="b">
         <v>0</v>
@@ -4311,18 +4311,18 @@
         <v>1</v>
       </c>
       <c r="I123">
-        <v>0.4864583333333333</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D124" t="b">
         <v>0</v>
@@ -4340,18 +4340,18 @@
         <v>1</v>
       </c>
       <c r="I124">
-        <v>0.4854166666666666</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D125" t="b">
         <v>0</v>
@@ -4369,12 +4369,12 @@
         <v>1</v>
       </c>
       <c r="I125">
-        <v>0.4760416666666667</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B126" t="b">
         <v>1</v>
@@ -4398,12 +4398,12 @@
         <v>1</v>
       </c>
       <c r="I126">
-        <v>0.4614583333333333</v>
+        <v>0.5041666666666667</v>
       </c>
     </row>
     <row r="127" spans="1:9">
       <c r="A127" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="B127" t="b">
         <v>1</v>
@@ -4427,12 +4427,12 @@
         <v>1</v>
       </c>
       <c r="I127">
-        <v>0.45</v>
+        <v>0.5041666666666667</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="B128" t="b">
         <v>1</v>
@@ -4456,35 +4456,354 @@
         <v>1</v>
       </c>
       <c r="I128">
-        <v>0.4260416666666667</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="129" spans="1:9">
       <c r="A129" t="s">
+        <v>121</v>
+      </c>
+      <c r="B129" t="b">
+        <v>1</v>
+      </c>
+      <c r="C129" t="b">
+        <v>0</v>
+      </c>
+      <c r="D129" t="b">
+        <v>0</v>
+      </c>
+      <c r="E129" t="b">
+        <v>0</v>
+      </c>
+      <c r="F129" t="b">
+        <v>0</v>
+      </c>
+      <c r="G129" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>1</v>
+      </c>
+      <c r="I129">
+        <v>0.4927083333333333</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" t="s">
+        <v>122</v>
+      </c>
+      <c r="B130" t="b">
+        <v>0</v>
+      </c>
+      <c r="C130" t="b">
+        <v>1</v>
+      </c>
+      <c r="D130" t="b">
+        <v>0</v>
+      </c>
+      <c r="E130" t="b">
+        <v>0</v>
+      </c>
+      <c r="F130" t="b">
+        <v>0</v>
+      </c>
+      <c r="G130" t="b">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>1</v>
+      </c>
+      <c r="I130">
+        <v>0.4895833333333333</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" t="s">
+        <v>123</v>
+      </c>
+      <c r="B131" t="b">
+        <v>1</v>
+      </c>
+      <c r="C131" t="b">
+        <v>0</v>
+      </c>
+      <c r="D131" t="b">
+        <v>0</v>
+      </c>
+      <c r="E131" t="b">
+        <v>0</v>
+      </c>
+      <c r="F131" t="b">
+        <v>0</v>
+      </c>
+      <c r="G131" t="b">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>1</v>
+      </c>
+      <c r="I131">
+        <v>0.4875</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" t="s">
+        <v>124</v>
+      </c>
+      <c r="B132" t="b">
+        <v>0</v>
+      </c>
+      <c r="C132" t="b">
+        <v>1</v>
+      </c>
+      <c r="D132" t="b">
+        <v>0</v>
+      </c>
+      <c r="E132" t="b">
+        <v>0</v>
+      </c>
+      <c r="F132" t="b">
+        <v>0</v>
+      </c>
+      <c r="G132" t="b">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>1</v>
+      </c>
+      <c r="I132">
+        <v>0.4864583333333333</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" t="s">
+        <v>125</v>
+      </c>
+      <c r="B133" t="b">
+        <v>0</v>
+      </c>
+      <c r="C133" t="b">
+        <v>1</v>
+      </c>
+      <c r="D133" t="b">
+        <v>0</v>
+      </c>
+      <c r="E133" t="b">
+        <v>0</v>
+      </c>
+      <c r="F133" t="b">
+        <v>0</v>
+      </c>
+      <c r="G133" t="b">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>1</v>
+      </c>
+      <c r="I133">
+        <v>0.4864583333333333</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" t="s">
+        <v>126</v>
+      </c>
+      <c r="B134" t="b">
+        <v>0</v>
+      </c>
+      <c r="C134" t="b">
+        <v>1</v>
+      </c>
+      <c r="D134" t="b">
+        <v>0</v>
+      </c>
+      <c r="E134" t="b">
+        <v>0</v>
+      </c>
+      <c r="F134" t="b">
+        <v>0</v>
+      </c>
+      <c r="G134" t="b">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>1</v>
+      </c>
+      <c r="I134">
+        <v>0.4864583333333333</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" t="s">
+        <v>127</v>
+      </c>
+      <c r="B135" t="b">
+        <v>1</v>
+      </c>
+      <c r="C135" t="b">
+        <v>0</v>
+      </c>
+      <c r="D135" t="b">
+        <v>0</v>
+      </c>
+      <c r="E135" t="b">
+        <v>0</v>
+      </c>
+      <c r="F135" t="b">
+        <v>0</v>
+      </c>
+      <c r="G135" t="b">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>1</v>
+      </c>
+      <c r="I135">
+        <v>0.4854166666666666</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136" t="s">
+        <v>128</v>
+      </c>
+      <c r="B136" t="b">
+        <v>1</v>
+      </c>
+      <c r="C136" t="b">
+        <v>0</v>
+      </c>
+      <c r="D136" t="b">
+        <v>0</v>
+      </c>
+      <c r="E136" t="b">
+        <v>0</v>
+      </c>
+      <c r="F136" t="b">
+        <v>0</v>
+      </c>
+      <c r="G136" t="b">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>1</v>
+      </c>
+      <c r="I136">
+        <v>0.4760416666666667</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="A137" t="s">
+        <v>129</v>
+      </c>
+      <c r="B137" t="b">
+        <v>1</v>
+      </c>
+      <c r="C137" t="b">
+        <v>0</v>
+      </c>
+      <c r="D137" t="b">
+        <v>0</v>
+      </c>
+      <c r="E137" t="b">
+        <v>0</v>
+      </c>
+      <c r="F137" t="b">
+        <v>0</v>
+      </c>
+      <c r="G137" t="b">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>1</v>
+      </c>
+      <c r="I137">
+        <v>0.4614583333333333</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" t="s">
+        <v>130</v>
+      </c>
+      <c r="B138" t="b">
+        <v>1</v>
+      </c>
+      <c r="C138" t="b">
+        <v>0</v>
+      </c>
+      <c r="D138" t="b">
+        <v>0</v>
+      </c>
+      <c r="E138" t="b">
+        <v>0</v>
+      </c>
+      <c r="F138" t="b">
+        <v>0</v>
+      </c>
+      <c r="G138" t="b">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>1</v>
+      </c>
+      <c r="I138">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" t="s">
+        <v>131</v>
+      </c>
+      <c r="B139" t="b">
+        <v>1</v>
+      </c>
+      <c r="C139" t="b">
+        <v>0</v>
+      </c>
+      <c r="D139" t="b">
+        <v>0</v>
+      </c>
+      <c r="E139" t="b">
+        <v>0</v>
+      </c>
+      <c r="F139" t="b">
+        <v>0</v>
+      </c>
+      <c r="G139" t="b">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>1</v>
+      </c>
+      <c r="I139">
+        <v>0.4260416666666667</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="A140" t="s">
         <v>132</v>
       </c>
-      <c r="B129" t="b">
-        <v>0</v>
-      </c>
-      <c r="C129" t="b">
-        <v>0</v>
-      </c>
-      <c r="D129" t="b">
-        <v>0</v>
-      </c>
-      <c r="E129" t="b">
-        <v>0</v>
-      </c>
-      <c r="F129" t="b">
-        <v>0</v>
-      </c>
-      <c r="G129" t="b">
-        <v>0</v>
-      </c>
-      <c r="H129">
-        <v>0</v>
-      </c>
-      <c r="I129">
+      <c r="B140" t="b">
+        <v>0</v>
+      </c>
+      <c r="C140" t="b">
+        <v>0</v>
+      </c>
+      <c r="D140" t="b">
+        <v>0</v>
+      </c>
+      <c r="E140" t="b">
+        <v>0</v>
+      </c>
+      <c r="F140" t="b">
+        <v>0</v>
+      </c>
+      <c r="G140" t="b">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
         <v>0.478125</v>
       </c>
     </row>

--- a/F_grouping/reference/backtesting_score.xlsx
+++ b/F_grouping/reference/backtesting_score.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="137">
   <si>
     <t>factor_name</t>
   </si>
@@ -52,13 +52,19 @@
     <t>I002</t>
   </si>
   <si>
+    <t>W001</t>
+  </si>
+  <si>
+    <t>W001_past</t>
+  </si>
+  <si>
+    <t>W002</t>
+  </si>
+  <si>
     <t>W004_I_signal</t>
   </si>
   <si>
-    <t>W001</t>
-  </si>
-  <si>
-    <t>W002</t>
+    <t>W001_current</t>
   </si>
   <si>
     <t>G004</t>
@@ -85,6 +91,9 @@
     <t>V004</t>
   </si>
   <si>
+    <t>V023</t>
+  </si>
+  <si>
     <t>I003</t>
   </si>
   <si>
@@ -140,6 +149,9 @@
   </si>
   <si>
     <t>V001</t>
+  </si>
+  <si>
+    <t>V024</t>
   </si>
   <si>
     <t>W004_V_signal</t>
@@ -744,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I140"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -807,7 +819,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
@@ -822,21 +834,21 @@
         <v>0</v>
       </c>
       <c r="F3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>0.5333333333333333</v>
+        <v>0.5510416666666668</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="b">
         <v>1</v>
@@ -860,12 +872,12 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>0.53125</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
@@ -889,12 +901,12 @@
         <v>4</v>
       </c>
       <c r="I5">
-        <v>0.521875</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" t="b">
         <v>1</v>
@@ -918,12 +930,12 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>0.51875</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
@@ -947,12 +959,12 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>0.51875</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B8" t="b">
         <v>1</v>
@@ -976,12 +988,12 @@
         <v>4</v>
       </c>
       <c r="I8">
-        <v>0.5145833333333332</v>
+        <v>0.5239583333333333</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" t="b">
         <v>1</v>
@@ -990,10 +1002,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -1005,12 +1017,12 @@
         <v>4</v>
       </c>
       <c r="I9">
-        <v>0.5104166666666666</v>
+        <v>0.5239583333333333</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B10" t="b">
         <v>1</v>
@@ -1019,10 +1031,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -1034,12 +1046,12 @@
         <v>4</v>
       </c>
       <c r="I10">
-        <v>0.509375</v>
+        <v>0.5239583333333333</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B11" t="b">
         <v>1</v>
@@ -1063,12 +1075,12 @@
         <v>4</v>
       </c>
       <c r="I11">
-        <v>0.5052083333333334</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B12" t="b">
         <v>1</v>
@@ -1077,10 +1089,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
@@ -1092,15 +1104,15 @@
         <v>4</v>
       </c>
       <c r="I12">
-        <v>0.478125</v>
+        <v>0.51875</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
@@ -1118,15 +1130,15 @@
         <v>1</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13">
-        <v>0.5354166666666667</v>
+        <v>0.5145833333333332</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B14" t="b">
         <v>1</v>
@@ -1138,7 +1150,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -1147,15 +1159,15 @@
         <v>1</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14">
-        <v>0.5302083333333333</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B15" t="b">
         <v>1</v>
@@ -1167,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
@@ -1176,15 +1188,15 @@
         <v>1</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15">
-        <v>0.5302083333333333</v>
+        <v>0.509375</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B16" t="b">
         <v>1</v>
@@ -1193,7 +1205,7 @@
         <v>1</v>
       </c>
       <c r="D16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -1205,15 +1217,15 @@
         <v>1</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I16">
-        <v>0.5291666666666667</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B17" t="b">
         <v>1</v>
@@ -1225,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
@@ -1234,24 +1246,24 @@
         <v>1</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>0.5291666666666667</v>
+        <v>0.478125</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="b">
         <v>1</v>
       </c>
       <c r="D18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -1266,12 +1278,12 @@
         <v>3</v>
       </c>
       <c r="I18">
-        <v>0.5291666666666666</v>
+        <v>0.5354166666666667</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B19" t="b">
         <v>1</v>
@@ -1295,12 +1307,12 @@
         <v>3</v>
       </c>
       <c r="I19">
-        <v>0.5229166666666666</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B20" t="b">
         <v>1</v>
@@ -1324,12 +1336,12 @@
         <v>3</v>
       </c>
       <c r="I20">
-        <v>0.521875</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B21" t="b">
         <v>1</v>
@@ -1353,12 +1365,12 @@
         <v>3</v>
       </c>
       <c r="I21">
-        <v>0.521875</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B22" t="b">
         <v>1</v>
@@ -1382,15 +1394,15 @@
         <v>3</v>
       </c>
       <c r="I22">
-        <v>0.5166666666666666</v>
+        <v>0.5291666666666667</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" t="b">
         <v>1</v>
@@ -1399,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1411,12 +1423,12 @@
         <v>3</v>
       </c>
       <c r="I23">
-        <v>0.5114583333333333</v>
+        <v>0.5291666666666667</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B24" t="b">
         <v>1</v>
@@ -1440,15 +1452,15 @@
         <v>3</v>
       </c>
       <c r="I24">
-        <v>0.5114583333333333</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" t="b">
         <v>1</v>
@@ -1457,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
@@ -1469,12 +1481,12 @@
         <v>3</v>
       </c>
       <c r="I25">
-        <v>0.5104166666666666</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B26" t="b">
         <v>1</v>
@@ -1498,12 +1510,12 @@
         <v>3</v>
       </c>
       <c r="I26">
-        <v>0.509375</v>
+        <v>0.5229166666666666</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B27" t="b">
         <v>1</v>
@@ -1527,12 +1539,12 @@
         <v>3</v>
       </c>
       <c r="I27">
-        <v>0.5083333333333334</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B28" t="b">
         <v>1</v>
@@ -1556,12 +1568,12 @@
         <v>3</v>
       </c>
       <c r="I28">
-        <v>0.5083333333333334</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B29" t="b">
         <v>1</v>
@@ -1585,15 +1597,15 @@
         <v>3</v>
       </c>
       <c r="I29">
-        <v>0.5072916666666666</v>
+        <v>0.5166666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="b">
         <v>1</v>
@@ -1602,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
@@ -1614,12 +1626,12 @@
         <v>3</v>
       </c>
       <c r="I30">
-        <v>0.5062500000000001</v>
+        <v>0.5114583333333333</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B31" t="b">
         <v>1</v>
@@ -1643,15 +1655,15 @@
         <v>3</v>
       </c>
       <c r="I31">
-        <v>0.5062500000000001</v>
+        <v>0.5114583333333333</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" t="b">
         <v>1</v>
@@ -1660,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
@@ -1672,12 +1684,12 @@
         <v>3</v>
       </c>
       <c r="I32">
-        <v>0.5062500000000001</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B33" t="b">
         <v>1</v>
@@ -1701,12 +1713,12 @@
         <v>3</v>
       </c>
       <c r="I33">
-        <v>0.5052083333333334</v>
+        <v>0.509375</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B34" t="b">
         <v>1</v>
@@ -1730,12 +1742,12 @@
         <v>3</v>
       </c>
       <c r="I34">
-        <v>0.503125</v>
+        <v>0.5083333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B35" t="b">
         <v>1</v>
@@ -1759,12 +1771,12 @@
         <v>3</v>
       </c>
       <c r="I35">
-        <v>0.503125</v>
+        <v>0.5083333333333334</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B36" t="b">
         <v>1</v>
@@ -1788,12 +1800,12 @@
         <v>3</v>
       </c>
       <c r="I36">
-        <v>0.5</v>
+        <v>0.5072916666666666</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="B37" t="b">
         <v>1</v>
@@ -1817,12 +1829,12 @@
         <v>3</v>
       </c>
       <c r="I37">
-        <v>0.5</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B38" t="b">
         <v>1</v>
@@ -1846,7 +1858,7 @@
         <v>3</v>
       </c>
       <c r="I38">
-        <v>0.5</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1875,7 +1887,7 @@
         <v>3</v>
       </c>
       <c r="I39">
-        <v>0.4989583333333334</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1892,24 +1904,24 @@
         <v>0</v>
       </c>
       <c r="E40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
       </c>
       <c r="G40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40">
         <v>3</v>
       </c>
       <c r="I40">
-        <v>0.4989583333333333</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="b">
         <v>1</v>
@@ -1933,12 +1945,12 @@
         <v>3</v>
       </c>
       <c r="I41">
-        <v>0.4979166666666666</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="b">
         <v>1</v>
@@ -1962,12 +1974,12 @@
         <v>3</v>
       </c>
       <c r="I42">
-        <v>0.4958333333333334</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B43" t="b">
         <v>1</v>
@@ -1991,12 +2003,12 @@
         <v>3</v>
       </c>
       <c r="I43">
-        <v>0.4958333333333334</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B44" t="b">
         <v>1</v>
@@ -2020,12 +2032,12 @@
         <v>3</v>
       </c>
       <c r="I44">
-        <v>0.4958333333333334</v>
+        <v>0.4989583333333334</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B45" t="b">
         <v>1</v>
@@ -2049,12 +2061,12 @@
         <v>3</v>
       </c>
       <c r="I45">
-        <v>0.4947916666666666</v>
+        <v>0.4989583333333333</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="B46" t="b">
         <v>1</v>
@@ -2078,12 +2090,12 @@
         <v>3</v>
       </c>
       <c r="I46">
-        <v>0.4927083333333334</v>
+        <v>0.4979166666666666</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="B47" t="b">
         <v>1</v>
@@ -2107,12 +2119,12 @@
         <v>3</v>
       </c>
       <c r="I47">
-        <v>0.4927083333333334</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="B48" t="b">
         <v>1</v>
@@ -2124,24 +2136,24 @@
         <v>0</v>
       </c>
       <c r="E48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
       </c>
       <c r="G48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48">
         <v>3</v>
       </c>
       <c r="I48">
-        <v>0.4927083333333334</v>
+        <v>0.4947916666666666</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="B49" t="b">
         <v>1</v>
@@ -2165,12 +2177,12 @@
         <v>3</v>
       </c>
       <c r="I49">
-        <v>0.4927083333333334</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B50" t="b">
         <v>1</v>
@@ -2194,12 +2206,12 @@
         <v>3</v>
       </c>
       <c r="I50">
-        <v>0.4916666666666666</v>
+        <v>0.490625</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B51" t="b">
         <v>1</v>
@@ -2223,12 +2235,12 @@
         <v>3</v>
       </c>
       <c r="I51">
-        <v>0.490625</v>
+        <v>0.4885416666666667</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B52" t="b">
         <v>1</v>
@@ -2252,12 +2264,12 @@
         <v>3</v>
       </c>
       <c r="I52">
-        <v>0.4885416666666667</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B53" t="b">
         <v>1</v>
@@ -2281,12 +2293,12 @@
         <v>3</v>
       </c>
       <c r="I53">
-        <v>0.4875</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B54" t="b">
         <v>1</v>
@@ -2310,12 +2322,12 @@
         <v>3</v>
       </c>
       <c r="I54">
-        <v>0.4875</v>
+        <v>0.4802083333333333</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B55" t="b">
         <v>1</v>
@@ -2339,12 +2351,12 @@
         <v>3</v>
       </c>
       <c r="I55">
-        <v>0.484375</v>
+        <v>0.4770833333333333</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B56" t="b">
         <v>1</v>
@@ -2362,18 +2374,18 @@
         <v>0</v>
       </c>
       <c r="G56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I56">
-        <v>0.4802083333333333</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B57" t="b">
         <v>1</v>
@@ -2391,18 +2403,18 @@
         <v>0</v>
       </c>
       <c r="G57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I57">
-        <v>0.4770833333333333</v>
+        <v>0.5270833333333332</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="B58" t="b">
         <v>1</v>
@@ -2420,18 +2432,18 @@
         <v>0</v>
       </c>
       <c r="G58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I58">
-        <v>0.465625</v>
+        <v>0.5260416666666667</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="B59" t="b">
         <v>1</v>
@@ -2449,18 +2461,18 @@
         <v>0</v>
       </c>
       <c r="G59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I59">
-        <v>0.4645833333333334</v>
+        <v>0.5260416666666667</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B60" t="b">
         <v>1</v>
@@ -2484,12 +2496,12 @@
         <v>2</v>
       </c>
       <c r="I60">
-        <v>0.5291666666666666</v>
+        <v>0.5239583333333334</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B61" t="b">
         <v>1</v>
@@ -2513,12 +2525,12 @@
         <v>2</v>
       </c>
       <c r="I61">
-        <v>0.5270833333333332</v>
+        <v>0.5177083333333334</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B62" t="b">
         <v>1</v>
@@ -2542,12 +2554,12 @@
         <v>2</v>
       </c>
       <c r="I62">
-        <v>0.5260416666666667</v>
+        <v>0.5166666666666667</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B63" t="b">
         <v>1</v>
@@ -2571,12 +2583,12 @@
         <v>2</v>
       </c>
       <c r="I63">
-        <v>0.5260416666666667</v>
+        <v>0.515625</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B64" t="b">
         <v>1</v>
@@ -2600,12 +2612,12 @@
         <v>2</v>
       </c>
       <c r="I64">
-        <v>0.5239583333333334</v>
+        <v>0.5135416666666666</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B65" t="b">
         <v>1</v>
@@ -2629,12 +2641,12 @@
         <v>2</v>
       </c>
       <c r="I65">
-        <v>0.5177083333333334</v>
+        <v>0.5135416666666666</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B66" t="b">
         <v>1</v>
@@ -2658,12 +2670,12 @@
         <v>2</v>
       </c>
       <c r="I66">
-        <v>0.5166666666666667</v>
+        <v>0.5104166666666667</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B67" t="b">
         <v>1</v>
@@ -2687,12 +2699,12 @@
         <v>2</v>
       </c>
       <c r="I67">
-        <v>0.515625</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B68" t="b">
         <v>1</v>
@@ -2716,12 +2728,12 @@
         <v>2</v>
       </c>
       <c r="I68">
-        <v>0.5135416666666666</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B69" t="b">
         <v>1</v>
@@ -2745,12 +2757,12 @@
         <v>2</v>
       </c>
       <c r="I69">
-        <v>0.5135416666666666</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B70" t="b">
         <v>1</v>
@@ -2774,12 +2786,12 @@
         <v>2</v>
       </c>
       <c r="I70">
-        <v>0.5104166666666667</v>
+        <v>0.50625</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B71" t="b">
         <v>1</v>
@@ -2803,12 +2815,12 @@
         <v>2</v>
       </c>
       <c r="I71">
-        <v>0.5083333333333333</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B72" t="b">
         <v>1</v>
@@ -2832,12 +2844,12 @@
         <v>2</v>
       </c>
       <c r="I72">
-        <v>0.5083333333333333</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B73" t="b">
         <v>1</v>
@@ -2861,12 +2873,12 @@
         <v>2</v>
       </c>
       <c r="I73">
-        <v>0.5062500000000001</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B74" t="b">
         <v>1</v>
@@ -2890,12 +2902,12 @@
         <v>2</v>
       </c>
       <c r="I74">
-        <v>0.50625</v>
+        <v>0.5020833333333333</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B75" t="b">
         <v>1</v>
@@ -2919,12 +2931,12 @@
         <v>2</v>
       </c>
       <c r="I75">
-        <v>0.503125</v>
+        <v>0.5010416666666667</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B76" t="b">
         <v>1</v>
@@ -2948,12 +2960,12 @@
         <v>2</v>
       </c>
       <c r="I76">
-        <v>0.503125</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B77" t="b">
         <v>1</v>
@@ -2977,12 +2989,12 @@
         <v>2</v>
       </c>
       <c r="I77">
-        <v>0.503125</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B78" t="b">
         <v>1</v>
@@ -3006,12 +3018,12 @@
         <v>2</v>
       </c>
       <c r="I78">
-        <v>0.5020833333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B79" t="b">
         <v>1</v>
@@ -3035,12 +3047,12 @@
         <v>2</v>
       </c>
       <c r="I79">
-        <v>0.5010416666666667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="B80" t="b">
         <v>1</v>
@@ -3064,12 +3076,12 @@
         <v>2</v>
       </c>
       <c r="I80">
-        <v>0.5000000000000001</v>
+        <v>0.4989583333333333</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="B81" t="b">
         <v>1</v>
@@ -3093,12 +3105,12 @@
         <v>2</v>
       </c>
       <c r="I81">
-        <v>0.5000000000000001</v>
+        <v>0.496875</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B82" t="b">
         <v>1</v>
@@ -3122,12 +3134,12 @@
         <v>2</v>
       </c>
       <c r="I82">
-        <v>0.5</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B83" t="b">
         <v>1</v>
@@ -3151,12 +3163,12 @@
         <v>2</v>
       </c>
       <c r="I83">
-        <v>0.5</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B84" t="b">
         <v>1</v>
@@ -3180,12 +3192,12 @@
         <v>2</v>
       </c>
       <c r="I84">
-        <v>0.5</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B85" t="b">
         <v>1</v>
@@ -3209,12 +3221,12 @@
         <v>2</v>
       </c>
       <c r="I85">
-        <v>0.5</v>
+        <v>0.4958333333333333</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B86" t="b">
         <v>1</v>
@@ -3238,12 +3250,12 @@
         <v>2</v>
       </c>
       <c r="I86">
-        <v>0.4989583333333333</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B87" t="b">
         <v>1</v>
@@ -3267,12 +3279,12 @@
         <v>2</v>
       </c>
       <c r="I87">
-        <v>0.496875</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B88" t="b">
         <v>1</v>
@@ -3296,12 +3308,12 @@
         <v>2</v>
       </c>
       <c r="I88">
-        <v>0.4958333333333334</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B89" t="b">
         <v>1</v>
@@ -3325,12 +3337,12 @@
         <v>2</v>
       </c>
       <c r="I89">
-        <v>0.4958333333333334</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B90" t="b">
         <v>1</v>
@@ -3354,12 +3366,12 @@
         <v>2</v>
       </c>
       <c r="I90">
-        <v>0.4958333333333334</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B91" t="b">
         <v>1</v>
@@ -3383,12 +3395,12 @@
         <v>2</v>
       </c>
       <c r="I91">
-        <v>0.4958333333333333</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B92" t="b">
         <v>1</v>
@@ -3412,12 +3424,12 @@
         <v>2</v>
       </c>
       <c r="I92">
-        <v>0.4947916666666667</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B93" t="b">
         <v>1</v>
@@ -3441,12 +3453,12 @@
         <v>2</v>
       </c>
       <c r="I93">
-        <v>0.4947916666666667</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B94" t="b">
         <v>1</v>
@@ -3470,12 +3482,12 @@
         <v>2</v>
       </c>
       <c r="I94">
-        <v>0.4947916666666667</v>
+        <v>0.4916666666666667</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B95" t="b">
         <v>1</v>
@@ -3499,12 +3511,12 @@
         <v>2</v>
       </c>
       <c r="I95">
-        <v>0.4947916666666667</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B96" t="b">
         <v>1</v>
@@ -3528,15 +3540,15 @@
         <v>2</v>
       </c>
       <c r="I96">
-        <v>0.4927083333333334</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C97" t="b">
         <v>1</v>
@@ -3551,18 +3563,18 @@
         <v>0</v>
       </c>
       <c r="G97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97">
         <v>2</v>
       </c>
       <c r="I97">
-        <v>0.4927083333333333</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B98" t="b">
         <v>1</v>
@@ -3586,12 +3598,12 @@
         <v>2</v>
       </c>
       <c r="I98">
-        <v>0.4927083333333333</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B99" t="b">
         <v>1</v>
@@ -3615,12 +3627,12 @@
         <v>2</v>
       </c>
       <c r="I99">
-        <v>0.4927083333333333</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B100" t="b">
         <v>1</v>
@@ -3644,12 +3656,12 @@
         <v>2</v>
       </c>
       <c r="I100">
-        <v>0.4916666666666667</v>
+        <v>0.4854166666666666</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B101" t="b">
         <v>1</v>
@@ -3673,12 +3685,12 @@
         <v>2</v>
       </c>
       <c r="I101">
-        <v>0.4916666666666666</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B102" t="b">
         <v>1</v>
@@ -3702,15 +3714,15 @@
         <v>2</v>
       </c>
       <c r="I102">
-        <v>0.4895833333333333</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C103" t="b">
         <v>1</v>
@@ -3725,18 +3737,18 @@
         <v>0</v>
       </c>
       <c r="G103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H103">
         <v>2</v>
       </c>
       <c r="I103">
-        <v>0.4885416666666666</v>
+        <v>0.4833333333333334</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B104" t="b">
         <v>1</v>
@@ -3760,12 +3772,12 @@
         <v>2</v>
       </c>
       <c r="I104">
-        <v>0.4885416666666666</v>
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B105" t="b">
         <v>1</v>
@@ -3789,12 +3801,12 @@
         <v>2</v>
       </c>
       <c r="I105">
-        <v>0.4864583333333333</v>
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B106" t="b">
         <v>1</v>
@@ -3818,12 +3830,12 @@
         <v>2</v>
       </c>
       <c r="I106">
-        <v>0.4854166666666666</v>
+        <v>0.4802083333333334</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B107" t="b">
         <v>1</v>
@@ -3847,12 +3859,12 @@
         <v>2</v>
       </c>
       <c r="I107">
-        <v>0.484375</v>
+        <v>0.4791666666666667</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B108" t="b">
         <v>1</v>
@@ -3876,12 +3888,12 @@
         <v>2</v>
       </c>
       <c r="I108">
-        <v>0.484375</v>
+        <v>0.4770833333333333</v>
       </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B109" t="b">
         <v>1</v>
@@ -3905,12 +3917,12 @@
         <v>2</v>
       </c>
       <c r="I109">
-        <v>0.4833333333333334</v>
+        <v>0.4739583333333333</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B110" t="b">
         <v>1</v>
@@ -3934,18 +3946,18 @@
         <v>2</v>
       </c>
       <c r="I110">
-        <v>0.4833333333333333</v>
+        <v>0.4739583333333333</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B111" t="b">
         <v>1</v>
       </c>
       <c r="C111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111" t="b">
         <v>0</v>
@@ -3960,18 +3972,18 @@
         <v>0</v>
       </c>
       <c r="H111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I111">
-        <v>0.4833333333333333</v>
+        <v>0.5354166666666667</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C112" t="b">
         <v>1</v>
@@ -3989,18 +4001,18 @@
         <v>0</v>
       </c>
       <c r="H112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I112">
-        <v>0.4802083333333334</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C113" t="b">
         <v>1</v>
@@ -4018,18 +4030,18 @@
         <v>0</v>
       </c>
       <c r="H113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I113">
-        <v>0.4791666666666667</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C114" t="b">
         <v>1</v>
@@ -4047,18 +4059,18 @@
         <v>0</v>
       </c>
       <c r="H114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I114">
-        <v>0.4770833333333333</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C115" t="b">
         <v>1</v>
@@ -4076,18 +4088,18 @@
         <v>0</v>
       </c>
       <c r="H115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I115">
-        <v>0.4739583333333333</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C116" t="b">
         <v>1</v>
@@ -4105,21 +4117,21 @@
         <v>0</v>
       </c>
       <c r="H116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I116">
-        <v>0.4739583333333333</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117" t="b">
         <v>0</v>
@@ -4137,12 +4149,12 @@
         <v>1</v>
       </c>
       <c r="I117">
-        <v>0.5354166666666667</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B118" t="b">
         <v>0</v>
@@ -4166,12 +4178,12 @@
         <v>1</v>
       </c>
       <c r="I118">
-        <v>0.53125</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B119" t="b">
         <v>0</v>
@@ -4195,18 +4207,18 @@
         <v>1</v>
       </c>
       <c r="I119">
-        <v>0.5125</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120" t="b">
         <v>0</v>
@@ -4224,18 +4236,18 @@
         <v>1</v>
       </c>
       <c r="I120">
-        <v>0.5104166666666666</v>
+        <v>0.5041666666666667</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D121" t="b">
         <v>0</v>
@@ -4253,18 +4265,18 @@
         <v>1</v>
       </c>
       <c r="I121">
-        <v>0.5104166666666666</v>
+        <v>0.5041666666666667</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="B122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D122" t="b">
         <v>0</v>
@@ -4282,18 +4294,18 @@
         <v>1</v>
       </c>
       <c r="I122">
-        <v>0.5104166666666666</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123" t="b">
         <v>0</v>
@@ -4311,12 +4323,12 @@
         <v>1</v>
       </c>
       <c r="I123">
-        <v>0.5104166666666666</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B124" t="b">
         <v>0</v>
@@ -4340,18 +4352,18 @@
         <v>1</v>
       </c>
       <c r="I124">
-        <v>0.5052083333333334</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125" t="b">
         <v>0</v>
@@ -4369,18 +4381,18 @@
         <v>1</v>
       </c>
       <c r="I125">
-        <v>0.5052083333333334</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D126" t="b">
         <v>0</v>
@@ -4398,18 +4410,18 @@
         <v>1</v>
       </c>
       <c r="I126">
-        <v>0.5041666666666667</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="127" spans="1:9">
       <c r="A127" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D127" t="b">
         <v>0</v>
@@ -4427,18 +4439,18 @@
         <v>1</v>
       </c>
       <c r="I127">
-        <v>0.5041666666666667</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D128" t="b">
         <v>0</v>
@@ -4456,12 +4468,12 @@
         <v>1</v>
       </c>
       <c r="I128">
-        <v>0.4947916666666667</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B129" t="b">
         <v>1</v>
@@ -4485,18 +4497,18 @@
         <v>1</v>
       </c>
       <c r="I129">
-        <v>0.4927083333333333</v>
+        <v>0.4854166666666666</v>
       </c>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D130" t="b">
         <v>0</v>
@@ -4514,12 +4526,12 @@
         <v>1</v>
       </c>
       <c r="I130">
-        <v>0.4895833333333333</v>
+        <v>0.4760416666666667</v>
       </c>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B131" t="b">
         <v>1</v>
@@ -4543,18 +4555,18 @@
         <v>1</v>
       </c>
       <c r="I131">
-        <v>0.4875</v>
+        <v>0.4614583333333333</v>
       </c>
     </row>
     <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D132" t="b">
         <v>0</v>
@@ -4572,18 +4584,18 @@
         <v>1</v>
       </c>
       <c r="I132">
-        <v>0.4864583333333333</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="133" spans="1:9">
       <c r="A133" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D133" t="b">
         <v>0</v>
@@ -4601,18 +4613,18 @@
         <v>1</v>
       </c>
       <c r="I133">
-        <v>0.4864583333333333</v>
+        <v>0.4260416666666667</v>
       </c>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B134" t="b">
         <v>0</v>
       </c>
       <c r="C134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D134" t="b">
         <v>0</v>
@@ -4627,183 +4639,9 @@
         <v>0</v>
       </c>
       <c r="H134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I134">
-        <v>0.4864583333333333</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9">
-      <c r="A135" t="s">
-        <v>127</v>
-      </c>
-      <c r="B135" t="b">
-        <v>1</v>
-      </c>
-      <c r="C135" t="b">
-        <v>0</v>
-      </c>
-      <c r="D135" t="b">
-        <v>0</v>
-      </c>
-      <c r="E135" t="b">
-        <v>0</v>
-      </c>
-      <c r="F135" t="b">
-        <v>0</v>
-      </c>
-      <c r="G135" t="b">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>1</v>
-      </c>
-      <c r="I135">
-        <v>0.4854166666666666</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9">
-      <c r="A136" t="s">
-        <v>128</v>
-      </c>
-      <c r="B136" t="b">
-        <v>1</v>
-      </c>
-      <c r="C136" t="b">
-        <v>0</v>
-      </c>
-      <c r="D136" t="b">
-        <v>0</v>
-      </c>
-      <c r="E136" t="b">
-        <v>0</v>
-      </c>
-      <c r="F136" t="b">
-        <v>0</v>
-      </c>
-      <c r="G136" t="b">
-        <v>0</v>
-      </c>
-      <c r="H136">
-        <v>1</v>
-      </c>
-      <c r="I136">
-        <v>0.4760416666666667</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9">
-      <c r="A137" t="s">
-        <v>129</v>
-      </c>
-      <c r="B137" t="b">
-        <v>1</v>
-      </c>
-      <c r="C137" t="b">
-        <v>0</v>
-      </c>
-      <c r="D137" t="b">
-        <v>0</v>
-      </c>
-      <c r="E137" t="b">
-        <v>0</v>
-      </c>
-      <c r="F137" t="b">
-        <v>0</v>
-      </c>
-      <c r="G137" t="b">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>1</v>
-      </c>
-      <c r="I137">
-        <v>0.4614583333333333</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9">
-      <c r="A138" t="s">
-        <v>130</v>
-      </c>
-      <c r="B138" t="b">
-        <v>1</v>
-      </c>
-      <c r="C138" t="b">
-        <v>0</v>
-      </c>
-      <c r="D138" t="b">
-        <v>0</v>
-      </c>
-      <c r="E138" t="b">
-        <v>0</v>
-      </c>
-      <c r="F138" t="b">
-        <v>0</v>
-      </c>
-      <c r="G138" t="b">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>1</v>
-      </c>
-      <c r="I138">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9">
-      <c r="A139" t="s">
-        <v>131</v>
-      </c>
-      <c r="B139" t="b">
-        <v>1</v>
-      </c>
-      <c r="C139" t="b">
-        <v>0</v>
-      </c>
-      <c r="D139" t="b">
-        <v>0</v>
-      </c>
-      <c r="E139" t="b">
-        <v>0</v>
-      </c>
-      <c r="F139" t="b">
-        <v>0</v>
-      </c>
-      <c r="G139" t="b">
-        <v>0</v>
-      </c>
-      <c r="H139">
-        <v>1</v>
-      </c>
-      <c r="I139">
-        <v>0.4260416666666667</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9">
-      <c r="A140" t="s">
-        <v>132</v>
-      </c>
-      <c r="B140" t="b">
-        <v>0</v>
-      </c>
-      <c r="C140" t="b">
-        <v>0</v>
-      </c>
-      <c r="D140" t="b">
-        <v>0</v>
-      </c>
-      <c r="E140" t="b">
-        <v>0</v>
-      </c>
-      <c r="F140" t="b">
-        <v>0</v>
-      </c>
-      <c r="G140" t="b">
-        <v>0</v>
-      </c>
-      <c r="H140">
-        <v>0</v>
-      </c>
-      <c r="I140">
         <v>0.478125</v>
       </c>
     </row>

--- a/F_grouping/reference/backtesting_score.xlsx
+++ b/F_grouping/reference/backtesting_score.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="245">
   <si>
     <t>factor_name</t>
   </si>
@@ -61,6 +61,9 @@
     <t>W003_I_signal</t>
   </si>
   <si>
+    <t>W006_binary</t>
+  </si>
+  <si>
     <t>W003_W_signal</t>
   </si>
   <si>
@@ -178,6 +181,9 @@
     <t>G062</t>
   </si>
   <si>
+    <t>I060</t>
+  </si>
+  <si>
     <t>W003_V</t>
   </si>
   <si>
@@ -211,6 +217,9 @@
     <t>G025</t>
   </si>
   <si>
+    <t>I061</t>
+  </si>
+  <si>
     <t>G046</t>
   </si>
   <si>
@@ -457,6 +466,9 @@
     <t>O010</t>
   </si>
   <si>
+    <t>I059</t>
+  </si>
+  <si>
     <t>I009</t>
   </si>
   <si>
@@ -475,6 +487,9 @@
     <t>G066</t>
   </si>
   <si>
+    <t>I072</t>
+  </si>
+  <si>
     <t>F011</t>
   </si>
   <si>
@@ -610,6 +625,9 @@
     <t>I012</t>
   </si>
   <si>
+    <t>I058</t>
+  </si>
+  <si>
     <t>G039</t>
   </si>
   <si>
@@ -623,6 +641,9 @@
   </si>
   <si>
     <t>D015</t>
+  </si>
+  <si>
+    <t>I057</t>
   </si>
   <si>
     <t>G016</t>
@@ -1059,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M227"/>
+  <dimension ref="A1:M242"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1146,7 +1167,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
@@ -1173,21 +1194,21 @@
         <v>6</v>
       </c>
       <c r="J3">
-        <v>0.5326329975758939</v>
+        <v>0.5413335173747426</v>
       </c>
       <c r="K3">
-        <v>1.020818141928755</v>
+        <v>1.009200594833866</v>
       </c>
       <c r="L3">
-        <v>0.001746286113433282</v>
+        <v>0.002000481442055657</v>
       </c>
       <c r="M3">
-        <v>0.5395833333333333</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" t="b">
         <v>1</v>
@@ -1214,21 +1235,21 @@
         <v>6</v>
       </c>
       <c r="J4">
-        <v>0.528267333354452</v>
+        <v>0.5326329975758939</v>
       </c>
       <c r="K4">
-        <v>1.035247767188338</v>
+        <v>1.020818141928755</v>
       </c>
       <c r="L4">
-        <v>0.001738702346857484</v>
+        <v>0.001746286113433282</v>
       </c>
       <c r="M4">
-        <v>0.525</v>
+        <v>0.5395833333333333</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
@@ -1255,21 +1276,21 @@
         <v>6</v>
       </c>
       <c r="J5">
-        <v>0.5264070920813524</v>
+        <v>0.5286951324510081</v>
       </c>
       <c r="K5">
-        <v>1.033659113470365</v>
+        <v>1.033368188934639</v>
       </c>
       <c r="L5">
-        <v>0.00168946491757375</v>
+        <v>0.001742068784585837</v>
       </c>
       <c r="M5">
-        <v>0.5510416666666668</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="b">
         <v>1</v>
@@ -1296,21 +1317,21 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>0.5247475680359789</v>
+        <v>0.528267333354452</v>
       </c>
       <c r="K6">
-        <v>1.045705096136908</v>
+        <v>1.035247767188338</v>
       </c>
       <c r="L6">
-        <v>0.001686269761205422</v>
+        <v>0.001738702346857484</v>
       </c>
       <c r="M6">
-        <v>0.5333333333333333</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
@@ -1337,21 +1358,21 @@
         <v>6</v>
       </c>
       <c r="J7">
-        <v>0.5247475680359789</v>
+        <v>0.5264070920813524</v>
       </c>
       <c r="K7">
-        <v>1.045705096136908</v>
+        <v>1.033659113470365</v>
       </c>
       <c r="L7">
-        <v>0.001686269761205422</v>
+        <v>0.00168946491757375</v>
       </c>
       <c r="M7">
-        <v>0.5333333333333333</v>
+        <v>0.5510416666666668</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" t="b">
         <v>1</v>
@@ -1378,21 +1399,21 @@
         <v>6</v>
       </c>
       <c r="J8">
-        <v>0.5243716231854127</v>
+        <v>0.5264070920813524</v>
       </c>
       <c r="K8">
-        <v>1.03943580295143</v>
+        <v>1.033659113470365</v>
       </c>
       <c r="L8">
-        <v>0.00159913383023423</v>
+        <v>0.00168946491757375</v>
       </c>
       <c r="M8">
-        <v>0.5239583333333333</v>
+        <v>0.5510416666666668</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9" t="b">
         <v>1</v>
@@ -1419,21 +1440,21 @@
         <v>6</v>
       </c>
       <c r="J9">
-        <v>0.5243716231854127</v>
+        <v>0.5247475680359789</v>
       </c>
       <c r="K9">
-        <v>1.03943580295143</v>
+        <v>1.045705096136908</v>
       </c>
       <c r="L9">
-        <v>0.00159913383023423</v>
+        <v>0.001686269761205422</v>
       </c>
       <c r="M9">
-        <v>0.5239583333333333</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B10" t="b">
         <v>1</v>
@@ -1460,21 +1481,21 @@
         <v>6</v>
       </c>
       <c r="J10">
-        <v>0.5293016338089147</v>
+        <v>0.5247475680359789</v>
       </c>
       <c r="K10">
-        <v>1.01854835424442</v>
+        <v>1.045705096136908</v>
       </c>
       <c r="L10">
-        <v>0.001559583303257609</v>
+        <v>0.001686269761205422</v>
       </c>
       <c r="M10">
-        <v>0.521875</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B11" t="b">
         <v>1</v>
@@ -1501,21 +1522,21 @@
         <v>6</v>
       </c>
       <c r="J11">
-        <v>0.5274627797329472</v>
+        <v>0.5247475680359789</v>
       </c>
       <c r="K11">
-        <v>1.021738443668535</v>
+        <v>1.045705096136908</v>
       </c>
       <c r="L11">
-        <v>0.001526807474973001</v>
+        <v>0.001686269761205422</v>
       </c>
       <c r="M11">
-        <v>0.5052083333333334</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B12" t="b">
         <v>1</v>
@@ -1542,21 +1563,21 @@
         <v>6</v>
       </c>
       <c r="J12">
-        <v>0.5274627797329472</v>
+        <v>0.5243716231854127</v>
       </c>
       <c r="K12">
-        <v>1.021738443668535</v>
+        <v>1.03943580295143</v>
       </c>
       <c r="L12">
-        <v>0.001526807474973001</v>
+        <v>0.00159913383023423</v>
       </c>
       <c r="M12">
-        <v>0.5052083333333334</v>
+        <v>0.5239583333333333</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B13" t="b">
         <v>1</v>
@@ -1583,21 +1604,21 @@
         <v>6</v>
       </c>
       <c r="J13">
-        <v>0.5318345484773038</v>
+        <v>0.5243716231854127</v>
       </c>
       <c r="K13">
-        <v>1.002369045795006</v>
+        <v>1.03943580295143</v>
       </c>
       <c r="L13">
-        <v>0.001501703365704792</v>
+        <v>0.00159913383023423</v>
       </c>
       <c r="M13">
-        <v>0.5145833333333332</v>
+        <v>0.5239583333333333</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B14" t="b">
         <v>1</v>
@@ -1624,21 +1645,21 @@
         <v>6</v>
       </c>
       <c r="J14">
-        <v>0.5230790641801295</v>
+        <v>0.5293016338089147</v>
       </c>
       <c r="K14">
-        <v>1.036234633409911</v>
+        <v>1.01854835424442</v>
       </c>
       <c r="L14">
-        <v>0.001486752530965102</v>
+        <v>0.001559583303257609</v>
       </c>
       <c r="M14">
-        <v>0.5104166666666666</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B15" t="b">
         <v>1</v>
@@ -1665,21 +1686,21 @@
         <v>6</v>
       </c>
       <c r="J15">
-        <v>0.5295746298664266</v>
+        <v>0.5274627797329472</v>
       </c>
       <c r="K15">
-        <v>1.010598045406975</v>
+        <v>1.021738443668535</v>
       </c>
       <c r="L15">
-        <v>0.001482352962142391</v>
+        <v>0.001526807474973001</v>
       </c>
       <c r="M15">
-        <v>0.4989583333333333</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B16" t="b">
         <v>1</v>
@@ -1688,10 +1709,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -1706,21 +1727,21 @@
         <v>6</v>
       </c>
       <c r="J16">
-        <v>0.522139473458666</v>
+        <v>0.5274627797329472</v>
       </c>
       <c r="K16">
-        <v>1.029620517094269</v>
+        <v>1.021738443668535</v>
       </c>
       <c r="L16">
-        <v>0.001261665355402021</v>
+        <v>0.001526807474973001</v>
       </c>
       <c r="M16">
-        <v>0.509375</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B17" t="b">
         <v>1</v>
@@ -1729,10 +1750,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -1747,24 +1768,24 @@
         <v>6</v>
       </c>
       <c r="J17">
-        <v>0.5260400122662108</v>
+        <v>0.5318345484773038</v>
       </c>
       <c r="K17">
-        <v>1.006561934830848</v>
+        <v>1.002369045795006</v>
       </c>
       <c r="L17">
-        <v>0.00117139656173353</v>
+        <v>0.001501703365704792</v>
       </c>
       <c r="M17">
-        <v>0.5104166666666666</v>
+        <v>0.5145833333333332</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="b">
         <v>1</v>
@@ -1785,24 +1806,24 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>0.5238688923055044</v>
+        <v>0.5230790641801295</v>
       </c>
       <c r="K18">
-        <v>1.029629034931843</v>
+        <v>1.036234633409911</v>
       </c>
       <c r="L18">
-        <v>0.00147542310169879</v>
+        <v>0.001486752530965102</v>
       </c>
       <c r="M18">
-        <v>0.5354166666666667</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B19" t="b">
         <v>1</v>
@@ -1811,7 +1832,7 @@
         <v>1</v>
       </c>
       <c r="D19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -1826,24 +1847,24 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>0.5259239610009919</v>
+        <v>0.5295746298664266</v>
       </c>
       <c r="K19">
-        <v>1.024440180595053</v>
+        <v>1.010598045406975</v>
       </c>
       <c r="L19">
-        <v>0.001462050106882569</v>
+        <v>0.001482352962142391</v>
       </c>
       <c r="M19">
-        <v>0.4947916666666667</v>
+        <v>0.4989583333333333</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B20" t="b">
         <v>1</v>
@@ -1855,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -1867,24 +1888,24 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>0.5254222623126102</v>
+        <v>0.522139473458666</v>
       </c>
       <c r="K20">
-        <v>1.025541915565631</v>
+        <v>1.029620517094269</v>
       </c>
       <c r="L20">
-        <v>0.001442979540345599</v>
+        <v>0.001261665355402021</v>
       </c>
       <c r="M20">
-        <v>0.5166666666666667</v>
+        <v>0.509375</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B21" t="b">
         <v>1</v>
@@ -1896,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1908,24 +1929,24 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>0.5306611663813147</v>
+        <v>0.522139473458666</v>
       </c>
       <c r="K21">
-        <v>1.001214605754448</v>
+        <v>1.029620517094269</v>
       </c>
       <c r="L21">
-        <v>0.001393158567997</v>
+        <v>0.001261665355402021</v>
       </c>
       <c r="M21">
-        <v>0.5333333333333333</v>
+        <v>0.509375</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B22" t="b">
         <v>1</v>
@@ -1937,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1949,33 +1970,33 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>0.5267587168871589</v>
+        <v>0.5260400122662108</v>
       </c>
       <c r="K22">
-        <v>1.01381851832546</v>
+        <v>1.006561934830848</v>
       </c>
       <c r="L22">
-        <v>0.001386854528959906</v>
+        <v>0.00117139656173353</v>
       </c>
       <c r="M22">
-        <v>0.4916666666666667</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="b">
         <v>1</v>
       </c>
       <c r="D23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
@@ -1993,21 +2014,21 @@
         <v>5</v>
       </c>
       <c r="J23">
-        <v>0.5292621513106435</v>
+        <v>0.5238688923055044</v>
       </c>
       <c r="K23">
-        <v>1.003112924875302</v>
+        <v>1.029629034931843</v>
       </c>
       <c r="L23">
-        <v>0.001385781283267948</v>
+        <v>0.00147542310169879</v>
       </c>
       <c r="M23">
-        <v>0.5052083333333334</v>
+        <v>0.5354166666666667</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B24" t="b">
         <v>1</v>
@@ -2034,21 +2055,21 @@
         <v>5</v>
       </c>
       <c r="J24">
-        <v>0.5272255462315896</v>
+        <v>0.5259239610009919</v>
       </c>
       <c r="K24">
-        <v>1.016213324008339</v>
+        <v>1.024440180595053</v>
       </c>
       <c r="L24">
-        <v>0.001385221207479327</v>
+        <v>0.001462050106882569</v>
       </c>
       <c r="M24">
-        <v>0.509375</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B25" t="b">
         <v>1</v>
@@ -2075,21 +2096,21 @@
         <v>5</v>
       </c>
       <c r="J25">
-        <v>0.527230640888951</v>
+        <v>0.5254222623126102</v>
       </c>
       <c r="K25">
-        <v>1.017321435277489</v>
+        <v>1.025541915565631</v>
       </c>
       <c r="L25">
-        <v>0.001383809737497815</v>
+        <v>0.001442979540345599</v>
       </c>
       <c r="M25">
-        <v>0.5062500000000001</v>
+        <v>0.5166666666666667</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B26" t="b">
         <v>1</v>
@@ -2116,21 +2137,21 @@
         <v>5</v>
       </c>
       <c r="J26">
-        <v>0.527230640888951</v>
+        <v>0.5306611663813147</v>
       </c>
       <c r="K26">
-        <v>1.017321435277489</v>
+        <v>1.001214605754448</v>
       </c>
       <c r="L26">
-        <v>0.001383809737497815</v>
+        <v>0.001393158567997</v>
       </c>
       <c r="M26">
-        <v>0.5062500000000001</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B27" t="b">
         <v>1</v>
@@ -2157,21 +2178,21 @@
         <v>5</v>
       </c>
       <c r="J27">
-        <v>0.5308208765483126</v>
+        <v>0.5267587168871589</v>
       </c>
       <c r="K27">
-        <v>1.000253944133511</v>
+        <v>1.01381851832546</v>
       </c>
       <c r="L27">
-        <v>0.001372369855072267</v>
+        <v>0.001386854528959906</v>
       </c>
       <c r="M27">
-        <v>0.521875</v>
+        <v>0.4916666666666667</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B28" t="b">
         <v>1</v>
@@ -2198,21 +2219,21 @@
         <v>5</v>
       </c>
       <c r="J28">
-        <v>0.5308208765483126</v>
+        <v>0.5292621513106435</v>
       </c>
       <c r="K28">
-        <v>1.000253944133511</v>
+        <v>1.003112924875302</v>
       </c>
       <c r="L28">
-        <v>0.001372369855072267</v>
+        <v>0.001385781283267948</v>
       </c>
       <c r="M28">
-        <v>0.521875</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B29" t="b">
         <v>1</v>
@@ -2239,21 +2260,21 @@
         <v>5</v>
       </c>
       <c r="J29">
-        <v>0.5251559719258638</v>
+        <v>0.5292621513106435</v>
       </c>
       <c r="K29">
-        <v>1.020060384914307</v>
+        <v>1.003112924875302</v>
       </c>
       <c r="L29">
-        <v>0.001334290050121707</v>
+        <v>0.001385781283267948</v>
       </c>
       <c r="M29">
-        <v>0.528125</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B30" t="b">
         <v>1</v>
@@ -2280,21 +2301,21 @@
         <v>5</v>
       </c>
       <c r="J30">
-        <v>0.5216241131709639</v>
+        <v>0.5272255462315896</v>
       </c>
       <c r="K30">
-        <v>1.026452298190757</v>
+        <v>1.016213324008339</v>
       </c>
       <c r="L30">
-        <v>0.001319505267780912</v>
+        <v>0.001385221207479327</v>
       </c>
       <c r="M30">
-        <v>0.5302083333333333</v>
+        <v>0.509375</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B31" t="b">
         <v>1</v>
@@ -2321,21 +2342,21 @@
         <v>5</v>
       </c>
       <c r="J31">
-        <v>0.5216241131709639</v>
+        <v>0.527230640888951</v>
       </c>
       <c r="K31">
-        <v>1.026452298190757</v>
+        <v>1.017321435277489</v>
       </c>
       <c r="L31">
-        <v>0.001319505267780912</v>
+        <v>0.001383809737497815</v>
       </c>
       <c r="M31">
-        <v>0.5302083333333333</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B32" t="b">
         <v>1</v>
@@ -2362,24 +2383,24 @@
         <v>5</v>
       </c>
       <c r="J32">
-        <v>0.5238826719623297</v>
+        <v>0.527230640888951</v>
       </c>
       <c r="K32">
-        <v>1.017844667630376</v>
+        <v>1.017321435277489</v>
       </c>
       <c r="L32">
-        <v>0.001303997694158954</v>
+        <v>0.001383809737497815</v>
       </c>
       <c r="M32">
-        <v>0.5229166666666666</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" t="b">
         <v>1</v>
@@ -2388,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -2403,21 +2424,21 @@
         <v>5</v>
       </c>
       <c r="J33">
-        <v>0.5234221515505412</v>
+        <v>0.5308208765483126</v>
       </c>
       <c r="K33">
-        <v>1.028143238415307</v>
+        <v>1.000253944133511</v>
       </c>
       <c r="L33">
-        <v>0.001276713928125536</v>
+        <v>0.001372369855072267</v>
       </c>
       <c r="M33">
-        <v>0.5093749999999999</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B34" t="b">
         <v>1</v>
@@ -2444,21 +2465,21 @@
         <v>5</v>
       </c>
       <c r="J34">
-        <v>0.5263881635527594</v>
+        <v>0.5308208765483126</v>
       </c>
       <c r="K34">
-        <v>1.006243464857576</v>
+        <v>1.000253944133511</v>
       </c>
       <c r="L34">
-        <v>0.001264886707377812</v>
+        <v>0.001372369855072267</v>
       </c>
       <c r="M34">
-        <v>0.4989583333333334</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B35" t="b">
         <v>1</v>
@@ -2485,21 +2506,21 @@
         <v>5</v>
       </c>
       <c r="J35">
-        <v>0.521893468605622</v>
+        <v>0.5251559719258638</v>
       </c>
       <c r="K35">
-        <v>1.027714449942352</v>
+        <v>1.020060384914307</v>
       </c>
       <c r="L35">
-        <v>0.001259061582846745</v>
+        <v>0.001334290050121707</v>
       </c>
       <c r="M35">
-        <v>0.5291666666666666</v>
+        <v>0.528125</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B36" t="b">
         <v>1</v>
@@ -2526,21 +2547,21 @@
         <v>5</v>
       </c>
       <c r="J36">
-        <v>0.5231460288359887</v>
+        <v>0.5216241131709639</v>
       </c>
       <c r="K36">
-        <v>1.009353167940071</v>
+        <v>1.026452298190757</v>
       </c>
       <c r="L36">
-        <v>0.001243943065068446</v>
+        <v>0.001319505267780912</v>
       </c>
       <c r="M36">
-        <v>0.5083333333333334</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B37" t="b">
         <v>1</v>
@@ -2567,21 +2588,21 @@
         <v>5</v>
       </c>
       <c r="J37">
-        <v>0.5231460288359887</v>
+        <v>0.5216241131709639</v>
       </c>
       <c r="K37">
-        <v>1.009353167940071</v>
+        <v>1.026452298190757</v>
       </c>
       <c r="L37">
-        <v>0.001243943065068446</v>
+        <v>0.001319505267780912</v>
       </c>
       <c r="M37">
-        <v>0.5083333333333334</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B38" t="b">
         <v>1</v>
@@ -2608,24 +2629,24 @@
         <v>5</v>
       </c>
       <c r="J38">
-        <v>0.5249483487374771</v>
+        <v>0.5216241131709639</v>
       </c>
       <c r="K38">
-        <v>1.010656440517342</v>
+        <v>1.026452298190757</v>
       </c>
       <c r="L38">
-        <v>0.00124216905849386</v>
+        <v>0.001319505267780912</v>
       </c>
       <c r="M38">
-        <v>0.5114583333333333</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39" t="b">
         <v>1</v>
@@ -2634,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -2649,24 +2670,24 @@
         <v>5</v>
       </c>
       <c r="J39">
-        <v>0.522159345841977</v>
+        <v>0.5238826719623297</v>
       </c>
       <c r="K39">
-        <v>1.027095400373154</v>
+        <v>1.017844667630376</v>
       </c>
       <c r="L39">
-        <v>0.00121660822769569</v>
+        <v>0.001303997694158954</v>
       </c>
       <c r="M39">
-        <v>0.5104166666666666</v>
+        <v>0.5229166666666666</v>
       </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" t="b">
         <v>1</v>
@@ -2675,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="E40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -2690,24 +2711,24 @@
         <v>5</v>
       </c>
       <c r="J40">
-        <v>0.5226674234384732</v>
+        <v>0.5234221515505412</v>
       </c>
       <c r="K40">
-        <v>1.014128127415725</v>
+        <v>1.028143238415307</v>
       </c>
       <c r="L40">
-        <v>0.001215576789972161</v>
+        <v>0.001276713928125536</v>
       </c>
       <c r="M40">
-        <v>0.503125</v>
+        <v>0.5093749999999999</v>
       </c>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" t="b">
         <v>1</v>
@@ -2716,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="E41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -2731,21 +2752,21 @@
         <v>5</v>
       </c>
       <c r="J41">
-        <v>0.5260315812750413</v>
+        <v>0.5263881635527594</v>
       </c>
       <c r="K41">
-        <v>1.009804187894823</v>
+        <v>1.006243464857576</v>
       </c>
       <c r="L41">
-        <v>0.001202429194092052</v>
+        <v>0.001264886707377812</v>
       </c>
       <c r="M41">
-        <v>0.5104166666666666</v>
+        <v>0.4989583333333334</v>
       </c>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B42" t="b">
         <v>1</v>
@@ -2772,21 +2793,21 @@
         <v>5</v>
       </c>
       <c r="J42">
-        <v>0.5200581185195348</v>
+        <v>0.521893468605622</v>
       </c>
       <c r="K42">
-        <v>1.026535582123912</v>
+        <v>1.027714449942352</v>
       </c>
       <c r="L42">
-        <v>0.001196634438047529</v>
+        <v>0.001259061582846745</v>
       </c>
       <c r="M42">
-        <v>0.5093749999999999</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B43" t="b">
         <v>1</v>
@@ -2813,21 +2834,21 @@
         <v>5</v>
       </c>
       <c r="J43">
-        <v>0.5258940840179638</v>
+        <v>0.521893468605622</v>
       </c>
       <c r="K43">
-        <v>1.001816433427225</v>
+        <v>1.027714449942352</v>
       </c>
       <c r="L43">
-        <v>0.001162966443983608</v>
+        <v>0.001259061582846745</v>
       </c>
       <c r="M43">
-        <v>0.4916666666666666</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B44" t="b">
         <v>1</v>
@@ -2854,21 +2875,21 @@
         <v>5</v>
       </c>
       <c r="J44">
-        <v>0.524655572745732</v>
+        <v>0.5231460288359887</v>
       </c>
       <c r="K44">
-        <v>1.002637461423354</v>
+        <v>1.009353167940071</v>
       </c>
       <c r="L44">
-        <v>0.001151836852341137</v>
+        <v>0.001243943065068446</v>
       </c>
       <c r="M44">
-        <v>0.5229166666666667</v>
+        <v>0.5083333333333334</v>
       </c>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B45" t="b">
         <v>1</v>
@@ -2895,21 +2916,21 @@
         <v>5</v>
       </c>
       <c r="J45">
-        <v>0.5256317306448246</v>
+        <v>0.5231460288359887</v>
       </c>
       <c r="K45">
-        <v>1.002163500574073</v>
+        <v>1.009353167940071</v>
       </c>
       <c r="L45">
-        <v>0.001151259103950406</v>
+        <v>0.001243943065068446</v>
       </c>
       <c r="M45">
-        <v>0.4875</v>
+        <v>0.5083333333333334</v>
       </c>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B46" t="b">
         <v>1</v>
@@ -2936,24 +2957,24 @@
         <v>5</v>
       </c>
       <c r="J46">
-        <v>0.5228375928727048</v>
+        <v>0.5249483487374771</v>
       </c>
       <c r="K46">
-        <v>1.008298428009464</v>
+        <v>1.010656440517342</v>
       </c>
       <c r="L46">
-        <v>0.001139488068136794</v>
+        <v>0.00124216905849386</v>
       </c>
       <c r="M46">
-        <v>0.5010416666666666</v>
+        <v>0.5114583333333333</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" t="b">
         <v>1</v>
@@ -2962,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="E47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
@@ -2977,21 +2998,21 @@
         <v>5</v>
       </c>
       <c r="J47">
-        <v>0.5228615176958756</v>
+        <v>0.522159345841977</v>
       </c>
       <c r="K47">
-        <v>1.002184552355568</v>
+        <v>1.027095400373154</v>
       </c>
       <c r="L47">
-        <v>0.001082863470171871</v>
+        <v>0.00121660822769569</v>
       </c>
       <c r="M47">
-        <v>0.5291666666666667</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B48" t="b">
         <v>1</v>
@@ -3018,21 +3039,21 @@
         <v>5</v>
       </c>
       <c r="J48">
-        <v>0.5228615176958756</v>
+        <v>0.5226674234384732</v>
       </c>
       <c r="K48">
-        <v>1.002184552355568</v>
+        <v>1.014128127415725</v>
       </c>
       <c r="L48">
-        <v>0.001082863470171871</v>
+        <v>0.001215576789972161</v>
       </c>
       <c r="M48">
-        <v>0.5291666666666667</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="49" spans="1:13">
       <c r="A49" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B49" t="b">
         <v>0</v>
@@ -3059,21 +3080,21 @@
         <v>5</v>
       </c>
       <c r="J49">
-        <v>0.5219101933037861</v>
+        <v>0.5260315812750413</v>
       </c>
       <c r="K49">
-        <v>1.015749889031079</v>
+        <v>1.009804187894823</v>
       </c>
       <c r="L49">
-        <v>0.001079857661840396</v>
+        <v>0.001202429194092052</v>
       </c>
       <c r="M49">
-        <v>0.5114583333333333</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="50" spans="1:13">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B50" t="b">
         <v>1</v>
@@ -3100,21 +3121,21 @@
         <v>5</v>
       </c>
       <c r="J50">
-        <v>0.520077373627629</v>
+        <v>0.5200581185195348</v>
       </c>
       <c r="K50">
-        <v>1.011812570525803</v>
+        <v>1.026535582123912</v>
       </c>
       <c r="L50">
-        <v>0.001075050382056652</v>
+        <v>0.001196634438047529</v>
       </c>
       <c r="M50">
-        <v>0.4958333333333334</v>
+        <v>0.5093749999999999</v>
       </c>
     </row>
     <row r="51" spans="1:13">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B51" t="b">
         <v>1</v>
@@ -3141,21 +3162,21 @@
         <v>5</v>
       </c>
       <c r="J51">
-        <v>0.5227987952432545</v>
+        <v>0.5232962473974613</v>
       </c>
       <c r="K51">
-        <v>1.002607237162842</v>
+        <v>1.011492190079051</v>
       </c>
       <c r="L51">
-        <v>0.001066854191525292</v>
+        <v>0.001195441772637978</v>
       </c>
       <c r="M51">
-        <v>0.4895833333333333</v>
+        <v>0.515625</v>
       </c>
     </row>
     <row r="52" spans="1:13">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B52" t="b">
         <v>1</v>
@@ -3182,21 +3203,21 @@
         <v>5</v>
       </c>
       <c r="J52">
-        <v>0.5223663648849615</v>
+        <v>0.5258940840179638</v>
       </c>
       <c r="K52">
-        <v>1.004747790219797</v>
+        <v>1.001816433427225</v>
       </c>
       <c r="L52">
-        <v>0.001043793413646326</v>
+        <v>0.001162966443983608</v>
       </c>
       <c r="M52">
-        <v>0.4895833333333334</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="53" spans="1:13">
       <c r="A53" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B53" t="b">
         <v>1</v>
@@ -3208,13 +3229,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="b">
         <v>1</v>
       </c>
       <c r="G53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -3223,21 +3244,21 @@
         <v>5</v>
       </c>
       <c r="J53">
-        <v>0.527514585400898</v>
+        <v>0.524655572745732</v>
       </c>
       <c r="K53">
-        <v>0.9886289855139003</v>
+        <v>1.002637461423354</v>
       </c>
       <c r="L53">
-        <v>0.001036979183638451</v>
+        <v>0.001151836852341137</v>
       </c>
       <c r="M53">
-        <v>0.5020833333333333</v>
+        <v>0.5229166666666667</v>
       </c>
     </row>
     <row r="54" spans="1:13">
       <c r="A54" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B54" t="b">
         <v>1</v>
@@ -3264,21 +3285,21 @@
         <v>5</v>
       </c>
       <c r="J54">
-        <v>0.5210202991663655</v>
+        <v>0.5256317306448246</v>
       </c>
       <c r="K54">
-        <v>1.001911636949535</v>
+        <v>1.002163500574073</v>
       </c>
       <c r="L54">
-        <v>0.0009670606235489155</v>
+        <v>0.001151259103950406</v>
       </c>
       <c r="M54">
-        <v>0.4916666666666667</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="55" spans="1:13">
       <c r="A55" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B55" t="b">
         <v>1</v>
@@ -3290,13 +3311,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" t="b">
         <v>1</v>
       </c>
       <c r="G55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -3305,21 +3326,21 @@
         <v>5</v>
       </c>
       <c r="J55">
-        <v>0.5226367348010115</v>
+        <v>0.5228375928727048</v>
       </c>
       <c r="K55">
-        <v>0.9968312997802476</v>
+        <v>1.008298428009464</v>
       </c>
       <c r="L55">
-        <v>0.000946024797853361</v>
+        <v>0.001139488068136794</v>
       </c>
       <c r="M55">
-        <v>0.4989583333333333</v>
+        <v>0.5010416666666666</v>
       </c>
     </row>
     <row r="56" spans="1:13">
       <c r="A56" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B56" t="b">
         <v>1</v>
@@ -3331,10 +3352,10 @@
         <v>0</v>
       </c>
       <c r="E56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="b">
         <v>1</v>
@@ -3346,21 +3367,21 @@
         <v>5</v>
       </c>
       <c r="J56">
-        <v>0.5141933088762702</v>
+        <v>0.5228615176958756</v>
       </c>
       <c r="K56">
-        <v>1.011327388809842</v>
+        <v>1.002184552355568</v>
       </c>
       <c r="L56">
-        <v>0.0007170640647862186</v>
+        <v>0.001082863470171871</v>
       </c>
       <c r="M56">
-        <v>0.478125</v>
+        <v>0.5291666666666667</v>
       </c>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B57" t="b">
         <v>1</v>
@@ -3378,33 +3399,33 @@
         <v>1</v>
       </c>
       <c r="G57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
       </c>
       <c r="I57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J57">
-        <v>0.5297794240863934</v>
+        <v>0.5228615176958756</v>
       </c>
       <c r="K57">
-        <v>0.9992569709596522</v>
+        <v>1.002184552355568</v>
       </c>
       <c r="L57">
-        <v>0.001307563203828672</v>
+        <v>0.001082863470171871</v>
       </c>
       <c r="M57">
-        <v>0.5083333333333333</v>
+        <v>0.5291666666666667</v>
       </c>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58" t="b">
         <v>1</v>
@@ -3413,10 +3434,10 @@
         <v>0</v>
       </c>
       <c r="E58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" t="b">
         <v>1</v>
@@ -3425,24 +3446,24 @@
         <v>1</v>
       </c>
       <c r="I58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J58">
-        <v>0.5180089528533888</v>
+        <v>0.5219101933037861</v>
       </c>
       <c r="K58">
-        <v>1.041562849821317</v>
+        <v>1.015749889031079</v>
       </c>
       <c r="L58">
-        <v>0.001301924747221952</v>
+        <v>0.001079857661840396</v>
       </c>
       <c r="M58">
-        <v>0.4958333333333333</v>
+        <v>0.5114583333333333</v>
       </c>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B59" t="b">
         <v>1</v>
@@ -3460,30 +3481,30 @@
         <v>1</v>
       </c>
       <c r="G59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
       </c>
       <c r="I59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J59">
-        <v>0.5309007241877264</v>
+        <v>0.520077373627629</v>
       </c>
       <c r="K59">
-        <v>0.98320207730054</v>
+        <v>1.011812570525803</v>
       </c>
       <c r="L59">
-        <v>0.001282222240572423</v>
+        <v>0.001075050382056652</v>
       </c>
       <c r="M59">
-        <v>0.5291666666666666</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B60" t="b">
         <v>1</v>
@@ -3501,30 +3522,30 @@
         <v>1</v>
       </c>
       <c r="G60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
       </c>
       <c r="I60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J60">
-        <v>0.528752194335537</v>
+        <v>0.5227987952432545</v>
       </c>
       <c r="K60">
-        <v>0.9991795766085996</v>
+        <v>1.002607237162842</v>
       </c>
       <c r="L60">
-        <v>0.00128056290185265</v>
+        <v>0.001066854191525292</v>
       </c>
       <c r="M60">
-        <v>0.5104166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B61" t="b">
         <v>1</v>
@@ -3539,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="F61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" t="b">
         <v>1</v>
@@ -3548,24 +3569,24 @@
         <v>1</v>
       </c>
       <c r="I61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J61">
-        <v>0.5187764494588618</v>
+        <v>0.5223663648849615</v>
       </c>
       <c r="K61">
-        <v>1.03395159028982</v>
+        <v>1.004747790219797</v>
       </c>
       <c r="L61">
-        <v>0.001242852088977111</v>
+        <v>0.001043793413646326</v>
       </c>
       <c r="M61">
-        <v>0.4989583333333334</v>
+        <v>0.4895833333333334</v>
       </c>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B62" t="b">
         <v>1</v>
@@ -3577,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
@@ -3589,24 +3610,24 @@
         <v>1</v>
       </c>
       <c r="I62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J62">
-        <v>0.5310624704935629</v>
+        <v>0.527514585400898</v>
       </c>
       <c r="K62">
-        <v>0.9882403204263138</v>
+        <v>0.9886289855139003</v>
       </c>
       <c r="L62">
-        <v>0.001239383675525021</v>
+        <v>0.001036979183638451</v>
       </c>
       <c r="M62">
-        <v>0.5135416666666666</v>
+        <v>0.5020833333333333</v>
       </c>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B63" t="b">
         <v>1</v>
@@ -3624,30 +3645,30 @@
         <v>1</v>
       </c>
       <c r="G63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
       </c>
       <c r="I63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J63">
-        <v>0.5301408803901906</v>
+        <v>0.5204511208433463</v>
       </c>
       <c r="K63">
-        <v>0.9878601455294825</v>
+        <v>1.011316915004425</v>
       </c>
       <c r="L63">
-        <v>0.001237346060837505</v>
+        <v>0.001036425097066138</v>
       </c>
       <c r="M63">
-        <v>0.4958333333333334</v>
+        <v>0.4958333333333333</v>
       </c>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B64" t="b">
         <v>1</v>
@@ -3665,30 +3686,30 @@
         <v>1</v>
       </c>
       <c r="G64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
       </c>
       <c r="I64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J64">
-        <v>0.5298900468986411</v>
+        <v>0.5210202991663655</v>
       </c>
       <c r="K64">
-        <v>0.9874770938479198</v>
+        <v>1.001911636949535</v>
       </c>
       <c r="L64">
-        <v>0.001221744762890552</v>
+        <v>0.0009670606235489155</v>
       </c>
       <c r="M64">
-        <v>0.5270833333333332</v>
+        <v>0.4916666666666667</v>
       </c>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B65" t="b">
         <v>1</v>
@@ -3700,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="b">
         <v>1</v>
@@ -3712,24 +3733,24 @@
         <v>1</v>
       </c>
       <c r="I65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J65">
-        <v>0.5302924432950098</v>
+        <v>0.5226367348010115</v>
       </c>
       <c r="K65">
-        <v>0.9886236977737551</v>
+        <v>0.9968312997802476</v>
       </c>
       <c r="L65">
-        <v>0.001210795016161763</v>
+        <v>0.000946024797853361</v>
       </c>
       <c r="M65">
-        <v>0.4927083333333333</v>
+        <v>0.4989583333333333</v>
       </c>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B66" t="b">
         <v>1</v>
@@ -3741,36 +3762,36 @@
         <v>0</v>
       </c>
       <c r="E66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
       </c>
       <c r="I66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J66">
-        <v>0.5298646885654992</v>
+        <v>0.5141933088762702</v>
       </c>
       <c r="K66">
-        <v>0.9800301579482247</v>
+        <v>1.011327388809842</v>
       </c>
       <c r="L66">
-        <v>0.001190977069276271</v>
+        <v>0.0007170640647862186</v>
       </c>
       <c r="M66">
-        <v>0.525</v>
+        <v>0.478125</v>
       </c>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B67" t="b">
         <v>1</v>
@@ -3797,21 +3818,21 @@
         <v>4</v>
       </c>
       <c r="J67">
-        <v>0.5297614744002548</v>
+        <v>0.5297794240863934</v>
       </c>
       <c r="K67">
-        <v>0.9877552616172895</v>
+        <v>0.9992569709596522</v>
       </c>
       <c r="L67">
-        <v>0.001166671573407331</v>
+        <v>0.001307563203828672</v>
       </c>
       <c r="M67">
-        <v>0.4927083333333333</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B68" t="b">
         <v>1</v>
@@ -3826,10 +3847,10 @@
         <v>0</v>
       </c>
       <c r="F68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -3838,21 +3859,21 @@
         <v>4</v>
       </c>
       <c r="J68">
-        <v>0.5297614744002548</v>
+        <v>0.5180089528533888</v>
       </c>
       <c r="K68">
-        <v>0.9877552616172895</v>
+        <v>1.041562849821317</v>
       </c>
       <c r="L68">
-        <v>0.001166671573407331</v>
+        <v>0.001301924747221952</v>
       </c>
       <c r="M68">
-        <v>0.4927083333333333</v>
+        <v>0.4958333333333333</v>
       </c>
     </row>
     <row r="69" spans="1:13">
       <c r="A69" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B69" t="b">
         <v>1</v>
@@ -3879,21 +3900,21 @@
         <v>4</v>
       </c>
       <c r="J69">
-        <v>0.5305573766766467</v>
+        <v>0.5309007241877264</v>
       </c>
       <c r="K69">
-        <v>0.9840564190268319</v>
+        <v>0.98320207730054</v>
       </c>
       <c r="L69">
-        <v>0.001164259924771176</v>
+        <v>0.001282222240572423</v>
       </c>
       <c r="M69">
-        <v>0.503125</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="70" spans="1:13">
       <c r="A70" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B70" t="b">
         <v>1</v>
@@ -3920,21 +3941,21 @@
         <v>4</v>
       </c>
       <c r="J70">
-        <v>0.5261420933400818</v>
+        <v>0.528752194335537</v>
       </c>
       <c r="K70">
-        <v>0.9934596756918352</v>
+        <v>0.9991795766085996</v>
       </c>
       <c r="L70">
-        <v>0.001161341879976893</v>
+        <v>0.00128056290185265</v>
       </c>
       <c r="M70">
-        <v>0.5</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="71" spans="1:13">
       <c r="A71" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B71" t="b">
         <v>1</v>
@@ -3949,10 +3970,10 @@
         <v>0</v>
       </c>
       <c r="F71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3961,21 +3982,21 @@
         <v>4</v>
       </c>
       <c r="J71">
-        <v>0.5299681187461873</v>
+        <v>0.5187764494588618</v>
       </c>
       <c r="K71">
-        <v>0.987638298990986</v>
+        <v>1.03395159028982</v>
       </c>
       <c r="L71">
-        <v>0.001161122643328618</v>
+        <v>0.001242852088977111</v>
       </c>
       <c r="M71">
-        <v>0.515625</v>
+        <v>0.4989583333333334</v>
       </c>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B72" t="b">
         <v>1</v>
@@ -4002,21 +4023,21 @@
         <v>4</v>
       </c>
       <c r="J72">
-        <v>0.5300091490614294</v>
+        <v>0.5310624704935629</v>
       </c>
       <c r="K72">
-        <v>0.9864760233095164</v>
+        <v>0.9882403204263138</v>
       </c>
       <c r="L72">
-        <v>0.001155256583239874</v>
+        <v>0.001239383675525021</v>
       </c>
       <c r="M72">
-        <v>0.5083333333333333</v>
+        <v>0.5135416666666666</v>
       </c>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B73" t="b">
         <v>1</v>
@@ -4043,21 +4064,21 @@
         <v>4</v>
       </c>
       <c r="J73">
-        <v>0.5299945357090986</v>
+        <v>0.5301408803901906</v>
       </c>
       <c r="K73">
-        <v>0.9870895708199896</v>
+        <v>0.9878601455294825</v>
       </c>
       <c r="L73">
-        <v>0.001153385064684222</v>
+        <v>0.001237346060837505</v>
       </c>
       <c r="M73">
-        <v>0.5041666666666667</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B74" t="b">
         <v>1</v>
@@ -4084,21 +4105,21 @@
         <v>4</v>
       </c>
       <c r="J74">
-        <v>0.5289773698207376</v>
+        <v>0.5298900468986411</v>
       </c>
       <c r="K74">
-        <v>0.9899196064597657</v>
+        <v>0.9874770938479198</v>
       </c>
       <c r="L74">
-        <v>0.001146005813496268</v>
+        <v>0.001221744762890552</v>
       </c>
       <c r="M74">
-        <v>0.4958333333333334</v>
+        <v>0.5270833333333332</v>
       </c>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B75" t="b">
         <v>1</v>
@@ -4125,21 +4146,21 @@
         <v>4</v>
       </c>
       <c r="J75">
-        <v>0.5299945357090986</v>
+        <v>0.5302924432950098</v>
       </c>
       <c r="K75">
-        <v>0.9851213528232992</v>
+        <v>0.9886236977737551</v>
       </c>
       <c r="L75">
-        <v>0.001132179485130683</v>
+        <v>0.001210795016161763</v>
       </c>
       <c r="M75">
-        <v>0.5</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="76" spans="1:13">
       <c r="A76" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B76" t="b">
         <v>1</v>
@@ -4166,21 +4187,21 @@
         <v>4</v>
       </c>
       <c r="J76">
-        <v>0.5299945357090986</v>
+        <v>0.5298646885654992</v>
       </c>
       <c r="K76">
-        <v>0.9851213528232992</v>
+        <v>0.9800301579482247</v>
       </c>
       <c r="L76">
-        <v>0.001132179485130683</v>
+        <v>0.001190977069276271</v>
       </c>
       <c r="M76">
-        <v>0.5</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="77" spans="1:13">
       <c r="A77" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B77" t="b">
         <v>1</v>
@@ -4195,10 +4216,10 @@
         <v>0</v>
       </c>
       <c r="F77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -4207,21 +4228,21 @@
         <v>4</v>
       </c>
       <c r="J77">
-        <v>0.5187720260724553</v>
+        <v>0.5297614744002548</v>
       </c>
       <c r="K77">
-        <v>1.023100726460465</v>
+        <v>0.9877552616172895</v>
       </c>
       <c r="L77">
-        <v>0.001128765158089612</v>
+        <v>0.001166671573407331</v>
       </c>
       <c r="M77">
-        <v>0.5072916666666666</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="78" spans="1:13">
       <c r="A78" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B78" t="b">
         <v>1</v>
@@ -4248,21 +4269,21 @@
         <v>4</v>
       </c>
       <c r="J78">
-        <v>0.5279886380261246</v>
+        <v>0.5297614744002548</v>
       </c>
       <c r="K78">
-        <v>0.9863885354070231</v>
+        <v>0.9877552616172895</v>
       </c>
       <c r="L78">
-        <v>0.001125560215956009</v>
+        <v>0.001166671573407331</v>
       </c>
       <c r="M78">
-        <v>0.5</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="79" spans="1:13">
       <c r="A79" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B79" t="b">
         <v>1</v>
@@ -4289,21 +4310,21 @@
         <v>4</v>
       </c>
       <c r="J79">
-        <v>0.5299871858568221</v>
+        <v>0.5305573766766467</v>
       </c>
       <c r="K79">
-        <v>0.9817049863412703</v>
+        <v>0.9840564190268319</v>
       </c>
       <c r="L79">
-        <v>0.001114893125026547</v>
+        <v>0.001164259924771176</v>
       </c>
       <c r="M79">
-        <v>0.496875</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B80" t="b">
         <v>1</v>
@@ -4330,21 +4351,21 @@
         <v>4</v>
       </c>
       <c r="J80">
-        <v>0.5252216575980102</v>
+        <v>0.5261420933400818</v>
       </c>
       <c r="K80">
-        <v>0.9937885590472615</v>
+        <v>0.9934596756918352</v>
       </c>
       <c r="L80">
-        <v>0.001107535642556418</v>
+        <v>0.001161341879976893</v>
       </c>
       <c r="M80">
-        <v>0.5260416666666667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="81" spans="1:13">
       <c r="A81" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B81" t="b">
         <v>1</v>
@@ -4371,21 +4392,21 @@
         <v>4</v>
       </c>
       <c r="J81">
-        <v>0.5252216575980102</v>
+        <v>0.5299681187461873</v>
       </c>
       <c r="K81">
-        <v>0.9937885590472615</v>
+        <v>0.987638298990986</v>
       </c>
       <c r="L81">
-        <v>0.001107535642556418</v>
+        <v>0.001161122643328618</v>
       </c>
       <c r="M81">
-        <v>0.5260416666666667</v>
+        <v>0.515625</v>
       </c>
     </row>
     <row r="82" spans="1:13">
       <c r="A82" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B82" t="b">
         <v>1</v>
@@ -4412,21 +4433,21 @@
         <v>4</v>
       </c>
       <c r="J82">
-        <v>0.5285021628342103</v>
+        <v>0.5300091490614294</v>
       </c>
       <c r="K82">
-        <v>0.9811206519954586</v>
+        <v>0.9864760233095164</v>
       </c>
       <c r="L82">
-        <v>0.001101098853941202</v>
+        <v>0.001155256583239874</v>
       </c>
       <c r="M82">
-        <v>0.5177083333333333</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="83" spans="1:13">
       <c r="A83" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B83" t="b">
         <v>1</v>
@@ -4453,21 +4474,21 @@
         <v>4</v>
       </c>
       <c r="J83">
-        <v>0.5287521910530835</v>
+        <v>0.5299945357090986</v>
       </c>
       <c r="K83">
-        <v>0.9858575796857367</v>
+        <v>0.9870895708199896</v>
       </c>
       <c r="L83">
-        <v>0.001100223629074958</v>
+        <v>0.001153385064684222</v>
       </c>
       <c r="M83">
-        <v>0.4895833333333333</v>
+        <v>0.5041666666666667</v>
       </c>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B84" t="b">
         <v>1</v>
@@ -4494,21 +4515,21 @@
         <v>4</v>
       </c>
       <c r="J84">
-        <v>0.5312836291778413</v>
+        <v>0.5289773698207376</v>
       </c>
       <c r="K84">
-        <v>0.9759026158426718</v>
+        <v>0.9899196064597657</v>
       </c>
       <c r="L84">
-        <v>0.001096069908270593</v>
+        <v>0.001146005813496268</v>
       </c>
       <c r="M84">
-        <v>0.5239583333333334</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B85" t="b">
         <v>1</v>
@@ -4535,21 +4556,21 @@
         <v>4</v>
       </c>
       <c r="J85">
-        <v>0.5271656171084507</v>
+        <v>0.5299945357090986</v>
       </c>
       <c r="K85">
-        <v>0.9922124507665936</v>
+        <v>0.9851213528232992</v>
       </c>
       <c r="L85">
-        <v>0.001084732067899307</v>
+        <v>0.001132179485130683</v>
       </c>
       <c r="M85">
-        <v>0.5135416666666666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="86" spans="1:13">
       <c r="A86" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B86" t="b">
         <v>1</v>
@@ -4576,21 +4597,21 @@
         <v>4</v>
       </c>
       <c r="J86">
-        <v>0.5271656171084507</v>
+        <v>0.5299945357090986</v>
       </c>
       <c r="K86">
-        <v>0.9922124507665936</v>
+        <v>0.9851213528232992</v>
       </c>
       <c r="L86">
-        <v>0.001084732067899307</v>
+        <v>0.001132179485130683</v>
       </c>
       <c r="M86">
-        <v>0.5135416666666666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87" spans="1:13">
       <c r="A87" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B87" t="b">
         <v>1</v>
@@ -4605,10 +4626,10 @@
         <v>0</v>
       </c>
       <c r="F87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -4617,21 +4638,21 @@
         <v>4</v>
       </c>
       <c r="J87">
-        <v>0.5297429893939507</v>
+        <v>0.5187720260724553</v>
       </c>
       <c r="K87">
-        <v>0.9794416097577223</v>
+        <v>1.023100726460465</v>
       </c>
       <c r="L87">
-        <v>0.001079057281849006</v>
+        <v>0.001128765158089612</v>
       </c>
       <c r="M87">
-        <v>0.4916666666666666</v>
+        <v>0.5072916666666666</v>
       </c>
     </row>
     <row r="88" spans="1:13">
       <c r="A88" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B88" t="b">
         <v>1</v>
@@ -4658,21 +4679,21 @@
         <v>4</v>
       </c>
       <c r="J88">
-        <v>0.5305301544410591</v>
+        <v>0.5279886380261246</v>
       </c>
       <c r="K88">
-        <v>0.9765922457580878</v>
+        <v>0.9863885354070231</v>
       </c>
       <c r="L88">
-        <v>0.001076160358732811</v>
+        <v>0.001125560215956009</v>
       </c>
       <c r="M88">
-        <v>0.4802083333333334</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89" spans="1:13">
       <c r="A89" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B89" t="b">
         <v>1</v>
@@ -4699,21 +4720,21 @@
         <v>4</v>
       </c>
       <c r="J89">
-        <v>0.5292156597886641</v>
+        <v>0.5299871858568221</v>
       </c>
       <c r="K89">
-        <v>0.9816946023028489</v>
+        <v>0.9817049863412703</v>
       </c>
       <c r="L89">
-        <v>0.001071865777100514</v>
+        <v>0.001114893125026547</v>
       </c>
       <c r="M89">
-        <v>0.5010416666666667</v>
+        <v>0.496875</v>
       </c>
     </row>
     <row r="90" spans="1:13">
       <c r="A90" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B90" t="b">
         <v>1</v>
@@ -4740,21 +4761,21 @@
         <v>4</v>
       </c>
       <c r="J90">
-        <v>0.52287605302681</v>
+        <v>0.5252216575980102</v>
       </c>
       <c r="K90">
-        <v>0.9968171231740112</v>
+        <v>0.9937885590472615</v>
       </c>
       <c r="L90">
-        <v>0.001067638130736437</v>
+        <v>0.001107535642556418</v>
       </c>
       <c r="M90">
-        <v>0.4947916666666667</v>
+        <v>0.5260416666666667</v>
       </c>
     </row>
     <row r="91" spans="1:13">
       <c r="A91" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B91" t="b">
         <v>1</v>
@@ -4781,21 +4802,21 @@
         <v>4</v>
       </c>
       <c r="J91">
-        <v>0.52287605302681</v>
+        <v>0.5252216575980102</v>
       </c>
       <c r="K91">
-        <v>0.9968171231740112</v>
+        <v>0.9937885590472615</v>
       </c>
       <c r="L91">
-        <v>0.001067638130736437</v>
+        <v>0.001107535642556418</v>
       </c>
       <c r="M91">
-        <v>0.4947916666666667</v>
+        <v>0.5260416666666667</v>
       </c>
     </row>
     <row r="92" spans="1:13">
       <c r="A92" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B92" t="b">
         <v>1</v>
@@ -4810,10 +4831,10 @@
         <v>0</v>
       </c>
       <c r="F92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -4822,21 +4843,21 @@
         <v>4</v>
       </c>
       <c r="J92">
-        <v>0.5159131963663766</v>
+        <v>0.5285021628342103</v>
       </c>
       <c r="K92">
-        <v>1.027777338427553</v>
+        <v>0.9811206519954586</v>
       </c>
       <c r="L92">
-        <v>0.001055275344201965</v>
+        <v>0.001101098853941202</v>
       </c>
       <c r="M92">
-        <v>0.5</v>
+        <v>0.5177083333333333</v>
       </c>
     </row>
     <row r="93" spans="1:13">
       <c r="A93" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B93" t="b">
         <v>1</v>
@@ -4863,21 +4884,21 @@
         <v>4</v>
       </c>
       <c r="J93">
-        <v>0.5246341870651349</v>
+        <v>0.5287521910530835</v>
       </c>
       <c r="K93">
-        <v>0.9933552089965371</v>
+        <v>0.9858575796857367</v>
       </c>
       <c r="L93">
-        <v>0.001054245750250405</v>
+        <v>0.001100223629074958</v>
       </c>
       <c r="M93">
-        <v>0.4979166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B94" t="b">
         <v>1</v>
@@ -4892,10 +4913,10 @@
         <v>0</v>
       </c>
       <c r="F94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -4904,21 +4925,21 @@
         <v>4</v>
       </c>
       <c r="J94">
-        <v>0.5170010232288733</v>
+        <v>0.5312836291778413</v>
       </c>
       <c r="K94">
-        <v>1.022997286102976</v>
+        <v>0.9759026158426718</v>
       </c>
       <c r="L94">
-        <v>0.001053298029116546</v>
+        <v>0.001096069908270593</v>
       </c>
       <c r="M94">
-        <v>0.4885416666666667</v>
+        <v>0.5239583333333334</v>
       </c>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B95" t="b">
         <v>1</v>
@@ -4945,21 +4966,21 @@
         <v>4</v>
       </c>
       <c r="J95">
-        <v>0.5228396342785835</v>
+        <v>0.5271656171084507</v>
       </c>
       <c r="K95">
-        <v>0.99748696362744</v>
+        <v>0.9922124507665936</v>
       </c>
       <c r="L95">
-        <v>0.001043839590745026</v>
+        <v>0.001084732067899307</v>
       </c>
       <c r="M95">
-        <v>0.5302083333333334</v>
+        <v>0.5135416666666666</v>
       </c>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B96" t="b">
         <v>1</v>
@@ -4974,10 +4995,10 @@
         <v>0</v>
       </c>
       <c r="F96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -4986,13 +5007,13 @@
         <v>4</v>
       </c>
       <c r="J96">
-        <v>0.5198233483025548</v>
+        <v>0.5271656171084507</v>
       </c>
       <c r="K96">
-        <v>1.009627166146061</v>
+        <v>0.9922124507665936</v>
       </c>
       <c r="L96">
-        <v>0.001038352380259842</v>
+        <v>0.001084732067899307</v>
       </c>
       <c r="M96">
         <v>0.5135416666666666</v>
@@ -5000,7 +5021,7 @@
     </row>
     <row r="97" spans="1:13">
       <c r="A97" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B97" t="b">
         <v>1</v>
@@ -5027,21 +5048,21 @@
         <v>4</v>
       </c>
       <c r="J97">
-        <v>0.5261395622789501</v>
+        <v>0.5297429893939507</v>
       </c>
       <c r="K97">
-        <v>0.987120827973565</v>
+        <v>0.9794416097577223</v>
       </c>
       <c r="L97">
-        <v>0.001036717914388316</v>
+        <v>0.001079057281849006</v>
       </c>
       <c r="M97">
-        <v>0.503125</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="98" spans="1:13">
       <c r="A98" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B98" t="b">
         <v>1</v>
@@ -5068,21 +5089,21 @@
         <v>4</v>
       </c>
       <c r="J98">
-        <v>0.5246825672326535</v>
+        <v>0.5305301544410591</v>
       </c>
       <c r="K98">
-        <v>0.9899336413597283</v>
+        <v>0.9765922457580878</v>
       </c>
       <c r="L98">
-        <v>0.001031896350464572</v>
+        <v>0.001076160358732811</v>
       </c>
       <c r="M98">
-        <v>0.5177083333333334</v>
+        <v>0.4802083333333334</v>
       </c>
     </row>
     <row r="99" spans="1:13">
       <c r="A99" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B99" t="b">
         <v>1</v>
@@ -5097,10 +5118,10 @@
         <v>0</v>
       </c>
       <c r="F99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -5109,21 +5130,21 @@
         <v>4</v>
       </c>
       <c r="J99">
-        <v>0.5199567813865503</v>
+        <v>0.5292156597886641</v>
       </c>
       <c r="K99">
-        <v>1.010282267275608</v>
+        <v>0.9816946023028489</v>
       </c>
       <c r="L99">
-        <v>0.001028322580159319</v>
+        <v>0.001071865777100514</v>
       </c>
       <c r="M99">
-        <v>0.5166666666666666</v>
+        <v>0.5010416666666667</v>
       </c>
     </row>
     <row r="100" spans="1:13">
       <c r="A100" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B100" t="b">
         <v>1</v>
@@ -5150,21 +5171,21 @@
         <v>4</v>
       </c>
       <c r="J100">
-        <v>0.5244010028997976</v>
+        <v>0.52287605302681</v>
       </c>
       <c r="K100">
-        <v>0.9970077646516021</v>
+        <v>0.9968171231740112</v>
       </c>
       <c r="L100">
-        <v>0.001027690327630743</v>
+        <v>0.001067638130736437</v>
       </c>
       <c r="M100">
-        <v>0.5104166666666667</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B101" t="b">
         <v>1</v>
@@ -5191,21 +5212,21 @@
         <v>4</v>
       </c>
       <c r="J101">
-        <v>0.523916283783208</v>
+        <v>0.52287605302681</v>
       </c>
       <c r="K101">
-        <v>0.9946731028692912</v>
+        <v>0.9968171231740112</v>
       </c>
       <c r="L101">
-        <v>0.001026066271995282</v>
+        <v>0.001067638130736437</v>
       </c>
       <c r="M101">
-        <v>0.5062500000000001</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B102" t="b">
         <v>1</v>
@@ -5220,10 +5241,10 @@
         <v>0</v>
       </c>
       <c r="F102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -5232,21 +5253,21 @@
         <v>4</v>
       </c>
       <c r="J102">
-        <v>0.522355113006814</v>
+        <v>0.5159131963663766</v>
       </c>
       <c r="K102">
-        <v>0.9936869675553917</v>
+        <v>1.027777338427553</v>
       </c>
       <c r="L102">
-        <v>0.001002242431500013</v>
+        <v>0.001055275344201965</v>
       </c>
       <c r="M102">
-        <v>0.4958333333333334</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B103" t="b">
         <v>1</v>
@@ -5261,10 +5282,10 @@
         <v>0</v>
       </c>
       <c r="F103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -5273,21 +5294,21 @@
         <v>4</v>
       </c>
       <c r="J103">
-        <v>0.5259653904714776</v>
+        <v>0.5159131963663766</v>
       </c>
       <c r="K103">
-        <v>0.9891514214954089</v>
+        <v>1.027777338427553</v>
       </c>
       <c r="L103">
-        <v>0.0009948985919904208</v>
+        <v>0.001055275344201965</v>
       </c>
       <c r="M103">
-        <v>0.4916666666666667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="104" spans="1:13">
       <c r="A104" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B104" t="b">
         <v>1</v>
@@ -5314,21 +5335,21 @@
         <v>4</v>
       </c>
       <c r="J104">
-        <v>0.5235644946037826</v>
+        <v>0.5246341870651349</v>
       </c>
       <c r="K104">
-        <v>0.9953679791124828</v>
+        <v>0.9933552089965371</v>
       </c>
       <c r="L104">
-        <v>0.000991361018590764</v>
+        <v>0.001054245750250405</v>
       </c>
       <c r="M104">
-        <v>0.4989583333333333</v>
+        <v>0.4979166666666666</v>
       </c>
     </row>
     <row r="105" spans="1:13">
       <c r="A105" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B105" t="b">
         <v>1</v>
@@ -5343,10 +5364,10 @@
         <v>0</v>
       </c>
       <c r="F105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="b">
         <v>1</v>
@@ -5355,21 +5376,21 @@
         <v>4</v>
       </c>
       <c r="J105">
-        <v>0.5233399600176396</v>
+        <v>0.5170010232288733</v>
       </c>
       <c r="K105">
-        <v>0.9959555301333897</v>
+        <v>1.022997286102976</v>
       </c>
       <c r="L105">
-        <v>0.0009801996462472072</v>
+        <v>0.001053298029116546</v>
       </c>
       <c r="M105">
-        <v>0.4833333333333333</v>
+        <v>0.4885416666666667</v>
       </c>
     </row>
     <row r="106" spans="1:13">
       <c r="A106" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B106" t="b">
         <v>1</v>
@@ -5396,21 +5417,21 @@
         <v>4</v>
       </c>
       <c r="J106">
-        <v>0.526154705505792</v>
+        <v>0.5228396342785835</v>
       </c>
       <c r="K106">
-        <v>0.9859074382220105</v>
+        <v>0.99748696362744</v>
       </c>
       <c r="L106">
-        <v>0.000979316235546076</v>
+        <v>0.001043839590745026</v>
       </c>
       <c r="M106">
-        <v>0.4958333333333333</v>
+        <v>0.5302083333333334</v>
       </c>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B107" t="b">
         <v>1</v>
@@ -5425,10 +5446,10 @@
         <v>0</v>
       </c>
       <c r="F107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" t="b">
         <v>1</v>
@@ -5437,21 +5458,21 @@
         <v>4</v>
       </c>
       <c r="J107">
-        <v>0.5225638971214088</v>
+        <v>0.5198233483025548</v>
       </c>
       <c r="K107">
-        <v>0.9999364983848775</v>
+        <v>1.009627166146061</v>
       </c>
       <c r="L107">
-        <v>0.0009656001050053646</v>
+        <v>0.001038352380259842</v>
       </c>
       <c r="M107">
-        <v>0.4739583333333333</v>
+        <v>0.5135416666666666</v>
       </c>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B108" t="b">
         <v>1</v>
@@ -5478,21 +5499,21 @@
         <v>4</v>
       </c>
       <c r="J108">
-        <v>0.5225638971214088</v>
+        <v>0.5261395622789501</v>
       </c>
       <c r="K108">
-        <v>0.9999364983848775</v>
+        <v>0.987120827973565</v>
       </c>
       <c r="L108">
-        <v>0.0009656001050053646</v>
+        <v>0.001036717914388316</v>
       </c>
       <c r="M108">
-        <v>0.4739583333333333</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B109" t="b">
         <v>1</v>
@@ -5519,21 +5540,21 @@
         <v>4</v>
       </c>
       <c r="J109">
-        <v>0.5238534260309985</v>
+        <v>0.5246825672326535</v>
       </c>
       <c r="K109">
-        <v>0.9942561248924289</v>
+        <v>0.9899336413597283</v>
       </c>
       <c r="L109">
-        <v>0.0009604932304826307</v>
+        <v>0.001031896350464572</v>
       </c>
       <c r="M109">
-        <v>0.5</v>
+        <v>0.5177083333333334</v>
       </c>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B110" t="b">
         <v>1</v>
@@ -5560,21 +5581,21 @@
         <v>4</v>
       </c>
       <c r="J110">
-        <v>0.5188515595754628</v>
+        <v>0.5199567813865503</v>
       </c>
       <c r="K110">
-        <v>1.008562178897924</v>
+        <v>1.010282267275608</v>
       </c>
       <c r="L110">
-        <v>0.0009520328796691887</v>
+        <v>0.001028322580159319</v>
       </c>
       <c r="M110">
-        <v>0.4854166666666667</v>
+        <v>0.5166666666666666</v>
       </c>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B111" t="b">
         <v>1</v>
@@ -5589,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="F111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" t="b">
         <v>1</v>
@@ -5601,21 +5622,21 @@
         <v>4</v>
       </c>
       <c r="J111">
-        <v>0.5172507722990763</v>
+        <v>0.5244010028997976</v>
       </c>
       <c r="K111">
-        <v>1.015785899206139</v>
+        <v>0.9970077646516021</v>
       </c>
       <c r="L111">
-        <v>0.0009492433028610605</v>
+        <v>0.001027690327630743</v>
       </c>
       <c r="M111">
-        <v>0.5062500000000001</v>
+        <v>0.5104166666666667</v>
       </c>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B112" t="b">
         <v>1</v>
@@ -5630,10 +5651,10 @@
         <v>0</v>
       </c>
       <c r="F112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" t="b">
         <v>1</v>
@@ -5642,21 +5663,21 @@
         <v>4</v>
       </c>
       <c r="J112">
-        <v>0.5177680301790935</v>
+        <v>0.523916283783208</v>
       </c>
       <c r="K112">
-        <v>1.009515013151155</v>
+        <v>0.9946731028692912</v>
       </c>
       <c r="L112">
-        <v>0.0009410096840942867</v>
+        <v>0.001026066271995282</v>
       </c>
       <c r="M112">
-        <v>0.4895833333333333</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B113" t="b">
         <v>1</v>
@@ -5671,10 +5692,10 @@
         <v>0</v>
       </c>
       <c r="F113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H113" t="b">
         <v>1</v>
@@ -5683,21 +5704,21 @@
         <v>4</v>
       </c>
       <c r="J113">
-        <v>0.5189974583803525</v>
+        <v>0.522355113006814</v>
       </c>
       <c r="K113">
-        <v>1.007972053216962</v>
+        <v>0.9936869675553917</v>
       </c>
       <c r="L113">
-        <v>0.0009409135695633095</v>
+        <v>0.001002242431500013</v>
       </c>
       <c r="M113">
-        <v>0.4822916666666667</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B114" t="b">
         <v>1</v>
@@ -5724,21 +5745,21 @@
         <v>4</v>
       </c>
       <c r="J114">
-        <v>0.5249073982095501</v>
+        <v>0.5259653904714776</v>
       </c>
       <c r="K114">
-        <v>0.9862169522338707</v>
+        <v>0.9891514214954089</v>
       </c>
       <c r="L114">
-        <v>0.0009383310523807906</v>
+        <v>0.0009948985919904208</v>
       </c>
       <c r="M114">
-        <v>0.4895833333333333</v>
+        <v>0.4916666666666667</v>
       </c>
     </row>
     <row r="115" spans="1:13">
       <c r="A115" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B115" t="b">
         <v>1</v>
@@ -5765,21 +5786,21 @@
         <v>4</v>
       </c>
       <c r="J115">
-        <v>0.5231282804602735</v>
+        <v>0.5235644946037826</v>
       </c>
       <c r="K115">
-        <v>0.9962419906552764</v>
+        <v>0.9953679791124828</v>
       </c>
       <c r="L115">
-        <v>0.0009369151322903755</v>
+        <v>0.000991361018590764</v>
       </c>
       <c r="M115">
-        <v>0.4885416666666666</v>
+        <v>0.4989583333333333</v>
       </c>
     </row>
     <row r="116" spans="1:13">
       <c r="A116" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B116" t="b">
         <v>1</v>
@@ -5806,21 +5827,21 @@
         <v>4</v>
       </c>
       <c r="J116">
-        <v>0.5293189696854399</v>
+        <v>0.5233399600176396</v>
       </c>
       <c r="K116">
-        <v>0.9654242585485517</v>
+        <v>0.9959555301333897</v>
       </c>
       <c r="L116">
-        <v>0.0009325216570301813</v>
+        <v>0.0009801996462472072</v>
       </c>
       <c r="M116">
-        <v>0.5062500000000001</v>
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="117" spans="1:13">
       <c r="A117" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B117" t="b">
         <v>1</v>
@@ -5847,21 +5868,21 @@
         <v>4</v>
       </c>
       <c r="J117">
-        <v>0.5293189696854399</v>
+        <v>0.526154705505792</v>
       </c>
       <c r="K117">
-        <v>0.9654242585485517</v>
+        <v>0.9859074382220105</v>
       </c>
       <c r="L117">
-        <v>0.0009325216570301813</v>
+        <v>0.000979316235546076</v>
       </c>
       <c r="M117">
-        <v>0.5062500000000001</v>
+        <v>0.4958333333333333</v>
       </c>
     </row>
     <row r="118" spans="1:13">
       <c r="A118" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B118" t="b">
         <v>1</v>
@@ -5888,21 +5909,21 @@
         <v>4</v>
       </c>
       <c r="J118">
-        <v>0.5269465413826945</v>
+        <v>0.5225638971214088</v>
       </c>
       <c r="K118">
-        <v>0.9783492880611059</v>
+        <v>0.9999364983848775</v>
       </c>
       <c r="L118">
-        <v>0.000931924219960699</v>
+        <v>0.0009656001050053646</v>
       </c>
       <c r="M118">
-        <v>0.4947916666666667</v>
+        <v>0.4739583333333333</v>
       </c>
     </row>
     <row r="119" spans="1:13">
       <c r="A119" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B119" t="b">
         <v>1</v>
@@ -5929,21 +5950,21 @@
         <v>4</v>
       </c>
       <c r="J119">
-        <v>0.5246592404580296</v>
+        <v>0.5225638971214088</v>
       </c>
       <c r="K119">
-        <v>0.9824557156715376</v>
+        <v>0.9999364983848775</v>
       </c>
       <c r="L119">
-        <v>0.0009277746994077157</v>
+        <v>0.0009656001050053646</v>
       </c>
       <c r="M119">
-        <v>0.5114583333333333</v>
+        <v>0.4739583333333333</v>
       </c>
     </row>
     <row r="120" spans="1:13">
       <c r="A120" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B120" t="b">
         <v>1</v>
@@ -5970,21 +5991,21 @@
         <v>4</v>
       </c>
       <c r="J120">
-        <v>0.5253889182765066</v>
+        <v>0.5238534260309985</v>
       </c>
       <c r="K120">
-        <v>0.9848697180583652</v>
+        <v>0.9942561248924289</v>
       </c>
       <c r="L120">
-        <v>0.0009266772938245408</v>
+        <v>0.0009604932304826307</v>
       </c>
       <c r="M120">
-        <v>0.4979166666666666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="121" spans="1:13">
       <c r="A121" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B121" t="b">
         <v>1</v>
@@ -5999,10 +6020,10 @@
         <v>0</v>
       </c>
       <c r="F121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121" t="b">
         <v>1</v>
@@ -6011,21 +6032,21 @@
         <v>4</v>
       </c>
       <c r="J121">
-        <v>0.5234914679981804</v>
+        <v>0.5188515595754628</v>
       </c>
       <c r="K121">
-        <v>0.9893793081695874</v>
+        <v>1.008562178897924</v>
       </c>
       <c r="L121">
-        <v>0.0009213500798947411</v>
+        <v>0.0009520328796691887</v>
       </c>
       <c r="M121">
-        <v>0.50625</v>
+        <v>0.4854166666666667</v>
       </c>
     </row>
     <row r="122" spans="1:13">
       <c r="A122" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B122" t="b">
         <v>1</v>
@@ -6040,10 +6061,10 @@
         <v>0</v>
       </c>
       <c r="F122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122" t="b">
         <v>1</v>
@@ -6052,21 +6073,21 @@
         <v>4</v>
       </c>
       <c r="J122">
-        <v>0.5256410910630306</v>
+        <v>0.5172507722990763</v>
       </c>
       <c r="K122">
-        <v>0.9784272247931242</v>
+        <v>1.015785899206139</v>
       </c>
       <c r="L122">
-        <v>0.0009176727701198046</v>
+        <v>0.0009492433028610605</v>
       </c>
       <c r="M122">
-        <v>0.515625</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="123" spans="1:13">
       <c r="A123" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B123" t="b">
         <v>1</v>
@@ -6081,10 +6102,10 @@
         <v>0</v>
       </c>
       <c r="F123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" t="b">
         <v>1</v>
@@ -6093,21 +6114,21 @@
         <v>4</v>
       </c>
       <c r="J123">
-        <v>0.5224132350376474</v>
+        <v>0.5177680301790935</v>
       </c>
       <c r="K123">
-        <v>0.9867362306782189</v>
+        <v>1.009515013151155</v>
       </c>
       <c r="L123">
-        <v>0.0009084242373368683</v>
+        <v>0.0009410096840942867</v>
       </c>
       <c r="M123">
-        <v>0.4885416666666666</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B124" t="b">
         <v>1</v>
@@ -6122,10 +6143,10 @@
         <v>0</v>
       </c>
       <c r="F124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124" t="b">
         <v>1</v>
@@ -6134,21 +6155,21 @@
         <v>4</v>
       </c>
       <c r="J124">
-        <v>0.5207299119032052</v>
+        <v>0.5189974583803525</v>
       </c>
       <c r="K124">
-        <v>0.9967952743879801</v>
+        <v>1.007972053216962</v>
       </c>
       <c r="L124">
-        <v>0.0009024498082932968</v>
+        <v>0.0009409135695633095</v>
       </c>
       <c r="M124">
-        <v>0.49375</v>
+        <v>0.4822916666666667</v>
       </c>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B125" t="b">
         <v>1</v>
@@ -6163,10 +6184,10 @@
         <v>0</v>
       </c>
       <c r="F125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H125" t="b">
         <v>1</v>
@@ -6175,21 +6196,21 @@
         <v>4</v>
       </c>
       <c r="J125">
-        <v>0.5192039639610935</v>
+        <v>0.5249073982095501</v>
       </c>
       <c r="K125">
-        <v>1.000817869341217</v>
+        <v>0.9862169522338707</v>
       </c>
       <c r="L125">
-        <v>0.000898343208344344</v>
+        <v>0.0009383310523807906</v>
       </c>
       <c r="M125">
-        <v>0.490625</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="126" spans="1:13">
       <c r="A126" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B126" t="b">
         <v>1</v>
@@ -6216,21 +6237,21 @@
         <v>4</v>
       </c>
       <c r="J126">
-        <v>0.5254208893632846</v>
+        <v>0.5231282804602735</v>
       </c>
       <c r="K126">
-        <v>0.9782536939503818</v>
+        <v>0.9962419906552764</v>
       </c>
       <c r="L126">
-        <v>0.0008972434375681095</v>
+        <v>0.0009369151322903755</v>
       </c>
       <c r="M126">
-        <v>0.503125</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="127" spans="1:13">
       <c r="A127" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B127" t="b">
         <v>1</v>
@@ -6257,21 +6278,21 @@
         <v>4</v>
       </c>
       <c r="J127">
-        <v>0.5215411276937636</v>
+        <v>0.5293189696854399</v>
       </c>
       <c r="K127">
-        <v>0.9942193869711776</v>
+        <v>0.9654242585485517</v>
       </c>
       <c r="L127">
-        <v>0.0008798636999232372</v>
+        <v>0.0009325216570301813</v>
       </c>
       <c r="M127">
-        <v>0.50625</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="128" spans="1:13">
       <c r="A128" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B128" t="b">
         <v>1</v>
@@ -6298,21 +6319,21 @@
         <v>4</v>
       </c>
       <c r="J128">
-        <v>0.5238693996708922</v>
+        <v>0.5293189696854399</v>
       </c>
       <c r="K128">
-        <v>0.9843049189916957</v>
+        <v>0.9654242585485517</v>
       </c>
       <c r="L128">
-        <v>0.0008674740552542172</v>
+        <v>0.0009325216570301813</v>
       </c>
       <c r="M128">
-        <v>0.484375</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="129" spans="1:13">
       <c r="A129" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B129" t="b">
         <v>1</v>
@@ -6339,21 +6360,21 @@
         <v>4</v>
       </c>
       <c r="J129">
-        <v>0.5238693996708922</v>
+        <v>0.5269465413826945</v>
       </c>
       <c r="K129">
-        <v>0.9843049189916957</v>
+        <v>0.9783492880611059</v>
       </c>
       <c r="L129">
-        <v>0.0008674740552542172</v>
+        <v>0.000931924219960699</v>
       </c>
       <c r="M129">
-        <v>0.484375</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="130" spans="1:13">
       <c r="A130" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B130" t="b">
         <v>1</v>
@@ -6380,21 +6401,21 @@
         <v>4</v>
       </c>
       <c r="J130">
-        <v>0.5218331875794566</v>
+        <v>0.5246592404580296</v>
       </c>
       <c r="K130">
-        <v>0.9929833864621642</v>
+        <v>0.9824557156715376</v>
       </c>
       <c r="L130">
-        <v>0.0008651781455750667</v>
+        <v>0.0009277746994077157</v>
       </c>
       <c r="M130">
-        <v>0.503125</v>
+        <v>0.5114583333333333</v>
       </c>
     </row>
     <row r="131" spans="1:13">
       <c r="A131" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B131" t="b">
         <v>1</v>
@@ -6421,21 +6442,21 @@
         <v>4</v>
       </c>
       <c r="J131">
-        <v>0.5274630733092988</v>
+        <v>0.5253889182765066</v>
       </c>
       <c r="K131">
-        <v>0.9696571152813476</v>
+        <v>0.9848697180583652</v>
       </c>
       <c r="L131">
-        <v>0.0008620868051855673</v>
+        <v>0.0009266772938245408</v>
       </c>
       <c r="M131">
-        <v>0.4927083333333334</v>
+        <v>0.4979166666666666</v>
       </c>
     </row>
     <row r="132" spans="1:13">
       <c r="A132" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B132" t="b">
         <v>1</v>
@@ -6462,21 +6483,21 @@
         <v>4</v>
       </c>
       <c r="J132">
-        <v>0.5241495285091906</v>
+        <v>0.5234914679981804</v>
       </c>
       <c r="K132">
-        <v>0.9801983954631733</v>
+        <v>0.9893793081695874</v>
       </c>
       <c r="L132">
-        <v>0.0008360238668380898</v>
+        <v>0.0009213500798947411</v>
       </c>
       <c r="M132">
-        <v>0.5</v>
+        <v>0.50625</v>
       </c>
     </row>
     <row r="133" spans="1:13">
       <c r="A133" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B133" t="b">
         <v>1</v>
@@ -6491,10 +6512,10 @@
         <v>0</v>
       </c>
       <c r="F133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133" t="b">
         <v>1</v>
@@ -6503,21 +6524,21 @@
         <v>4</v>
       </c>
       <c r="J133">
-        <v>0.5113220775110638</v>
+        <v>0.5256410910630306</v>
       </c>
       <c r="K133">
-        <v>1.027849471350162</v>
+        <v>0.9784272247931242</v>
       </c>
       <c r="L133">
-        <v>0.000796172723851922</v>
+        <v>0.0009176727701198046</v>
       </c>
       <c r="M133">
-        <v>0.4802083333333333</v>
+        <v>0.515625</v>
       </c>
     </row>
     <row r="134" spans="1:13">
       <c r="A134" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B134" t="b">
         <v>1</v>
@@ -6532,10 +6553,10 @@
         <v>0</v>
       </c>
       <c r="F134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H134" t="b">
         <v>1</v>
@@ -6544,21 +6565,21 @@
         <v>4</v>
       </c>
       <c r="J134">
-        <v>0.5162156348666548</v>
+        <v>0.5224132350376474</v>
       </c>
       <c r="K134">
-        <v>1.005944008142189</v>
+        <v>0.9867362306782189</v>
       </c>
       <c r="L134">
-        <v>0.0007905088693574015</v>
+        <v>0.0009084242373368683</v>
       </c>
       <c r="M134">
-        <v>0.46875</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="135" spans="1:13">
       <c r="A135" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B135" t="b">
         <v>1</v>
@@ -6573,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="F135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H135" t="b">
         <v>1</v>
@@ -6585,21 +6606,21 @@
         <v>4</v>
       </c>
       <c r="J135">
-        <v>0.5154390182889224</v>
+        <v>0.5207299119032052</v>
       </c>
       <c r="K135">
-        <v>1.006876671767273</v>
+        <v>0.9967952743879801</v>
       </c>
       <c r="L135">
-        <v>0.0007851455361724275</v>
+        <v>0.0009024498082932968</v>
       </c>
       <c r="M135">
-        <v>0.4979166666666666</v>
+        <v>0.49375</v>
       </c>
     </row>
     <row r="136" spans="1:13">
       <c r="A136" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B136" t="b">
         <v>1</v>
@@ -6626,21 +6647,21 @@
         <v>4</v>
       </c>
       <c r="J136">
-        <v>0.5161649229993595</v>
+        <v>0.5192039639610935</v>
       </c>
       <c r="K136">
-        <v>1.005701276064777</v>
+        <v>1.000817869341217</v>
       </c>
       <c r="L136">
-        <v>0.000748251739419787</v>
+        <v>0.000898343208344344</v>
       </c>
       <c r="M136">
-        <v>0.484375</v>
+        <v>0.490625</v>
       </c>
     </row>
     <row r="137" spans="1:13">
       <c r="A137" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B137" t="b">
         <v>1</v>
@@ -6655,10 +6676,10 @@
         <v>0</v>
       </c>
       <c r="F137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H137" t="b">
         <v>1</v>
@@ -6667,21 +6688,21 @@
         <v>4</v>
       </c>
       <c r="J137">
-        <v>0.516377346220273</v>
+        <v>0.5254208893632846</v>
       </c>
       <c r="K137">
-        <v>1.000074514129528</v>
+        <v>0.9782536939503818</v>
       </c>
       <c r="L137">
-        <v>0.0007365939605200051</v>
+        <v>0.0008972434375681095</v>
       </c>
       <c r="M137">
-        <v>0.4895833333333334</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="138" spans="1:13">
       <c r="A138" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B138" t="b">
         <v>1</v>
@@ -6696,10 +6717,10 @@
         <v>0</v>
       </c>
       <c r="F138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H138" t="b">
         <v>1</v>
@@ -6708,21 +6729,21 @@
         <v>4</v>
       </c>
       <c r="J138">
-        <v>0.516377346220273</v>
+        <v>0.5215411276937636</v>
       </c>
       <c r="K138">
-        <v>1.000074514129528</v>
+        <v>0.9942193869711776</v>
       </c>
       <c r="L138">
-        <v>0.0007365939605200051</v>
+        <v>0.0008798636999232372</v>
       </c>
       <c r="M138">
-        <v>0.4895833333333334</v>
+        <v>0.50625</v>
       </c>
     </row>
     <row r="139" spans="1:13">
       <c r="A139" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B139" t="b">
         <v>1</v>
@@ -6749,21 +6770,21 @@
         <v>4</v>
       </c>
       <c r="J139">
-        <v>0.5252819226799594</v>
+        <v>0.5238693996708922</v>
       </c>
       <c r="K139">
-        <v>0.9657840052244776</v>
+        <v>0.9843049189916957</v>
       </c>
       <c r="L139">
-        <v>0.0007327282295901741</v>
+        <v>0.0008674740552542172</v>
       </c>
       <c r="M139">
-        <v>0.4833333333333334</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="140" spans="1:13">
       <c r="A140" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B140" t="b">
         <v>1</v>
@@ -6790,21 +6811,21 @@
         <v>4</v>
       </c>
       <c r="J140">
-        <v>0.5203266322127637</v>
+        <v>0.5238693996708922</v>
       </c>
       <c r="K140">
-        <v>0.9801483289053664</v>
+        <v>0.9843049189916957</v>
       </c>
       <c r="L140">
-        <v>0.0007320675175348148</v>
+        <v>0.0008674740552542172</v>
       </c>
       <c r="M140">
-        <v>0.4791666666666667</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="141" spans="1:13">
       <c r="A141" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B141" t="b">
         <v>1</v>
@@ -6819,10 +6840,10 @@
         <v>0</v>
       </c>
       <c r="F141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" t="b">
         <v>1</v>
@@ -6831,21 +6852,21 @@
         <v>4</v>
       </c>
       <c r="J141">
-        <v>0.5139602475674263</v>
+        <v>0.5218331875794566</v>
       </c>
       <c r="K141">
-        <v>1.00959239495847</v>
+        <v>0.9929833864621642</v>
       </c>
       <c r="L141">
-        <v>0.0007282484964984896</v>
+        <v>0.0008651781455750667</v>
       </c>
       <c r="M141">
-        <v>0.4947916666666666</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="142" spans="1:13">
       <c r="A142" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B142" t="b">
         <v>1</v>
@@ -6872,21 +6893,21 @@
         <v>4</v>
       </c>
       <c r="J142">
-        <v>0.522859606143931</v>
+        <v>0.5274630733092988</v>
       </c>
       <c r="K142">
-        <v>0.9718821072685966</v>
+        <v>0.9696571152813476</v>
       </c>
       <c r="L142">
-        <v>0.0006937009876564704</v>
+        <v>0.0008620868051855673</v>
       </c>
       <c r="M142">
-        <v>0.4989583333333333</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="143" spans="1:13">
       <c r="A143" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B143" t="b">
         <v>1</v>
@@ -6913,21 +6934,21 @@
         <v>4</v>
       </c>
       <c r="J143">
-        <v>0.5233927526094866</v>
+        <v>0.5241495285091906</v>
       </c>
       <c r="K143">
-        <v>0.9673644431560058</v>
+        <v>0.9801983954631733</v>
       </c>
       <c r="L143">
-        <v>0.0006894083531337102</v>
+        <v>0.0008360238668380898</v>
       </c>
       <c r="M143">
-        <v>0.4864583333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144" spans="1:13">
       <c r="A144" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B144" t="b">
         <v>1</v>
@@ -6942,10 +6963,10 @@
         <v>0</v>
       </c>
       <c r="F144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" t="b">
         <v>1</v>
@@ -6954,21 +6975,21 @@
         <v>4</v>
       </c>
       <c r="J144">
-        <v>0.5223632219988027</v>
+        <v>0.5113220775110638</v>
       </c>
       <c r="K144">
-        <v>0.9731092189198931</v>
+        <v>1.027849471350162</v>
       </c>
       <c r="L144">
-        <v>0.0006852428700327241</v>
+        <v>0.000796172723851922</v>
       </c>
       <c r="M144">
-        <v>0.4770833333333333</v>
+        <v>0.4802083333333333</v>
       </c>
     </row>
     <row r="145" spans="1:13">
       <c r="A145" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B145" t="b">
         <v>1</v>
@@ -6995,21 +7016,21 @@
         <v>4</v>
       </c>
       <c r="J145">
-        <v>0.5141420199530164</v>
+        <v>0.5162156348666548</v>
       </c>
       <c r="K145">
-        <v>1.003862045984636</v>
+        <v>1.005944008142189</v>
       </c>
       <c r="L145">
-        <v>0.0006611235074699496</v>
+        <v>0.0007905088693574015</v>
       </c>
       <c r="M145">
-        <v>0.4802083333333333</v>
+        <v>0.46875</v>
       </c>
     </row>
     <row r="146" spans="1:13">
       <c r="A146" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B146" t="b">
         <v>1</v>
@@ -7024,10 +7045,10 @@
         <v>0</v>
       </c>
       <c r="F146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" t="b">
         <v>1</v>
@@ -7036,21 +7057,21 @@
         <v>4</v>
       </c>
       <c r="J146">
-        <v>0.5216807441949667</v>
+        <v>0.5154390182889224</v>
       </c>
       <c r="K146">
-        <v>0.9732889917800195</v>
+        <v>1.006876671767273</v>
       </c>
       <c r="L146">
-        <v>0.0006411740977063922</v>
+        <v>0.0007851455361724275</v>
       </c>
       <c r="M146">
-        <v>0.4854166666666666</v>
+        <v>0.4979166666666666</v>
       </c>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B147" t="b">
         <v>1</v>
@@ -7065,10 +7086,10 @@
         <v>0</v>
       </c>
       <c r="F147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147" t="b">
         <v>1</v>
@@ -7077,21 +7098,21 @@
         <v>4</v>
       </c>
       <c r="J147">
-        <v>0.5232255188372845</v>
+        <v>0.5107527446617868</v>
       </c>
       <c r="K147">
-        <v>0.9637010066522516</v>
+        <v>1.020142389319354</v>
       </c>
       <c r="L147">
-        <v>0.000636913294165422</v>
+        <v>0.0007512563231564298</v>
       </c>
       <c r="M147">
-        <v>0.5260416666666667</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="148" spans="1:13">
       <c r="A148" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B148" t="b">
         <v>1</v>
@@ -7106,10 +7127,10 @@
         <v>0</v>
       </c>
       <c r="F148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148" t="b">
         <v>1</v>
@@ -7118,21 +7139,21 @@
         <v>4</v>
       </c>
       <c r="J148">
-        <v>0.52550765664565</v>
+        <v>0.5161649229993595</v>
       </c>
       <c r="K148">
-        <v>0.9524489433246164</v>
+        <v>1.005701276064777</v>
       </c>
       <c r="L148">
-        <v>0.0006077689722168509</v>
+        <v>0.000748251739419787</v>
       </c>
       <c r="M148">
-        <v>0.5020833333333333</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="149" spans="1:13">
       <c r="A149" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B149" t="b">
         <v>1</v>
@@ -7159,21 +7180,21 @@
         <v>4</v>
       </c>
       <c r="J149">
-        <v>0.511293232251511</v>
+        <v>0.516377346220273</v>
       </c>
       <c r="K149">
-        <v>1.007836680557942</v>
+        <v>1.000074514129528</v>
       </c>
       <c r="L149">
-        <v>0.0006001944671426257</v>
+        <v>0.0007365939605200051</v>
       </c>
       <c r="M149">
-        <v>0.4791666666666666</v>
+        <v>0.4895833333333334</v>
       </c>
     </row>
     <row r="150" spans="1:13">
       <c r="A150" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B150" t="b">
         <v>1</v>
@@ -7188,10 +7209,10 @@
         <v>0</v>
       </c>
       <c r="F150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150" t="b">
         <v>1</v>
@@ -7200,21 +7221,21 @@
         <v>4</v>
       </c>
       <c r="J150">
-        <v>0.5210619340950617</v>
+        <v>0.516377346220273</v>
       </c>
       <c r="K150">
-        <v>0.9690889545169888</v>
+        <v>1.000074514129528</v>
       </c>
       <c r="L150">
-        <v>0.0005962227094571275</v>
+        <v>0.0007365939605200051</v>
       </c>
       <c r="M150">
-        <v>0.4927083333333333</v>
+        <v>0.4895833333333334</v>
       </c>
     </row>
     <row r="151" spans="1:13">
       <c r="A151" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B151" t="b">
         <v>1</v>
@@ -7226,10 +7247,10 @@
         <v>0</v>
       </c>
       <c r="E151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G151" t="b">
         <v>0</v>
@@ -7241,21 +7262,21 @@
         <v>4</v>
       </c>
       <c r="J151">
-        <v>0.5159984944998335</v>
+        <v>0.5252819226799594</v>
       </c>
       <c r="K151">
-        <v>0.9915305620267537</v>
+        <v>0.9657840052244776</v>
       </c>
       <c r="L151">
-        <v>0.0005917391459450919</v>
+        <v>0.0007327282295901741</v>
       </c>
       <c r="M151">
-        <v>0.4947916666666666</v>
+        <v>0.4833333333333334</v>
       </c>
     </row>
     <row r="152" spans="1:13">
       <c r="A152" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B152" t="b">
         <v>1</v>
@@ -7282,21 +7303,21 @@
         <v>4</v>
       </c>
       <c r="J152">
-        <v>0.5247363008648167</v>
+        <v>0.5203266322127637</v>
       </c>
       <c r="K152">
-        <v>0.9537950398630312</v>
+        <v>0.9801483289053664</v>
       </c>
       <c r="L152">
-        <v>0.0005713886925227532</v>
+        <v>0.0007320675175348148</v>
       </c>
       <c r="M152">
-        <v>0.4979166666666667</v>
+        <v>0.4791666666666667</v>
       </c>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B153" t="b">
         <v>1</v>
@@ -7323,21 +7344,21 @@
         <v>4</v>
       </c>
       <c r="J153">
-        <v>0.5105493256251157</v>
+        <v>0.5139602475674263</v>
       </c>
       <c r="K153">
-        <v>1.006912348456769</v>
+        <v>1.00959239495847</v>
       </c>
       <c r="L153">
-        <v>0.0005616190870091131</v>
+        <v>0.0007282484964984896</v>
       </c>
       <c r="M153">
-        <v>0.5104166666666666</v>
+        <v>0.4947916666666666</v>
       </c>
     </row>
     <row r="154" spans="1:13">
       <c r="A154" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B154" t="b">
         <v>1</v>
@@ -7352,10 +7373,10 @@
         <v>0</v>
       </c>
       <c r="F154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154" t="b">
         <v>1</v>
@@ -7364,21 +7385,21 @@
         <v>4</v>
       </c>
       <c r="J154">
-        <v>0.5254300272643465</v>
+        <v>0.5092803338048851</v>
       </c>
       <c r="K154">
-        <v>0.9503543930871714</v>
+        <v>1.025236577326679</v>
       </c>
       <c r="L154">
-        <v>0.0005535438497237457</v>
+        <v>0.0007229622527524834</v>
       </c>
       <c r="M154">
-        <v>0.503125</v>
+        <v>0.4895833333333334</v>
       </c>
     </row>
     <row r="155" spans="1:13">
       <c r="A155" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B155" t="b">
         <v>1</v>
@@ -7393,10 +7414,10 @@
         <v>0</v>
       </c>
       <c r="F155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H155" t="b">
         <v>1</v>
@@ -7405,24 +7426,24 @@
         <v>4</v>
       </c>
       <c r="J155">
-        <v>0.5100546569530306</v>
+        <v>0.522859606143931</v>
       </c>
       <c r="K155">
-        <v>1.003087107953841</v>
+        <v>0.9718821072685966</v>
       </c>
       <c r="L155">
-        <v>0.0004587586230065534</v>
+        <v>0.0006937009876564704</v>
       </c>
       <c r="M155">
-        <v>0.4770833333333333</v>
+        <v>0.4989583333333333</v>
       </c>
     </row>
     <row r="156" spans="1:13">
       <c r="A156" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C156" t="b">
         <v>1</v>
@@ -7443,27 +7464,27 @@
         <v>1</v>
       </c>
       <c r="I156">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J156">
-        <v>0.5244042977164801</v>
+        <v>0.5233927526094866</v>
       </c>
       <c r="K156">
-        <v>0.9885842874963859</v>
+        <v>0.9673644431560058</v>
       </c>
       <c r="L156">
-        <v>0.001066159236814448</v>
+        <v>0.0006894083531337102</v>
       </c>
       <c r="M156">
-        <v>0.5104166666666666</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="157" spans="1:13">
       <c r="A157" t="s">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="B157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C157" t="b">
         <v>1</v>
@@ -7484,27 +7505,27 @@
         <v>1</v>
       </c>
       <c r="I157">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J157">
-        <v>0.5244042977164801</v>
+        <v>0.5223632219988027</v>
       </c>
       <c r="K157">
-        <v>0.9885842874963859</v>
+        <v>0.9731092189198931</v>
       </c>
       <c r="L157">
-        <v>0.001066159236814448</v>
+        <v>0.0006852428700327241</v>
       </c>
       <c r="M157">
-        <v>0.5104166666666666</v>
+        <v>0.4770833333333333</v>
       </c>
     </row>
     <row r="158" spans="1:13">
       <c r="A158" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C158" t="b">
         <v>1</v>
@@ -7516,36 +7537,36 @@
         <v>0</v>
       </c>
       <c r="F158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" t="b">
         <v>1</v>
       </c>
       <c r="I158">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J158">
-        <v>0.5244042977164801</v>
+        <v>0.5141420199530164</v>
       </c>
       <c r="K158">
-        <v>0.9885842874963859</v>
+        <v>1.003862045984636</v>
       </c>
       <c r="L158">
-        <v>0.001066159236814448</v>
+        <v>0.0006611235074699496</v>
       </c>
       <c r="M158">
-        <v>0.5104166666666666</v>
+        <v>0.4802083333333333</v>
       </c>
     </row>
     <row r="159" spans="1:13">
       <c r="A159" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C159" t="b">
         <v>1</v>
@@ -7566,27 +7587,27 @@
         <v>1</v>
       </c>
       <c r="I159">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J159">
-        <v>0.5244042977164801</v>
+        <v>0.5216807441949667</v>
       </c>
       <c r="K159">
-        <v>0.9885842874963859</v>
+        <v>0.9732889917800195</v>
       </c>
       <c r="L159">
-        <v>0.001066159236814448</v>
+        <v>0.0006411740977063922</v>
       </c>
       <c r="M159">
-        <v>0.5104166666666666</v>
+        <v>0.4854166666666666</v>
       </c>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C160" t="b">
         <v>1</v>
@@ -7607,27 +7628,27 @@
         <v>1</v>
       </c>
       <c r="I160">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J160">
-        <v>0.5244042977164801</v>
+        <v>0.5232255188372845</v>
       </c>
       <c r="K160">
-        <v>0.9884511944364173</v>
+        <v>0.9637010066522516</v>
       </c>
       <c r="L160">
-        <v>0.001064362037465958</v>
+        <v>0.000636913294165422</v>
       </c>
       <c r="M160">
-        <v>0.5104166666666666</v>
+        <v>0.5260416666666667</v>
       </c>
     </row>
     <row r="161" spans="1:13">
       <c r="A161" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C161" t="b">
         <v>1</v>
@@ -7648,27 +7669,27 @@
         <v>1</v>
       </c>
       <c r="I161">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J161">
-        <v>0.5244042977164801</v>
+        <v>0.52550765664565</v>
       </c>
       <c r="K161">
-        <v>0.9884511944364173</v>
+        <v>0.9524489433246164</v>
       </c>
       <c r="L161">
-        <v>0.001064362037465958</v>
+        <v>0.0006077689722168509</v>
       </c>
       <c r="M161">
-        <v>0.5104166666666666</v>
+        <v>0.5020833333333333</v>
       </c>
     </row>
     <row r="162" spans="1:13">
       <c r="A162" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C162" t="b">
         <v>1</v>
@@ -7689,27 +7710,27 @@
         <v>1</v>
       </c>
       <c r="I162">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J162">
-        <v>0.5192872108413109</v>
+        <v>0.511293232251511</v>
       </c>
       <c r="K162">
-        <v>1.018973281135655</v>
+        <v>1.007836680557942</v>
       </c>
       <c r="L162">
-        <v>0.001049116939531248</v>
+        <v>0.0006001944671426257</v>
       </c>
       <c r="M162">
-        <v>0.4885416666666666</v>
+        <v>0.4791666666666666</v>
       </c>
     </row>
     <row r="163" spans="1:13">
       <c r="A163" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C163" t="b">
         <v>1</v>
@@ -7730,27 +7751,27 @@
         <v>1</v>
       </c>
       <c r="I163">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J163">
-        <v>0.5231160748800475</v>
+        <v>0.5210619340950617</v>
       </c>
       <c r="K163">
-        <v>0.9922050009974825</v>
+        <v>0.9690889545169888</v>
       </c>
       <c r="L163">
-        <v>0.00104273229376505</v>
+        <v>0.0005962227094571275</v>
       </c>
       <c r="M163">
-        <v>0.5104166666666666</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C164" t="b">
         <v>1</v>
@@ -7759,10 +7780,10 @@
         <v>0</v>
       </c>
       <c r="E164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G164" t="b">
         <v>0</v>
@@ -7771,27 +7792,27 @@
         <v>1</v>
       </c>
       <c r="I164">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J164">
-        <v>0.5275298593470076</v>
+        <v>0.5159984944998335</v>
       </c>
       <c r="K164">
-        <v>0.9813086030036071</v>
+        <v>0.9915305620267537</v>
       </c>
       <c r="L164">
-        <v>0.001028149792052128</v>
+        <v>0.0005917391459450919</v>
       </c>
       <c r="M164">
-        <v>0.53125</v>
+        <v>0.4947916666666666</v>
       </c>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C165" t="b">
         <v>1</v>
@@ -7812,27 +7833,27 @@
         <v>1</v>
       </c>
       <c r="I165">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J165">
-        <v>0.5231359571107191</v>
+        <v>0.5247363008648167</v>
       </c>
       <c r="K165">
-        <v>0.98037097188942</v>
+        <v>0.9537950398630312</v>
       </c>
       <c r="L165">
-        <v>0.000893498047604321</v>
+        <v>0.0005713886925227532</v>
       </c>
       <c r="M165">
-        <v>0.5062500000000001</v>
+        <v>0.4979166666666667</v>
       </c>
     </row>
     <row r="166" spans="1:13">
       <c r="A166" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C166" t="b">
         <v>1</v>
@@ -7844,33 +7865,33 @@
         <v>0</v>
       </c>
       <c r="F166" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166" t="b">
         <v>1</v>
       </c>
       <c r="I166">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J166">
-        <v>0.5233894425353072</v>
+        <v>0.5105493256251157</v>
       </c>
       <c r="K166">
-        <v>0.9793076438534227</v>
+        <v>1.006912348456769</v>
       </c>
       <c r="L166">
-        <v>0.0008921416916242469</v>
+        <v>0.0005616190870091131</v>
       </c>
       <c r="M166">
-        <v>0.5052083333333334</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="167" spans="1:13">
       <c r="A167" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B167" t="b">
         <v>1</v>
@@ -7885,7 +7906,7 @@
         <v>0</v>
       </c>
       <c r="F167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G167" t="b">
         <v>0</v>
@@ -7894,24 +7915,24 @@
         <v>1</v>
       </c>
       <c r="I167">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J167">
-        <v>0.5192338475090287</v>
+        <v>0.5254300272643465</v>
       </c>
       <c r="K167">
-        <v>0.9987041425442801</v>
+        <v>0.9503543930871714</v>
       </c>
       <c r="L167">
-        <v>0.0008845818834857927</v>
+        <v>0.0005535438497237457</v>
       </c>
       <c r="M167">
-        <v>0.5322916666666666</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B168" t="b">
         <v>1</v>
@@ -7929,30 +7950,30 @@
         <v>0</v>
       </c>
       <c r="G168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168" t="b">
         <v>1</v>
       </c>
       <c r="I168">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J168">
-        <v>0.5198672919538527</v>
+        <v>0.5100546569530306</v>
       </c>
       <c r="K168">
-        <v>0.9987315111297436</v>
+        <v>1.003087107953841</v>
       </c>
       <c r="L168">
-        <v>0.0008841936926848471</v>
+        <v>0.0004587586230065534</v>
       </c>
       <c r="M168">
-        <v>0.49375</v>
+        <v>0.4770833333333333</v>
       </c>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B169" t="b">
         <v>0</v>
@@ -7979,21 +8000,21 @@
         <v>3</v>
       </c>
       <c r="J169">
-        <v>0.5200709602353479</v>
+        <v>0.5244042977164801</v>
       </c>
       <c r="K169">
-        <v>0.9905491851146765</v>
+        <v>0.9885842874963859</v>
       </c>
       <c r="L169">
-        <v>0.0008736703711149079</v>
+        <v>0.001066159236814448</v>
       </c>
       <c r="M169">
-        <v>0.5052083333333334</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="170" spans="1:13">
       <c r="A170" t="s">
-        <v>180</v>
+        <v>47</v>
       </c>
       <c r="B170" t="b">
         <v>0</v>
@@ -8020,24 +8041,24 @@
         <v>3</v>
       </c>
       <c r="J170">
-        <v>0.5267930360859814</v>
+        <v>0.5244042977164801</v>
       </c>
       <c r="K170">
-        <v>0.9681505661246683</v>
+        <v>0.9885842874963859</v>
       </c>
       <c r="L170">
-        <v>0.0008664300752523453</v>
+        <v>0.001066159236814448</v>
       </c>
       <c r="M170">
-        <v>0.5125</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="171" spans="1:13">
       <c r="A171" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C171" t="b">
         <v>1</v>
@@ -8049,7 +8070,7 @@
         <v>0</v>
       </c>
       <c r="F171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G171" t="b">
         <v>0</v>
@@ -8061,24 +8082,24 @@
         <v>3</v>
       </c>
       <c r="J171">
-        <v>0.5182197619615945</v>
+        <v>0.5244042977164801</v>
       </c>
       <c r="K171">
-        <v>0.9971492140155174</v>
+        <v>0.9885842874963859</v>
       </c>
       <c r="L171">
-        <v>0.0007830581664438754</v>
+        <v>0.001066159236814448</v>
       </c>
       <c r="M171">
-        <v>0.4885416666666667</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="172" spans="1:13">
       <c r="A172" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C172" t="b">
         <v>1</v>
@@ -8090,7 +8111,7 @@
         <v>0</v>
       </c>
       <c r="F172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G172" t="b">
         <v>0</v>
@@ -8102,21 +8123,21 @@
         <v>3</v>
       </c>
       <c r="J172">
-        <v>0.5180079641635738</v>
+        <v>0.5244042977164801</v>
       </c>
       <c r="K172">
-        <v>0.9930154688490294</v>
+        <v>0.9885842874963859</v>
       </c>
       <c r="L172">
-        <v>0.0007436123378321152</v>
+        <v>0.001066159236814448</v>
       </c>
       <c r="M172">
-        <v>0.5052083333333333</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="173" spans="1:13">
       <c r="A173" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B173" t="b">
         <v>0</v>
@@ -8143,21 +8164,21 @@
         <v>3</v>
       </c>
       <c r="J173">
-        <v>0.5234560622148109</v>
+        <v>0.5244042977164801</v>
       </c>
       <c r="K173">
-        <v>0.9717472102175606</v>
+        <v>0.9884511944364173</v>
       </c>
       <c r="L173">
-        <v>0.00073269489577126</v>
+        <v>0.001064362037465958</v>
       </c>
       <c r="M173">
-        <v>0.4864583333333333</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="174" spans="1:13">
       <c r="A174" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B174" t="b">
         <v>0</v>
@@ -8184,21 +8205,21 @@
         <v>3</v>
       </c>
       <c r="J174">
-        <v>0.5234560622148109</v>
+        <v>0.5244042977164801</v>
       </c>
       <c r="K174">
-        <v>0.971601320550558</v>
+        <v>0.9884511944364173</v>
       </c>
       <c r="L174">
-        <v>0.0007308976964227724</v>
+        <v>0.001064362037465958</v>
       </c>
       <c r="M174">
-        <v>0.4864583333333333</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="175" spans="1:13">
       <c r="A175" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B175" t="b">
         <v>0</v>
@@ -8213,10 +8234,10 @@
         <v>0</v>
       </c>
       <c r="F175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H175" t="b">
         <v>1</v>
@@ -8225,21 +8246,21 @@
         <v>3</v>
       </c>
       <c r="J175">
-        <v>0.5234560622148109</v>
+        <v>0.5192872108413109</v>
       </c>
       <c r="K175">
-        <v>0.971601320550558</v>
+        <v>1.018973281135655</v>
       </c>
       <c r="L175">
-        <v>0.0007308976964227724</v>
+        <v>0.001049116939531248</v>
       </c>
       <c r="M175">
-        <v>0.4864583333333333</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="176" spans="1:13">
       <c r="A176" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B176" t="b">
         <v>0</v>
@@ -8266,21 +8287,21 @@
         <v>3</v>
       </c>
       <c r="J176">
-        <v>0.5239598709511586</v>
+        <v>0.5231160748800475</v>
       </c>
       <c r="K176">
-        <v>0.9706949604113161</v>
+        <v>0.9922050009974825</v>
       </c>
       <c r="L176">
-        <v>0.0007291866763826655</v>
+        <v>0.00104273229376505</v>
       </c>
       <c r="M176">
-        <v>0.4864583333333333</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="177" spans="1:13">
       <c r="A177" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B177" t="b">
         <v>0</v>
@@ -8307,24 +8328,24 @@
         <v>3</v>
       </c>
       <c r="J177">
-        <v>0.5210785744255899</v>
+        <v>0.5275298593470076</v>
       </c>
       <c r="K177">
-        <v>0.9749718742391276</v>
+        <v>0.9813086030036071</v>
       </c>
       <c r="L177">
-        <v>0.000714895212202447</v>
+        <v>0.001028149792052128</v>
       </c>
       <c r="M177">
-        <v>0.515625</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C178" t="b">
         <v>1</v>
@@ -8336,7 +8357,7 @@
         <v>0</v>
       </c>
       <c r="F178" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G178" t="b">
         <v>0</v>
@@ -8348,24 +8369,24 @@
         <v>3</v>
       </c>
       <c r="J178">
-        <v>0.5194735709869261</v>
+        <v>0.5231359571107191</v>
       </c>
       <c r="K178">
-        <v>0.9855299692785617</v>
+        <v>0.98037097188942</v>
       </c>
       <c r="L178">
-        <v>0.0007021950040928086</v>
+        <v>0.000893498047604321</v>
       </c>
       <c r="M178">
-        <v>0.4791666666666666</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B179" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C179" t="b">
         <v>1</v>
@@ -8377,7 +8398,7 @@
         <v>0</v>
       </c>
       <c r="F179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G179" t="b">
         <v>0</v>
@@ -8389,24 +8410,24 @@
         <v>3</v>
       </c>
       <c r="J179">
-        <v>0.5180691783672811</v>
+        <v>0.5233894425353072</v>
       </c>
       <c r="K179">
-        <v>0.989820876148517</v>
+        <v>0.9793076438534227</v>
       </c>
       <c r="L179">
-        <v>0.000688837434176379</v>
+        <v>0.0008921416916242469</v>
       </c>
       <c r="M179">
-        <v>0.496875</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C180" t="b">
         <v>1</v>
@@ -8418,7 +8439,7 @@
         <v>0</v>
       </c>
       <c r="F180" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G180" t="b">
         <v>0</v>
@@ -8430,21 +8451,21 @@
         <v>3</v>
       </c>
       <c r="J180">
-        <v>0.5229710737969118</v>
+        <v>0.5192338475090287</v>
       </c>
       <c r="K180">
-        <v>0.9714128344104337</v>
+        <v>0.9987041425442801</v>
       </c>
       <c r="L180">
-        <v>0.0006866117622530046</v>
+        <v>0.0008845818834857927</v>
       </c>
       <c r="M180">
-        <v>0.4895833333333333</v>
+        <v>0.5322916666666666</v>
       </c>
     </row>
     <row r="181" spans="1:13">
       <c r="A181" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B181" t="b">
         <v>1</v>
@@ -8471,24 +8492,24 @@
         <v>3</v>
       </c>
       <c r="J181">
-        <v>0.5157650159283291</v>
+        <v>0.5198672919538527</v>
       </c>
       <c r="K181">
-        <v>0.997450211035142</v>
+        <v>0.9987315111297436</v>
       </c>
       <c r="L181">
-        <v>0.0006662326185625674</v>
+        <v>0.0008841936926848471</v>
       </c>
       <c r="M181">
-        <v>0.4833333333333333</v>
+        <v>0.49375</v>
       </c>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C182" t="b">
         <v>1</v>
@@ -8500,7 +8521,7 @@
         <v>0</v>
       </c>
       <c r="F182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G182" t="b">
         <v>0</v>
@@ -8512,24 +8533,24 @@
         <v>3</v>
       </c>
       <c r="J182">
-        <v>0.5157517735407376</v>
+        <v>0.5200709602353479</v>
       </c>
       <c r="K182">
-        <v>0.9989495523341765</v>
+        <v>0.9905491851146765</v>
       </c>
       <c r="L182">
-        <v>0.0006646361709553138</v>
+        <v>0.0008736703711149079</v>
       </c>
       <c r="M182">
-        <v>0.5166666666666667</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="183" spans="1:13">
       <c r="A183" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C183" t="b">
         <v>1</v>
@@ -8541,7 +8562,7 @@
         <v>0</v>
       </c>
       <c r="F183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G183" t="b">
         <v>0</v>
@@ -8553,21 +8574,21 @@
         <v>3</v>
       </c>
       <c r="J183">
-        <v>0.5167093111339377</v>
+        <v>0.5267930360859814</v>
       </c>
       <c r="K183">
-        <v>0.9877716194231716</v>
+        <v>0.9681505661246683</v>
       </c>
       <c r="L183">
-        <v>0.0006635241993630008</v>
+        <v>0.0008664300752523453</v>
       </c>
       <c r="M183">
-        <v>0.4833333333333333</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B184" t="b">
         <v>1</v>
@@ -8594,21 +8615,21 @@
         <v>3</v>
       </c>
       <c r="J184">
-        <v>0.5157801982551765</v>
+        <v>0.5182197619615945</v>
       </c>
       <c r="K184">
-        <v>0.995327891897728</v>
+        <v>0.9971492140155174</v>
       </c>
       <c r="L184">
-        <v>0.0006490197998480877</v>
+        <v>0.0007830581664438754</v>
       </c>
       <c r="M184">
-        <v>0.5145833333333334</v>
+        <v>0.4885416666666667</v>
       </c>
     </row>
     <row r="185" spans="1:13">
       <c r="A185" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="B185" t="b">
         <v>1</v>
@@ -8635,24 +8656,24 @@
         <v>3</v>
       </c>
       <c r="J185">
-        <v>0.5169402096969444</v>
+        <v>0.5180079641635738</v>
       </c>
       <c r="K185">
-        <v>0.984050631254914</v>
+        <v>0.9930154688490294</v>
       </c>
       <c r="L185">
-        <v>0.0005810074201798114</v>
+        <v>0.0007436123378321152</v>
       </c>
       <c r="M185">
-        <v>0.4947916666666667</v>
+        <v>0.5052083333333333</v>
       </c>
     </row>
     <row r="186" spans="1:13">
       <c r="A186" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C186" t="b">
         <v>1</v>
@@ -8664,7 +8685,7 @@
         <v>0</v>
       </c>
       <c r="F186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G186" t="b">
         <v>0</v>
@@ -8676,24 +8697,24 @@
         <v>3</v>
       </c>
       <c r="J186">
-        <v>0.5156703938454192</v>
+        <v>0.5234560622148109</v>
       </c>
       <c r="K186">
-        <v>0.9884858475378093</v>
+        <v>0.9717472102175606</v>
       </c>
       <c r="L186">
-        <v>0.0005782858865009393</v>
+        <v>0.00073269489577126</v>
       </c>
       <c r="M186">
-        <v>0.4958333333333333</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C187" t="b">
         <v>1</v>
@@ -8705,7 +8726,7 @@
         <v>0</v>
       </c>
       <c r="F187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G187" t="b">
         <v>0</v>
@@ -8717,27 +8738,27 @@
         <v>3</v>
       </c>
       <c r="J187">
-        <v>0.5182188056282635</v>
+        <v>0.5234560622148109</v>
       </c>
       <c r="K187">
-        <v>0.9789663885454715</v>
+        <v>0.971601320550558</v>
       </c>
       <c r="L187">
-        <v>0.0005393895141692327</v>
+        <v>0.0007308976964227724</v>
       </c>
       <c r="M187">
-        <v>0.4927083333333334</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="188" spans="1:13">
       <c r="A188" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D188" t="b">
         <v>0</v>
@@ -8758,24 +8779,24 @@
         <v>3</v>
       </c>
       <c r="J188">
-        <v>0.5205084601106268</v>
+        <v>0.5234560622148109</v>
       </c>
       <c r="K188">
-        <v>0.9624047968558334</v>
+        <v>0.971601320550558</v>
       </c>
       <c r="L188">
-        <v>0.0005081874366535753</v>
+        <v>0.0007308976964227724</v>
       </c>
       <c r="M188">
-        <v>0.5104166666666667</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C189" t="b">
         <v>1</v>
@@ -8787,7 +8808,7 @@
         <v>0</v>
       </c>
       <c r="F189" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G189" t="b">
         <v>0</v>
@@ -8799,27 +8820,27 @@
         <v>3</v>
       </c>
       <c r="J189">
-        <v>0.5182988314177761</v>
+        <v>0.5239598709511586</v>
       </c>
       <c r="K189">
-        <v>0.9683770987623133</v>
+        <v>0.9706949604113161</v>
       </c>
       <c r="L189">
-        <v>0.00046383460297976</v>
+        <v>0.0007291866763826655</v>
       </c>
       <c r="M189">
-        <v>0.5145833333333334</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="190" spans="1:13">
       <c r="A190" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C190" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D190" t="b">
         <v>0</v>
@@ -8840,27 +8861,27 @@
         <v>3</v>
       </c>
       <c r="J190">
-        <v>0.5215973952014604</v>
+        <v>0.5210785744255899</v>
       </c>
       <c r="K190">
-        <v>0.956465781904547</v>
+        <v>0.9749718742391276</v>
       </c>
       <c r="L190">
-        <v>0.0004617678766313561</v>
+        <v>0.000714895212202447</v>
       </c>
       <c r="M190">
-        <v>0.5</v>
+        <v>0.515625</v>
       </c>
     </row>
     <row r="191" spans="1:13">
       <c r="A191" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B191" t="b">
         <v>1</v>
       </c>
       <c r="C191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D191" t="b">
         <v>0</v>
@@ -8869,7 +8890,7 @@
         <v>0</v>
       </c>
       <c r="F191" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G191" t="b">
         <v>0</v>
@@ -8881,27 +8902,27 @@
         <v>3</v>
       </c>
       <c r="J191">
-        <v>0.52419721049946</v>
+        <v>0.5194735709869261</v>
       </c>
       <c r="K191">
-        <v>0.9445965735500413</v>
+        <v>0.9855299692785617</v>
       </c>
       <c r="L191">
-        <v>0.0004515943899109011</v>
+        <v>0.0007021950040928086</v>
       </c>
       <c r="M191">
-        <v>0.5041666666666667</v>
+        <v>0.4791666666666666</v>
       </c>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B192" t="b">
         <v>1</v>
       </c>
       <c r="C192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D192" t="b">
         <v>0</v>
@@ -8913,7 +8934,7 @@
         <v>0</v>
       </c>
       <c r="G192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H192" t="b">
         <v>1</v>
@@ -8922,27 +8943,27 @@
         <v>3</v>
       </c>
       <c r="J192">
-        <v>0.5084803559328442</v>
+        <v>0.5180691783672811</v>
       </c>
       <c r="K192">
-        <v>1.000145368038369</v>
+        <v>0.989820876148517</v>
       </c>
       <c r="L192">
-        <v>0.0003839825488022947</v>
+        <v>0.000688837434176379</v>
       </c>
       <c r="M192">
-        <v>0.4729166666666667</v>
+        <v>0.496875</v>
       </c>
     </row>
     <row r="193" spans="1:13">
       <c r="A193" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D193" t="b">
         <v>0</v>
@@ -8963,21 +8984,21 @@
         <v>3</v>
       </c>
       <c r="J193">
-        <v>0.5208649234022996</v>
+        <v>0.5229710737969118</v>
       </c>
       <c r="K193">
-        <v>0.9454882101058439</v>
+        <v>0.9714128344104337</v>
       </c>
       <c r="L193">
-        <v>0.0003112942761380053</v>
+        <v>0.0006866117622530046</v>
       </c>
       <c r="M193">
-        <v>0.4927083333333333</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B194" t="b">
         <v>1</v>
@@ -9004,27 +9025,27 @@
         <v>3</v>
       </c>
       <c r="J194">
-        <v>0.5090224632640803</v>
+        <v>0.5157650159283291</v>
       </c>
       <c r="K194">
-        <v>0.9728240975197352</v>
+        <v>0.997450211035142</v>
       </c>
       <c r="L194">
-        <v>9.092625250419969E-05</v>
+        <v>0.0006662326185625674</v>
       </c>
       <c r="M194">
-        <v>0.4666666666666667</v>
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="195" spans="1:13">
       <c r="A195" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B195" t="b">
         <v>1</v>
       </c>
       <c r="C195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D195" t="b">
         <v>0</v>
@@ -9036,7 +9057,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H195" t="b">
         <v>1</v>
@@ -9045,24 +9066,24 @@
         <v>3</v>
       </c>
       <c r="J195">
-        <v>0.498043480585272</v>
+        <v>0.5157517735407376</v>
       </c>
       <c r="K195">
-        <v>1.01171519342194</v>
+        <v>0.9989495523341765</v>
       </c>
       <c r="L195">
-        <v>3.900113765166399E-05</v>
+        <v>0.0006646361709553138</v>
       </c>
       <c r="M195">
-        <v>0.446875</v>
+        <v>0.5166666666666667</v>
       </c>
     </row>
     <row r="196" spans="1:13">
       <c r="A196" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B196" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C196" t="b">
         <v>1</v>
@@ -9083,30 +9104,30 @@
         <v>1</v>
       </c>
       <c r="I196">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J196">
-        <v>0.5192860597624637</v>
+        <v>0.5167093111339377</v>
       </c>
       <c r="K196">
-        <v>0.9883310584528118</v>
+        <v>0.9877716194231716</v>
       </c>
       <c r="L196">
-        <v>0.0007947444603153772</v>
+        <v>0.0006635241993630008</v>
       </c>
       <c r="M196">
-        <v>0.5104166666666666</v>
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B197" t="b">
         <v>1</v>
       </c>
       <c r="C197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D197" t="b">
         <v>0</v>
@@ -9124,30 +9145,30 @@
         <v>1</v>
       </c>
       <c r="I197">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J197">
-        <v>0.5128883453974573</v>
+        <v>0.5157801982551765</v>
       </c>
       <c r="K197">
-        <v>0.9927130709575864</v>
+        <v>0.995327891897728</v>
       </c>
       <c r="L197">
-        <v>0.0005181985736232644</v>
+        <v>0.0006490197998480877</v>
       </c>
       <c r="M197">
-        <v>0.4770833333333333</v>
+        <v>0.5145833333333334</v>
       </c>
     </row>
     <row r="198" spans="1:13">
       <c r="A198" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B198" t="b">
         <v>1</v>
       </c>
       <c r="C198" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D198" t="b">
         <v>0</v>
@@ -9165,30 +9186,30 @@
         <v>1</v>
       </c>
       <c r="I198">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J198">
-        <v>0.5192913061316812</v>
+        <v>0.5169402096969444</v>
       </c>
       <c r="K198">
-        <v>0.9681219590791648</v>
+        <v>0.984050631254914</v>
       </c>
       <c r="L198">
-        <v>0.0005151313972340504</v>
+        <v>0.0005810074201798114</v>
       </c>
       <c r="M198">
-        <v>0.4854166666666666</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B199" t="b">
         <v>1</v>
       </c>
       <c r="C199" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D199" t="b">
         <v>0</v>
@@ -9206,30 +9227,30 @@
         <v>1</v>
       </c>
       <c r="I199">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J199">
-        <v>0.5146971432210451</v>
+        <v>0.5156703938454192</v>
       </c>
       <c r="K199">
-        <v>0.9823797202731411</v>
+        <v>0.9884858475378093</v>
       </c>
       <c r="L199">
-        <v>0.0004710530184552176</v>
+        <v>0.0005782858865009393</v>
       </c>
       <c r="M199">
-        <v>0.4958333333333334</v>
+        <v>0.4958333333333333</v>
       </c>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B200" t="b">
         <v>1</v>
       </c>
       <c r="C200" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D200" t="b">
         <v>0</v>
@@ -9247,27 +9268,27 @@
         <v>1</v>
       </c>
       <c r="I200">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J200">
-        <v>0.5180052468709013</v>
+        <v>0.5182188056282635</v>
       </c>
       <c r="K200">
-        <v>0.9669254428894065</v>
+        <v>0.9789663885454715</v>
       </c>
       <c r="L200">
-        <v>0.0004307954719285946</v>
+        <v>0.0005393895141692327</v>
       </c>
       <c r="M200">
-        <v>0.4697916666666667</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="201" spans="1:13">
       <c r="A201" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C201" t="b">
         <v>0</v>
@@ -9279,33 +9300,33 @@
         <v>0</v>
       </c>
       <c r="F201" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H201" t="b">
         <v>1</v>
       </c>
       <c r="I201">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J201">
-        <v>0.521425828542861</v>
+        <v>0.5092599221677537</v>
       </c>
       <c r="K201">
-        <v>0.9540601634518397</v>
+        <v>1.008857221698815</v>
       </c>
       <c r="L201">
-        <v>0.0004242879750097382</v>
+        <v>0.0005340122910058503</v>
       </c>
       <c r="M201">
-        <v>0.4802083333333334</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B202" t="b">
         <v>1</v>
@@ -9320,7 +9341,7 @@
         <v>0</v>
       </c>
       <c r="F202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G202" t="b">
         <v>0</v>
@@ -9329,30 +9350,30 @@
         <v>1</v>
       </c>
       <c r="I202">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J202">
-        <v>0.5118724123598453</v>
+        <v>0.5205084601106268</v>
       </c>
       <c r="K202">
-        <v>0.9888213931203325</v>
+        <v>0.9624047968558334</v>
       </c>
       <c r="L202">
-        <v>0.0004202665643346187</v>
+        <v>0.0005081874366535753</v>
       </c>
       <c r="M202">
-        <v>0.5041666666666667</v>
+        <v>0.5104166666666667</v>
       </c>
     </row>
     <row r="203" spans="1:13">
       <c r="A203" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B203" t="b">
         <v>1</v>
       </c>
       <c r="C203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D203" t="b">
         <v>0</v>
@@ -9370,24 +9391,24 @@
         <v>1</v>
       </c>
       <c r="I203">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J203">
-        <v>0.5116389999777903</v>
+        <v>0.5182988314177761</v>
       </c>
       <c r="K203">
-        <v>0.9891164727382922</v>
+        <v>0.9683770987623133</v>
       </c>
       <c r="L203">
-        <v>0.0004136568838493608</v>
+        <v>0.00046383460297976</v>
       </c>
       <c r="M203">
-        <v>0.465625</v>
+        <v>0.5145833333333334</v>
       </c>
     </row>
     <row r="204" spans="1:13">
       <c r="A204" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B204" t="b">
         <v>1</v>
@@ -9402,7 +9423,7 @@
         <v>0</v>
       </c>
       <c r="F204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G204" t="b">
         <v>0</v>
@@ -9411,24 +9432,24 @@
         <v>1</v>
       </c>
       <c r="I204">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J204">
-        <v>0.5107855868489263</v>
+        <v>0.5215973952014604</v>
       </c>
       <c r="K204">
-        <v>0.9920941941379633</v>
+        <v>0.956465781904547</v>
       </c>
       <c r="L204">
-        <v>0.0004007577390793323</v>
+        <v>0.0004617678766313561</v>
       </c>
       <c r="M204">
-        <v>0.465625</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="205" spans="1:13">
       <c r="A205" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B205" t="b">
         <v>1</v>
@@ -9443,7 +9464,7 @@
         <v>0</v>
       </c>
       <c r="F205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G205" t="b">
         <v>0</v>
@@ -9452,24 +9473,24 @@
         <v>1</v>
       </c>
       <c r="I205">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J205">
-        <v>0.5172228199978071</v>
+        <v>0.52419721049946</v>
       </c>
       <c r="K205">
-        <v>0.9647596950132241</v>
+        <v>0.9445965735500413</v>
       </c>
       <c r="L205">
-        <v>0.0003743848584789409</v>
+        <v>0.0004515943899109011</v>
       </c>
       <c r="M205">
-        <v>0.490625</v>
+        <v>0.5041666666666667</v>
       </c>
     </row>
     <row r="206" spans="1:13">
       <c r="A206" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B206" t="b">
         <v>1</v>
@@ -9487,33 +9508,33 @@
         <v>0</v>
       </c>
       <c r="G206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H206" t="b">
         <v>1</v>
       </c>
       <c r="I206">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J206">
-        <v>0.5172216763136824</v>
+        <v>0.5084803559328442</v>
       </c>
       <c r="K206">
-        <v>0.9638635136795901</v>
+        <v>1.000145368038369</v>
       </c>
       <c r="L206">
-        <v>0.0003591400964410646</v>
+        <v>0.0003839825488022947</v>
       </c>
       <c r="M206">
-        <v>0.45</v>
+        <v>0.4729166666666667</v>
       </c>
     </row>
     <row r="207" spans="1:13">
       <c r="A207" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C207" t="b">
         <v>0</v>
@@ -9525,33 +9546,33 @@
         <v>0</v>
       </c>
       <c r="F207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H207" t="b">
         <v>1</v>
       </c>
       <c r="I207">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J207">
-        <v>0.5211521948687453</v>
+        <v>0.5073071838753863</v>
       </c>
       <c r="K207">
-        <v>0.9456457750496761</v>
+        <v>1.003492775274981</v>
       </c>
       <c r="L207">
-        <v>0.0003144118998875088</v>
+        <v>0.00037555091593558</v>
       </c>
       <c r="M207">
-        <v>0.478125</v>
+        <v>0.46875</v>
       </c>
     </row>
     <row r="208" spans="1:13">
       <c r="A208" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B208" t="b">
         <v>1</v>
@@ -9566,7 +9587,7 @@
         <v>0</v>
       </c>
       <c r="F208" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G208" t="b">
         <v>0</v>
@@ -9575,30 +9596,30 @@
         <v>1</v>
       </c>
       <c r="I208">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J208">
-        <v>0.5149567139418781</v>
+        <v>0.5208649234022996</v>
       </c>
       <c r="K208">
-        <v>0.968398745608279</v>
+        <v>0.9454882101058439</v>
       </c>
       <c r="L208">
-        <v>0.0003109924505142643</v>
+        <v>0.0003112942761380053</v>
       </c>
       <c r="M208">
-        <v>0.4833333333333334</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="209" spans="1:13">
       <c r="A209" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B209" t="b">
         <v>1</v>
       </c>
       <c r="C209" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D209" t="b">
         <v>0</v>
@@ -9616,24 +9637,24 @@
         <v>1</v>
       </c>
       <c r="I209">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J209">
-        <v>0.5125866183873925</v>
+        <v>0.5090224632640803</v>
       </c>
       <c r="K209">
-        <v>0.9765055242819229</v>
+        <v>0.9728240975197352</v>
       </c>
       <c r="L209">
-        <v>0.0003016252330849768</v>
+        <v>9.092625250419969E-05</v>
       </c>
       <c r="M209">
-        <v>0.4854166666666666</v>
+        <v>0.4666666666666667</v>
       </c>
     </row>
     <row r="210" spans="1:13">
       <c r="A210" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B210" t="b">
         <v>1</v>
@@ -9651,36 +9672,36 @@
         <v>0</v>
       </c>
       <c r="G210" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H210" t="b">
         <v>1</v>
       </c>
       <c r="I210">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J210">
-        <v>0.5138663949396409</v>
+        <v>0.498043480585272</v>
       </c>
       <c r="K210">
-        <v>0.9677390336165562</v>
+        <v>1.01171519342194</v>
       </c>
       <c r="L210">
-        <v>0.0002442213938235176</v>
+        <v>3.900113765166399E-05</v>
       </c>
       <c r="M210">
-        <v>0.4947916666666667</v>
+        <v>0.446875</v>
       </c>
     </row>
     <row r="211" spans="1:13">
       <c r="A211" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B211" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C211" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D211" t="b">
         <v>0</v>
@@ -9701,21 +9722,21 @@
         <v>2</v>
       </c>
       <c r="J211">
-        <v>0.5077892431961631</v>
+        <v>0.5192860597624637</v>
       </c>
       <c r="K211">
-        <v>0.9867771372874354</v>
+        <v>0.9883310584528118</v>
       </c>
       <c r="L211">
-        <v>0.0002048585635184588</v>
+        <v>0.0007947444603153772</v>
       </c>
       <c r="M211">
-        <v>0.4708333333333334</v>
+        <v>0.5104166666666666</v>
       </c>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B212" t="b">
         <v>1</v>
@@ -9742,21 +9763,21 @@
         <v>2</v>
       </c>
       <c r="J212">
-        <v>0.5107790455517796</v>
+        <v>0.5128883453974573</v>
       </c>
       <c r="K212">
-        <v>0.975677966194201</v>
+        <v>0.9927130709575864</v>
       </c>
       <c r="L212">
-        <v>0.0002023413935013672</v>
+        <v>0.0005181985736232644</v>
       </c>
       <c r="M212">
-        <v>0.4666666666666667</v>
+        <v>0.4770833333333333</v>
       </c>
     </row>
     <row r="213" spans="1:13">
       <c r="A213" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B213" t="b">
         <v>1</v>
@@ -9783,21 +9804,21 @@
         <v>2</v>
       </c>
       <c r="J213">
-        <v>0.5134129596946581</v>
+        <v>0.5192913061316812</v>
       </c>
       <c r="K213">
-        <v>0.9603573342942637</v>
+        <v>0.9681219590791648</v>
       </c>
       <c r="L213">
-        <v>0.0001467025775373776</v>
+        <v>0.0005151313972340504</v>
       </c>
       <c r="M213">
-        <v>0.5354166666666667</v>
+        <v>0.4854166666666666</v>
       </c>
     </row>
     <row r="214" spans="1:13">
       <c r="A214" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B214" t="b">
         <v>1</v>
@@ -9824,21 +9845,21 @@
         <v>2</v>
       </c>
       <c r="J214">
-        <v>0.5044139628673301</v>
+        <v>0.5146971432210451</v>
       </c>
       <c r="K214">
-        <v>0.9951175019058784</v>
+        <v>0.9823797202731411</v>
       </c>
       <c r="L214">
-        <v>0.0001413509157678745</v>
+        <v>0.0004710530184552176</v>
       </c>
       <c r="M214">
-        <v>0.484375</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="215" spans="1:13">
       <c r="A215" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B215" t="b">
         <v>1</v>
@@ -9865,24 +9886,24 @@
         <v>2</v>
       </c>
       <c r="J215">
-        <v>0.5084622088699371</v>
+        <v>0.5180052468709013</v>
       </c>
       <c r="K215">
-        <v>0.9711824902332508</v>
+        <v>0.9669254428894065</v>
       </c>
       <c r="L215">
-        <v>4.250511853415573E-05</v>
+        <v>0.0004307954719285946</v>
       </c>
       <c r="M215">
-        <v>0.4760416666666667</v>
+        <v>0.4697916666666667</v>
       </c>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C216" t="b">
         <v>0</v>
@@ -9894,7 +9915,7 @@
         <v>0</v>
       </c>
       <c r="F216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G216" t="b">
         <v>0</v>
@@ -9906,27 +9927,27 @@
         <v>2</v>
       </c>
       <c r="J216">
-        <v>0.5059372449167735</v>
+        <v>0.521425828542861</v>
       </c>
       <c r="K216">
-        <v>0.9802384896159418</v>
+        <v>0.9540601634518397</v>
       </c>
       <c r="L216">
-        <v>3.491829125961306E-05</v>
+        <v>0.0004242879750097382</v>
       </c>
       <c r="M216">
-        <v>0.46875</v>
+        <v>0.4802083333333334</v>
       </c>
     </row>
     <row r="217" spans="1:13">
       <c r="A217" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B217" t="b">
         <v>1</v>
       </c>
       <c r="C217" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D217" t="b">
         <v>0</v>
@@ -9941,33 +9962,33 @@
         <v>0</v>
       </c>
       <c r="H217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I217">
         <v>2</v>
       </c>
       <c r="J217">
-        <v>0.5102427732589988</v>
+        <v>0.5118724123598453</v>
       </c>
       <c r="K217">
-        <v>0.9592376571912364</v>
+        <v>0.9888213931203325</v>
       </c>
       <c r="L217">
-        <v>-1.679337356870932E-05</v>
+        <v>0.0004202665643346187</v>
       </c>
       <c r="M217">
-        <v>0.4645833333333333</v>
+        <v>0.5041666666666667</v>
       </c>
     </row>
     <row r="218" spans="1:13">
       <c r="A218" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B218" t="b">
         <v>1</v>
       </c>
       <c r="C218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D218" t="b">
         <v>0</v>
@@ -9982,27 +10003,27 @@
         <v>0</v>
       </c>
       <c r="H218" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I218">
         <v>2</v>
       </c>
       <c r="J218">
-        <v>0.5036638944043103</v>
+        <v>0.5116389999777903</v>
       </c>
       <c r="K218">
-        <v>0.9822248407953188</v>
+        <v>0.9891164727382922</v>
       </c>
       <c r="L218">
-        <v>-3.73627218610069E-05</v>
+        <v>0.0004136568838493608</v>
       </c>
       <c r="M218">
-        <v>0.4572916666666667</v>
+        <v>0.465625</v>
       </c>
     </row>
     <row r="219" spans="1:13">
       <c r="A219" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B219" t="b">
         <v>1</v>
@@ -10023,27 +10044,27 @@
         <v>0</v>
       </c>
       <c r="H219" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I219">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J219">
-        <v>0.5080731717638939</v>
+        <v>0.5107855868489263</v>
       </c>
       <c r="K219">
-        <v>0.9671206618702717</v>
+        <v>0.9920941941379633</v>
       </c>
       <c r="L219">
-        <v>-1.600518697063361E-05</v>
+        <v>0.0004007577390793323</v>
       </c>
       <c r="M219">
-        <v>0.4614583333333333</v>
+        <v>0.465625</v>
       </c>
     </row>
     <row r="220" spans="1:13">
       <c r="A220" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B220" t="b">
         <v>1</v>
@@ -10064,27 +10085,27 @@
         <v>0</v>
       </c>
       <c r="H220" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I220">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J220">
-        <v>0.4980599149895381</v>
+        <v>0.5172228199978071</v>
       </c>
       <c r="K220">
-        <v>0.9978631355506703</v>
+        <v>0.9647596950132241</v>
       </c>
       <c r="L220">
-        <v>-0.0001213400092365598</v>
+        <v>0.0003743848584789409</v>
       </c>
       <c r="M220">
-        <v>0.4760416666666666</v>
+        <v>0.490625</v>
       </c>
     </row>
     <row r="221" spans="1:13">
       <c r="A221" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B221" t="b">
         <v>1</v>
@@ -10105,30 +10126,30 @@
         <v>0</v>
       </c>
       <c r="H221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I221">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J221">
-        <v>0.504643606538516</v>
+        <v>0.5172216763136824</v>
       </c>
       <c r="K221">
-        <v>0.9656168808879457</v>
+        <v>0.9638635136795901</v>
       </c>
       <c r="L221">
-        <v>-0.0001910988700251262</v>
+        <v>0.0003591400964410646</v>
       </c>
       <c r="M221">
-        <v>0.4875</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="222" spans="1:13">
       <c r="A222" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B222" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C222" t="b">
         <v>0</v>
@@ -10140,33 +10161,33 @@
         <v>0</v>
       </c>
       <c r="F222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G222" t="b">
         <v>0</v>
       </c>
       <c r="H222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I222">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J222">
-        <v>0.4948973953569638</v>
+        <v>0.5211521948687453</v>
       </c>
       <c r="K222">
-        <v>0.9782862384550919</v>
+        <v>0.9456457750496761</v>
       </c>
       <c r="L222">
-        <v>-0.0004846782247422767</v>
+        <v>0.0003144118998875088</v>
       </c>
       <c r="M222">
-        <v>0.45</v>
+        <v>0.478125</v>
       </c>
     </row>
     <row r="223" spans="1:13">
       <c r="A223" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B223" t="b">
         <v>1</v>
@@ -10187,27 +10208,27 @@
         <v>0</v>
       </c>
       <c r="H223" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I223">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J223">
-        <v>0.5041399556108799</v>
+        <v>0.5149567139418781</v>
       </c>
       <c r="K223">
-        <v>0.9379107395309157</v>
+        <v>0.968398745608279</v>
       </c>
       <c r="L223">
-        <v>-0.0005528484870497855</v>
+        <v>0.0003109924505142643</v>
       </c>
       <c r="M223">
-        <v>0.4447916666666667</v>
+        <v>0.4833333333333334</v>
       </c>
     </row>
     <row r="224" spans="1:13">
       <c r="A224" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B224" t="b">
         <v>1</v>
@@ -10228,27 +10249,27 @@
         <v>0</v>
       </c>
       <c r="H224" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I224">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J224">
-        <v>0.4907824101008133</v>
+        <v>0.5125866183873925</v>
       </c>
       <c r="K224">
-        <v>0.9709557512183234</v>
+        <v>0.9765055242819229</v>
       </c>
       <c r="L224">
-        <v>-0.0007712571387079928</v>
+        <v>0.0003016252330849768</v>
       </c>
       <c r="M224">
-        <v>0.4385416666666667</v>
+        <v>0.4854166666666666</v>
       </c>
     </row>
     <row r="225" spans="1:13">
       <c r="A225" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B225" t="b">
         <v>1</v>
@@ -10269,27 +10290,27 @@
         <v>0</v>
       </c>
       <c r="H225" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I225">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J225">
-        <v>0.4909423672431471</v>
+        <v>0.5138663949396409</v>
       </c>
       <c r="K225">
-        <v>0.9575175230782224</v>
+        <v>0.9677390336165562</v>
       </c>
       <c r="L225">
-        <v>-0.0009393748524447957</v>
+        <v>0.0002442213938235176</v>
       </c>
       <c r="M225">
-        <v>0.4291666666666667</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="226" spans="1:13">
       <c r="A226" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B226" t="b">
         <v>1</v>
@@ -10310,62 +10331,677 @@
         <v>0</v>
       </c>
       <c r="H226" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I226">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J226">
-        <v>0.4951541371093768</v>
+        <v>0.5077892431961631</v>
       </c>
       <c r="K226">
-        <v>0.9308585329906285</v>
+        <v>0.9867771372874354</v>
       </c>
       <c r="L226">
-        <v>-0.001040784429799158</v>
+        <v>0.0002048585635184588</v>
       </c>
       <c r="M226">
-        <v>0.41875</v>
+        <v>0.4708333333333334</v>
       </c>
     </row>
     <row r="227" spans="1:13">
       <c r="A227" t="s">
+        <v>229</v>
+      </c>
+      <c r="B227" t="b">
+        <v>1</v>
+      </c>
+      <c r="C227" t="b">
+        <v>0</v>
+      </c>
+      <c r="D227" t="b">
+        <v>0</v>
+      </c>
+      <c r="E227" t="b">
+        <v>0</v>
+      </c>
+      <c r="F227" t="b">
+        <v>0</v>
+      </c>
+      <c r="G227" t="b">
+        <v>0</v>
+      </c>
+      <c r="H227" t="b">
+        <v>1</v>
+      </c>
+      <c r="I227">
+        <v>2</v>
+      </c>
+      <c r="J227">
+        <v>0.5107790455517796</v>
+      </c>
+      <c r="K227">
+        <v>0.975677966194201</v>
+      </c>
+      <c r="L227">
+        <v>0.0002023413935013672</v>
+      </c>
+      <c r="M227">
+        <v>0.4666666666666667</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13">
+      <c r="A228" t="s">
+        <v>230</v>
+      </c>
+      <c r="B228" t="b">
+        <v>1</v>
+      </c>
+      <c r="C228" t="b">
+        <v>0</v>
+      </c>
+      <c r="D228" t="b">
+        <v>0</v>
+      </c>
+      <c r="E228" t="b">
+        <v>0</v>
+      </c>
+      <c r="F228" t="b">
+        <v>0</v>
+      </c>
+      <c r="G228" t="b">
+        <v>0</v>
+      </c>
+      <c r="H228" t="b">
+        <v>1</v>
+      </c>
+      <c r="I228">
+        <v>2</v>
+      </c>
+      <c r="J228">
+        <v>0.5134129596946581</v>
+      </c>
+      <c r="K228">
+        <v>0.9603573342942637</v>
+      </c>
+      <c r="L228">
+        <v>0.0001467025775373776</v>
+      </c>
+      <c r="M228">
+        <v>0.5354166666666667</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13">
+      <c r="A229" t="s">
+        <v>231</v>
+      </c>
+      <c r="B229" t="b">
+        <v>1</v>
+      </c>
+      <c r="C229" t="b">
+        <v>0</v>
+      </c>
+      <c r="D229" t="b">
+        <v>0</v>
+      </c>
+      <c r="E229" t="b">
+        <v>0</v>
+      </c>
+      <c r="F229" t="b">
+        <v>0</v>
+      </c>
+      <c r="G229" t="b">
+        <v>0</v>
+      </c>
+      <c r="H229" t="b">
+        <v>1</v>
+      </c>
+      <c r="I229">
+        <v>2</v>
+      </c>
+      <c r="J229">
+        <v>0.5044139628673301</v>
+      </c>
+      <c r="K229">
+        <v>0.9951175019058784</v>
+      </c>
+      <c r="L229">
+        <v>0.0001413509157678745</v>
+      </c>
+      <c r="M229">
+        <v>0.484375</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13">
+      <c r="A230" t="s">
+        <v>232</v>
+      </c>
+      <c r="B230" t="b">
+        <v>1</v>
+      </c>
+      <c r="C230" t="b">
+        <v>0</v>
+      </c>
+      <c r="D230" t="b">
+        <v>0</v>
+      </c>
+      <c r="E230" t="b">
+        <v>0</v>
+      </c>
+      <c r="F230" t="b">
+        <v>0</v>
+      </c>
+      <c r="G230" t="b">
+        <v>0</v>
+      </c>
+      <c r="H230" t="b">
+        <v>1</v>
+      </c>
+      <c r="I230">
+        <v>2</v>
+      </c>
+      <c r="J230">
+        <v>0.5084622088699371</v>
+      </c>
+      <c r="K230">
+        <v>0.9711824902332508</v>
+      </c>
+      <c r="L230">
+        <v>4.250511853415573E-05</v>
+      </c>
+      <c r="M230">
+        <v>0.4760416666666667</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13">
+      <c r="A231" t="s">
+        <v>233</v>
+      </c>
+      <c r="B231" t="b">
+        <v>1</v>
+      </c>
+      <c r="C231" t="b">
+        <v>0</v>
+      </c>
+      <c r="D231" t="b">
+        <v>0</v>
+      </c>
+      <c r="E231" t="b">
+        <v>0</v>
+      </c>
+      <c r="F231" t="b">
+        <v>0</v>
+      </c>
+      <c r="G231" t="b">
+        <v>0</v>
+      </c>
+      <c r="H231" t="b">
+        <v>1</v>
+      </c>
+      <c r="I231">
+        <v>2</v>
+      </c>
+      <c r="J231">
+        <v>0.5059372449167735</v>
+      </c>
+      <c r="K231">
+        <v>0.9802384896159418</v>
+      </c>
+      <c r="L231">
+        <v>3.491829125961306E-05</v>
+      </c>
+      <c r="M231">
+        <v>0.46875</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13">
+      <c r="A232" t="s">
+        <v>234</v>
+      </c>
+      <c r="B232" t="b">
+        <v>1</v>
+      </c>
+      <c r="C232" t="b">
+        <v>1</v>
+      </c>
+      <c r="D232" t="b">
+        <v>0</v>
+      </c>
+      <c r="E232" t="b">
+        <v>0</v>
+      </c>
+      <c r="F232" t="b">
+        <v>0</v>
+      </c>
+      <c r="G232" t="b">
+        <v>0</v>
+      </c>
+      <c r="H232" t="b">
+        <v>0</v>
+      </c>
+      <c r="I232">
+        <v>2</v>
+      </c>
+      <c r="J232">
+        <v>0.5102427732589988</v>
+      </c>
+      <c r="K232">
+        <v>0.9592376571912364</v>
+      </c>
+      <c r="L232">
+        <v>-1.679337356870932E-05</v>
+      </c>
+      <c r="M232">
+        <v>0.4645833333333333</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13">
+      <c r="A233" t="s">
+        <v>235</v>
+      </c>
+      <c r="B233" t="b">
+        <v>1</v>
+      </c>
+      <c r="C233" t="b">
+        <v>1</v>
+      </c>
+      <c r="D233" t="b">
+        <v>0</v>
+      </c>
+      <c r="E233" t="b">
+        <v>0</v>
+      </c>
+      <c r="F233" t="b">
+        <v>0</v>
+      </c>
+      <c r="G233" t="b">
+        <v>0</v>
+      </c>
+      <c r="H233" t="b">
+        <v>0</v>
+      </c>
+      <c r="I233">
+        <v>2</v>
+      </c>
+      <c r="J233">
+        <v>0.5036638944043103</v>
+      </c>
+      <c r="K233">
+        <v>0.9822248407953188</v>
+      </c>
+      <c r="L233">
+        <v>-3.73627218610069E-05</v>
+      </c>
+      <c r="M233">
+        <v>0.4572916666666667</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13">
+      <c r="A234" t="s">
+        <v>236</v>
+      </c>
+      <c r="B234" t="b">
+        <v>1</v>
+      </c>
+      <c r="C234" t="b">
+        <v>0</v>
+      </c>
+      <c r="D234" t="b">
+        <v>0</v>
+      </c>
+      <c r="E234" t="b">
+        <v>0</v>
+      </c>
+      <c r="F234" t="b">
+        <v>0</v>
+      </c>
+      <c r="G234" t="b">
+        <v>0</v>
+      </c>
+      <c r="H234" t="b">
+        <v>0</v>
+      </c>
+      <c r="I234">
+        <v>1</v>
+      </c>
+      <c r="J234">
+        <v>0.5080731717638939</v>
+      </c>
+      <c r="K234">
+        <v>0.9671206618702717</v>
+      </c>
+      <c r="L234">
+        <v>-1.600518697063361E-05</v>
+      </c>
+      <c r="M234">
+        <v>0.4614583333333333</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13">
+      <c r="A235" t="s">
         <v>237</v>
       </c>
-      <c r="B227" t="b">
-        <v>1</v>
-      </c>
-      <c r="C227" t="b">
-        <v>0</v>
-      </c>
-      <c r="D227" t="b">
-        <v>0</v>
-      </c>
-      <c r="E227" t="b">
-        <v>0</v>
-      </c>
-      <c r="F227" t="b">
-        <v>0</v>
-      </c>
-      <c r="G227" t="b">
-        <v>0</v>
-      </c>
-      <c r="H227" t="b">
-        <v>0</v>
-      </c>
-      <c r="I227">
-        <v>1</v>
-      </c>
-      <c r="J227">
+      <c r="B235" t="b">
+        <v>1</v>
+      </c>
+      <c r="C235" t="b">
+        <v>0</v>
+      </c>
+      <c r="D235" t="b">
+        <v>0</v>
+      </c>
+      <c r="E235" t="b">
+        <v>0</v>
+      </c>
+      <c r="F235" t="b">
+        <v>0</v>
+      </c>
+      <c r="G235" t="b">
+        <v>0</v>
+      </c>
+      <c r="H235" t="b">
+        <v>0</v>
+      </c>
+      <c r="I235">
+        <v>1</v>
+      </c>
+      <c r="J235">
+        <v>0.4980599149895381</v>
+      </c>
+      <c r="K235">
+        <v>0.9978631355506703</v>
+      </c>
+      <c r="L235">
+        <v>-0.0001213400092365598</v>
+      </c>
+      <c r="M235">
+        <v>0.4760416666666666</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13">
+      <c r="A236" t="s">
+        <v>238</v>
+      </c>
+      <c r="B236" t="b">
+        <v>1</v>
+      </c>
+      <c r="C236" t="b">
+        <v>0</v>
+      </c>
+      <c r="D236" t="b">
+        <v>0</v>
+      </c>
+      <c r="E236" t="b">
+        <v>0</v>
+      </c>
+      <c r="F236" t="b">
+        <v>0</v>
+      </c>
+      <c r="G236" t="b">
+        <v>0</v>
+      </c>
+      <c r="H236" t="b">
+        <v>0</v>
+      </c>
+      <c r="I236">
+        <v>1</v>
+      </c>
+      <c r="J236">
+        <v>0.504643606538516</v>
+      </c>
+      <c r="K236">
+        <v>0.9656168808879457</v>
+      </c>
+      <c r="L236">
+        <v>-0.0001910988700251262</v>
+      </c>
+      <c r="M236">
+        <v>0.4875</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13">
+      <c r="A237" t="s">
+        <v>239</v>
+      </c>
+      <c r="B237" t="b">
+        <v>1</v>
+      </c>
+      <c r="C237" t="b">
+        <v>0</v>
+      </c>
+      <c r="D237" t="b">
+        <v>0</v>
+      </c>
+      <c r="E237" t="b">
+        <v>0</v>
+      </c>
+      <c r="F237" t="b">
+        <v>0</v>
+      </c>
+      <c r="G237" t="b">
+        <v>0</v>
+      </c>
+      <c r="H237" t="b">
+        <v>0</v>
+      </c>
+      <c r="I237">
+        <v>1</v>
+      </c>
+      <c r="J237">
+        <v>0.4948973953569638</v>
+      </c>
+      <c r="K237">
+        <v>0.9782862384550919</v>
+      </c>
+      <c r="L237">
+        <v>-0.0004846782247422767</v>
+      </c>
+      <c r="M237">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13">
+      <c r="A238" t="s">
+        <v>240</v>
+      </c>
+      <c r="B238" t="b">
+        <v>1</v>
+      </c>
+      <c r="C238" t="b">
+        <v>0</v>
+      </c>
+      <c r="D238" t="b">
+        <v>0</v>
+      </c>
+      <c r="E238" t="b">
+        <v>0</v>
+      </c>
+      <c r="F238" t="b">
+        <v>0</v>
+      </c>
+      <c r="G238" t="b">
+        <v>0</v>
+      </c>
+      <c r="H238" t="b">
+        <v>0</v>
+      </c>
+      <c r="I238">
+        <v>1</v>
+      </c>
+      <c r="J238">
+        <v>0.5041399556108799</v>
+      </c>
+      <c r="K238">
+        <v>0.9379107395309157</v>
+      </c>
+      <c r="L238">
+        <v>-0.0005528484870497855</v>
+      </c>
+      <c r="M238">
+        <v>0.4447916666666667</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13">
+      <c r="A239" t="s">
+        <v>241</v>
+      </c>
+      <c r="B239" t="b">
+        <v>1</v>
+      </c>
+      <c r="C239" t="b">
+        <v>0</v>
+      </c>
+      <c r="D239" t="b">
+        <v>0</v>
+      </c>
+      <c r="E239" t="b">
+        <v>0</v>
+      </c>
+      <c r="F239" t="b">
+        <v>0</v>
+      </c>
+      <c r="G239" t="b">
+        <v>0</v>
+      </c>
+      <c r="H239" t="b">
+        <v>0</v>
+      </c>
+      <c r="I239">
+        <v>1</v>
+      </c>
+      <c r="J239">
+        <v>0.4907824101008133</v>
+      </c>
+      <c r="K239">
+        <v>0.9709557512183234</v>
+      </c>
+      <c r="L239">
+        <v>-0.0007712571387079928</v>
+      </c>
+      <c r="M239">
+        <v>0.4385416666666667</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13">
+      <c r="A240" t="s">
+        <v>242</v>
+      </c>
+      <c r="B240" t="b">
+        <v>1</v>
+      </c>
+      <c r="C240" t="b">
+        <v>0</v>
+      </c>
+      <c r="D240" t="b">
+        <v>0</v>
+      </c>
+      <c r="E240" t="b">
+        <v>0</v>
+      </c>
+      <c r="F240" t="b">
+        <v>0</v>
+      </c>
+      <c r="G240" t="b">
+        <v>0</v>
+      </c>
+      <c r="H240" t="b">
+        <v>0</v>
+      </c>
+      <c r="I240">
+        <v>1</v>
+      </c>
+      <c r="J240">
+        <v>0.4909423672431471</v>
+      </c>
+      <c r="K240">
+        <v>0.9575175230782224</v>
+      </c>
+      <c r="L240">
+        <v>-0.0009393748524447957</v>
+      </c>
+      <c r="M240">
+        <v>0.4291666666666667</v>
+      </c>
+    </row>
+    <row r="241" spans="1:13">
+      <c r="A241" t="s">
+        <v>243</v>
+      </c>
+      <c r="B241" t="b">
+        <v>1</v>
+      </c>
+      <c r="C241" t="b">
+        <v>0</v>
+      </c>
+      <c r="D241" t="b">
+        <v>0</v>
+      </c>
+      <c r="E241" t="b">
+        <v>0</v>
+      </c>
+      <c r="F241" t="b">
+        <v>0</v>
+      </c>
+      <c r="G241" t="b">
+        <v>0</v>
+      </c>
+      <c r="H241" t="b">
+        <v>0</v>
+      </c>
+      <c r="I241">
+        <v>1</v>
+      </c>
+      <c r="J241">
+        <v>0.4951541371093768</v>
+      </c>
+      <c r="K241">
+        <v>0.9308585329906285</v>
+      </c>
+      <c r="L241">
+        <v>-0.001040784429799158</v>
+      </c>
+      <c r="M241">
+        <v>0.41875</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13">
+      <c r="A242" t="s">
+        <v>244</v>
+      </c>
+      <c r="B242" t="b">
+        <v>1</v>
+      </c>
+      <c r="C242" t="b">
+        <v>0</v>
+      </c>
+      <c r="D242" t="b">
+        <v>0</v>
+      </c>
+      <c r="E242" t="b">
+        <v>0</v>
+      </c>
+      <c r="F242" t="b">
+        <v>0</v>
+      </c>
+      <c r="G242" t="b">
+        <v>0</v>
+      </c>
+      <c r="H242" t="b">
+        <v>0</v>
+      </c>
+      <c r="I242">
+        <v>1</v>
+      </c>
+      <c r="J242">
         <v>0.4938984167507682</v>
       </c>
-      <c r="K227">
+      <c r="K242">
         <v>0.9193260416617381</v>
       </c>
-      <c r="L227">
+      <c r="L242">
         <v>-0.001247304949413837</v>
       </c>
-      <c r="M227">
+      <c r="M242">
         <v>0.4385416666666667</v>
       </c>
     </row>
